--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03_240626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03_240626.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TungNM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74B4DF3-CC7A-4316-AAEF-6C4675680F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E83E94B-0970-4E97-83FC-B8818EB8205A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,15 +16,15 @@
     <sheet name="XuatKho_SX" sheetId="10" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">XuatKho_SX!$A$9:$F$170</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_SX!$A$1:$J$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">XuatKho_SX!$A$9:$F$172</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_SX!$A$1:$J$183</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="202">
   <si>
     <t>STT</t>
   </si>
@@ -114,9 +114,6 @@
     <t>CS3225X7R106K500NRL</t>
   </si>
   <si>
-    <t>CC0603KRX7R9BB104</t>
-  </si>
-  <si>
     <t>CC0402JRNPO9BN220</t>
   </si>
   <si>
@@ -162,9 +159,6 @@
     <t>CL10A226MQ8NRNE</t>
   </si>
   <si>
-    <t>1206X106K500NT</t>
-  </si>
-  <si>
     <t>CC0402FRNPO9BN120</t>
   </si>
   <si>
@@ -604,90 +598,6 @@
   </si>
   <si>
     <t>Dây nguồn</t>
-  </si>
-  <si>
-    <t>TM-704</t>
-  </si>
-  <si>
-    <t>AC0402FR-0710KL</t>
-  </si>
-  <si>
-    <t>1RC0402F2208</t>
-  </si>
-  <si>
-    <t>GRM21BR61C106KE15L</t>
-  </si>
-  <si>
-    <t>Gerber_Camerabox-gx-V4</t>
-  </si>
-  <si>
-    <t>LTST-C190KSKT</t>
-  </si>
-  <si>
-    <t>CGA0603X5R105K500JT</t>
-  </si>
-  <si>
-    <t>CL10A475KL8NRNC</t>
-  </si>
-  <si>
-    <t>0402N220J500CT</t>
-  </si>
-  <si>
-    <t>GCM155R71H822KA55D</t>
-  </si>
-  <si>
-    <t>TCC1206X7R104K101DT</t>
-  </si>
-  <si>
-    <t>1206B225K101NT</t>
-  </si>
-  <si>
-    <t>0805CG100J500NT</t>
-  </si>
-  <si>
-    <t>PTVS5V0S1UR,115</t>
-  </si>
-  <si>
-    <t>1RC0402F1053</t>
-  </si>
-  <si>
-    <t>CR0402AFX-1002GAS</t>
-  </si>
-  <si>
-    <t>HRC0402F1501DNTO</t>
-  </si>
-  <si>
-    <t>WR04X1911FTL</t>
-  </si>
-  <si>
-    <t>FRH0402D1001TS</t>
-  </si>
-  <si>
-    <t>1RC0402F2201</t>
-  </si>
-  <si>
-    <t>1RC0402F3402</t>
-  </si>
-  <si>
-    <t>AC0402FR-07357KL</t>
-  </si>
-  <si>
-    <t>AC0402FR-07499KL</t>
-  </si>
-  <si>
-    <t>AC0402FR-0775RL</t>
-  </si>
-  <si>
-    <t>RT0603DRD071RL</t>
-  </si>
-  <si>
-    <t>RC1206JR-070RL</t>
-  </si>
-  <si>
-    <t>XRCB2012U801-1R5TF</t>
-  </si>
-  <si>
-    <t>CL21A106KOQNNNE</t>
   </si>
   <si>
     <t>X4621WRS-2x03I-C40D64</t>
@@ -718,6 +628,12 @@
   </si>
   <si>
     <t>Hà Nội, ngày 24 tháng 06 năm 2026</t>
+  </si>
+  <si>
+    <t>ASM_Board_GX</t>
+  </si>
+  <si>
+    <t>ASM_Board_RK3562</t>
   </si>
 </sst>
 </file>
@@ -728,7 +644,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;\ _₫_-;_-@_-"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -830,12 +746,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
@@ -855,7 +765,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -874,14 +784,8 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -990,14 +894,14 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1005,28 +909,13 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1036,7 +925,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1112,103 +1001,82 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,7 +1086,17 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1368,13 +1246,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>488016</xdr:colOff>
-      <xdr:row>201</xdr:row>
+      <xdr:row>173</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>307037</xdr:colOff>
-      <xdr:row>201</xdr:row>
+      <xdr:row>173</xdr:row>
       <xdr:rowOff>3941</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1753,7 +1631,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L224"/>
+  <dimension ref="A1:L196"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
@@ -1763,60 +1641,61 @@
     <col min="5" max="5" width="20.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
     <col min="7" max="12" width="9.140625" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="29.140625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="42" t="s">
+      <c r="A2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="43"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="42" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="43"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="44" t="s">
+      <c r="A4" s="45"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="45"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="40"/>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="54"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="49"/>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
@@ -1827,7 +1706,7 @@
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="26" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1861,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>15</v>
@@ -1870,7 +1749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20">
         <v>1</v>
       </c>
@@ -1878,33 +1757,33 @@
         <v>23</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D10" s="27">
+        <v>165</v>
+      </c>
+      <c r="D10" s="32">
         <v>500</v>
       </c>
-      <c r="E10" s="57" t="s">
-        <v>170</v>
+      <c r="E10" s="52" t="s">
+        <v>168</v>
       </c>
       <c r="F10" s="20"/>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="20">
         <v>2</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" s="27">
+        <v>165</v>
+      </c>
+      <c r="D11" s="32">
         <v>500</v>
       </c>
-      <c r="E11" s="58"/>
+      <c r="E11" s="52"/>
       <c r="F11" s="20"/>
     </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="20">
         <v>3</v>
       </c>
@@ -1912,49 +1791,49 @@
         <v>24</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D12" s="27">
+        <v>165</v>
+      </c>
+      <c r="D12" s="32">
         <v>499</v>
       </c>
-      <c r="E12" s="58"/>
+      <c r="E12" s="52"/>
       <c r="F12" s="20"/>
     </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="20">
         <v>4</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D13" s="27">
+        <v>165</v>
+      </c>
+      <c r="D13" s="32">
         <v>510</v>
       </c>
-      <c r="E13" s="58"/>
+      <c r="E13" s="52"/>
       <c r="F13" s="20"/>
     </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="20">
         <v>5</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D14" s="27">
+        <v>165</v>
+      </c>
+      <c r="D14" s="32">
         <v>6500</v>
       </c>
-      <c r="E14" s="58"/>
+      <c r="E14" s="52"/>
       <c r="F14" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="20">
         <v>6</v>
       </c>
@@ -1962,15 +1841,15 @@
         <v>26</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D15" s="27">
+        <v>165</v>
+      </c>
+      <c r="D15" s="32">
         <v>1000</v>
       </c>
-      <c r="E15" s="58"/>
+      <c r="E15" s="52"/>
       <c r="F15" s="20"/>
     </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="20">
         <v>7</v>
       </c>
@@ -1978,15 +1857,15 @@
         <v>27</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D16" s="27">
+        <v>165</v>
+      </c>
+      <c r="D16" s="32">
         <v>1000</v>
       </c>
-      <c r="E16" s="58"/>
+      <c r="E16" s="52"/>
       <c r="F16" s="20"/>
     </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="20">
         <v>8</v>
       </c>
@@ -1994,382 +1873,382 @@
         <v>28</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D17" s="27">
+        <v>165</v>
+      </c>
+      <c r="D17" s="32">
         <v>2500</v>
       </c>
-      <c r="E17" s="58"/>
+      <c r="E17" s="52"/>
       <c r="F17" s="20"/>
     </row>
-    <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="20">
         <v>9</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D18" s="27">
+        <v>165</v>
+      </c>
+      <c r="D18" s="32">
         <v>2000</v>
       </c>
-      <c r="E18" s="58"/>
+      <c r="E18" s="52"/>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="20">
         <v>10</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D19" s="27">
+        <v>165</v>
+      </c>
+      <c r="D19" s="32">
         <v>1000</v>
       </c>
-      <c r="E19" s="58"/>
+      <c r="E19" s="52"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="20">
         <v>11</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D20" s="27">
+        <v>165</v>
+      </c>
+      <c r="D20" s="32">
         <v>500</v>
       </c>
-      <c r="E20" s="58"/>
+      <c r="E20" s="52"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="20">
         <v>12</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D21" s="27">
+        <v>165</v>
+      </c>
+      <c r="D21" s="32">
         <v>45400</v>
       </c>
-      <c r="E21" s="58"/>
+      <c r="E21" s="52"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="20">
         <v>13</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D22" s="27">
+        <v>165</v>
+      </c>
+      <c r="D22" s="32">
         <v>1000</v>
       </c>
-      <c r="E22" s="58"/>
+      <c r="E22" s="52"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="20">
         <v>14</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D23" s="27">
+        <v>165</v>
+      </c>
+      <c r="D23" s="32">
         <v>500</v>
       </c>
-      <c r="E23" s="58"/>
+      <c r="E23" s="52"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="20">
         <v>15</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D24" s="27">
+        <v>165</v>
+      </c>
+      <c r="D24" s="32">
         <v>520</v>
       </c>
-      <c r="E24" s="58"/>
+      <c r="E24" s="52"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="20">
         <v>16</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D25" s="27">
+        <v>165</v>
+      </c>
+      <c r="D25" s="32">
         <v>500</v>
       </c>
-      <c r="E25" s="58"/>
+      <c r="E25" s="52"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="20">
         <v>17</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D26" s="27">
+        <v>165</v>
+      </c>
+      <c r="D26" s="32">
         <v>1500</v>
       </c>
-      <c r="E26" s="58"/>
+      <c r="E26" s="52"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="20">
         <v>18</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D27" s="27">
+        <v>165</v>
+      </c>
+      <c r="D27" s="32">
         <v>1500</v>
       </c>
-      <c r="E27" s="58"/>
+      <c r="E27" s="52"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="20">
         <v>19</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D28" s="27">
+        <v>165</v>
+      </c>
+      <c r="D28" s="32">
         <v>1500</v>
       </c>
-      <c r="E28" s="58"/>
+      <c r="E28" s="52"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="20">
         <v>20</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D29" s="27">
+        <v>165</v>
+      </c>
+      <c r="D29" s="32">
         <v>1500</v>
       </c>
-      <c r="E29" s="58"/>
+      <c r="E29" s="52"/>
       <c r="F29" s="20"/>
     </row>
-    <row r="30" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="20">
         <v>21</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D30" s="27">
+        <v>165</v>
+      </c>
+      <c r="D30" s="32">
         <v>6500</v>
       </c>
-      <c r="E30" s="58"/>
+      <c r="E30" s="52"/>
       <c r="F30" s="20"/>
     </row>
-    <row r="31" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="20">
         <v>22</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D31" s="27">
+        <v>165</v>
+      </c>
+      <c r="D31" s="32">
         <v>1447</v>
       </c>
-      <c r="E31" s="58"/>
+      <c r="E31" s="52"/>
       <c r="F31" s="20"/>
     </row>
-    <row r="32" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="20">
         <v>23</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D32" s="27">
+        <v>165</v>
+      </c>
+      <c r="D32" s="32">
         <v>14000</v>
       </c>
-      <c r="E32" s="58"/>
+      <c r="E32" s="52"/>
       <c r="F32" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="20">
         <v>24</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" s="27">
+        <v>165</v>
+      </c>
+      <c r="D33" s="32">
         <v>1500</v>
       </c>
-      <c r="E33" s="58"/>
+      <c r="E33" s="52"/>
       <c r="F33" s="20"/>
     </row>
-    <row r="34" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="20">
         <v>25</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D34" s="27">
+        <v>165</v>
+      </c>
+      <c r="D34" s="32">
         <v>5000</v>
       </c>
-      <c r="E34" s="58"/>
+      <c r="E34" s="52"/>
       <c r="F34" s="20"/>
     </row>
-    <row r="35" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="20">
         <v>26</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D35" s="27">
+        <v>165</v>
+      </c>
+      <c r="D35" s="32">
         <v>1500</v>
       </c>
-      <c r="E35" s="58"/>
+      <c r="E35" s="52"/>
       <c r="F35" s="20"/>
     </row>
-    <row r="36" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="20">
         <v>27</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D36" s="27">
+        <v>165</v>
+      </c>
+      <c r="D36" s="32">
         <v>500</v>
       </c>
-      <c r="E36" s="58"/>
+      <c r="E36" s="52"/>
       <c r="F36" s="20"/>
     </row>
-    <row r="37" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="20">
         <v>28</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D37" s="27">
+        <v>165</v>
+      </c>
+      <c r="D37" s="32">
         <v>2000</v>
       </c>
-      <c r="E37" s="58"/>
+      <c r="E37" s="52"/>
       <c r="F37" s="20"/>
     </row>
-    <row r="38" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="20">
         <v>29</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D38" s="27">
+        <v>165</v>
+      </c>
+      <c r="D38" s="32">
         <v>1520</v>
       </c>
-      <c r="E38" s="58"/>
+      <c r="E38" s="52"/>
       <c r="F38" s="20"/>
     </row>
-    <row r="39" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="20">
         <v>30</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D39" s="27">
+        <v>165</v>
+      </c>
+      <c r="D39" s="32">
         <v>1000</v>
       </c>
-      <c r="E39" s="58"/>
+      <c r="E39" s="52"/>
       <c r="F39" s="20"/>
     </row>
-    <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="20">
         <v>31</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D40" s="27">
+        <v>165</v>
+      </c>
+      <c r="D40" s="32">
         <v>500</v>
       </c>
-      <c r="E40" s="58"/>
+      <c r="E40" s="52"/>
       <c r="F40" s="20"/>
     </row>
     <row r="41" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
@@ -2377,15 +2256,15 @@
         <v>32</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D41" s="27">
+        <v>165</v>
+      </c>
+      <c r="D41" s="32">
         <v>520</v>
       </c>
-      <c r="E41" s="58"/>
+      <c r="E41" s="52"/>
       <c r="F41" s="20"/>
     </row>
     <row r="42" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2393,15 +2272,15 @@
         <v>33</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D42" s="27">
+        <v>165</v>
+      </c>
+      <c r="D42" s="32">
         <v>1500</v>
       </c>
-      <c r="E42" s="58"/>
+      <c r="E42" s="52"/>
       <c r="F42" s="20"/>
     </row>
     <row r="43" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2409,15 +2288,15 @@
         <v>34</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D43" s="27">
+        <v>165</v>
+      </c>
+      <c r="D43" s="32">
         <v>1600</v>
       </c>
-      <c r="E43" s="58"/>
+      <c r="E43" s="52"/>
       <c r="F43" s="20"/>
     </row>
     <row r="44" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2425,15 +2304,15 @@
         <v>35</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D44" s="27">
+        <v>165</v>
+      </c>
+      <c r="D44" s="32">
         <v>1000</v>
       </c>
-      <c r="E44" s="58"/>
+      <c r="E44" s="52"/>
       <c r="F44" s="20"/>
     </row>
     <row r="45" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2441,15 +2320,15 @@
         <v>36</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D45" s="27">
+        <v>165</v>
+      </c>
+      <c r="D45" s="32">
         <v>500</v>
       </c>
-      <c r="E45" s="58"/>
+      <c r="E45" s="52"/>
       <c r="F45" s="21"/>
     </row>
     <row r="46" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2457,15 +2336,15 @@
         <v>37</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D46" s="27">
+        <v>165</v>
+      </c>
+      <c r="D46" s="32">
         <v>500</v>
       </c>
-      <c r="E46" s="58"/>
+      <c r="E46" s="52"/>
       <c r="F46" s="20"/>
     </row>
     <row r="47" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2473,15 +2352,15 @@
         <v>38</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D47" s="27">
+        <v>165</v>
+      </c>
+      <c r="D47" s="32">
         <v>500</v>
       </c>
-      <c r="E47" s="58"/>
+      <c r="E47" s="52"/>
       <c r="F47" s="20"/>
     </row>
     <row r="48" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2489,15 +2368,15 @@
         <v>39</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D48" s="27">
+        <v>165</v>
+      </c>
+      <c r="D48" s="32">
         <v>2050</v>
       </c>
-      <c r="E48" s="58"/>
+      <c r="E48" s="52"/>
       <c r="F48" s="20"/>
     </row>
     <row r="49" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2505,15 +2384,15 @@
         <v>40</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D49" s="27">
+        <v>165</v>
+      </c>
+      <c r="D49" s="32">
         <v>500</v>
       </c>
-      <c r="E49" s="58"/>
+      <c r="E49" s="52"/>
       <c r="F49" s="20"/>
     </row>
     <row r="50" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2521,15 +2400,15 @@
         <v>41</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D50" s="27">
+        <v>165</v>
+      </c>
+      <c r="D50" s="32">
         <v>500</v>
       </c>
-      <c r="E50" s="58"/>
+      <c r="E50" s="52"/>
       <c r="F50" s="20"/>
     </row>
     <row r="51" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2537,17 +2416,17 @@
         <v>42</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D51" s="27">
+        <v>165</v>
+      </c>
+      <c r="D51" s="32">
         <v>1600</v>
       </c>
-      <c r="E51" s="58"/>
+      <c r="E51" s="52"/>
       <c r="F51" s="21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2555,15 +2434,15 @@
         <v>43</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D52" s="27">
+        <v>165</v>
+      </c>
+      <c r="D52" s="32">
         <v>600</v>
       </c>
-      <c r="E52" s="58"/>
+      <c r="E52" s="52"/>
       <c r="F52" s="20"/>
     </row>
     <row r="53" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2571,15 +2450,15 @@
         <v>44</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D53" s="27">
+        <v>165</v>
+      </c>
+      <c r="D53" s="32">
         <v>1000</v>
       </c>
-      <c r="E53" s="58"/>
+      <c r="E53" s="52"/>
       <c r="F53" s="20"/>
     </row>
     <row r="54" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2587,15 +2466,15 @@
         <v>45</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D54" s="27">
+        <v>165</v>
+      </c>
+      <c r="D54" s="32">
         <v>5500</v>
       </c>
-      <c r="E54" s="58"/>
+      <c r="E54" s="52"/>
       <c r="F54" s="20"/>
     </row>
     <row r="55" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2603,15 +2482,15 @@
         <v>46</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D55" s="27">
+        <v>165</v>
+      </c>
+      <c r="D55" s="32">
         <v>3550</v>
       </c>
-      <c r="E55" s="58"/>
+      <c r="E55" s="52"/>
       <c r="F55" s="20"/>
     </row>
     <row r="56" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2619,15 +2498,15 @@
         <v>47</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D56" s="27">
+        <v>165</v>
+      </c>
+      <c r="D56" s="32">
         <v>550</v>
       </c>
-      <c r="E56" s="58"/>
+      <c r="E56" s="52"/>
       <c r="F56" s="20"/>
     </row>
     <row r="57" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2635,15 +2514,15 @@
         <v>48</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D57" s="27">
+        <v>165</v>
+      </c>
+      <c r="D57" s="32">
         <v>1000</v>
       </c>
-      <c r="E57" s="58"/>
+      <c r="E57" s="52"/>
       <c r="F57" s="20"/>
     </row>
     <row r="58" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2651,15 +2530,15 @@
         <v>49</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D58" s="27">
+        <v>165</v>
+      </c>
+      <c r="D58" s="32">
         <v>2000</v>
       </c>
-      <c r="E58" s="58"/>
+      <c r="E58" s="52"/>
       <c r="F58" s="20"/>
     </row>
     <row r="59" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2667,17 +2546,17 @@
         <v>50</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D59" s="27">
+        <v>165</v>
+      </c>
+      <c r="D59" s="32">
         <v>10770</v>
       </c>
-      <c r="E59" s="58"/>
+      <c r="E59" s="52"/>
       <c r="F59" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2685,15 +2564,15 @@
         <v>51</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D60" s="27">
+        <v>165</v>
+      </c>
+      <c r="D60" s="32">
         <v>1000</v>
       </c>
-      <c r="E60" s="58"/>
+      <c r="E60" s="52"/>
       <c r="F60" s="20"/>
     </row>
     <row r="61" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2701,15 +2580,15 @@
         <v>52</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D61" s="27">
+        <v>165</v>
+      </c>
+      <c r="D61" s="32">
         <v>2500</v>
       </c>
-      <c r="E61" s="58"/>
+      <c r="E61" s="52"/>
       <c r="F61" s="20"/>
     </row>
     <row r="62" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2717,15 +2596,15 @@
         <v>53</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D62" s="27">
+        <v>165</v>
+      </c>
+      <c r="D62" s="32">
         <v>1000</v>
       </c>
-      <c r="E62" s="58"/>
+      <c r="E62" s="52"/>
       <c r="F62" s="20"/>
     </row>
     <row r="63" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2733,17 +2612,17 @@
         <v>54</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D63" s="27">
+        <v>165</v>
+      </c>
+      <c r="D63" s="32">
         <v>500</v>
       </c>
-      <c r="E63" s="58"/>
+      <c r="E63" s="52"/>
       <c r="F63" s="21" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2751,15 +2630,15 @@
         <v>55</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D64" s="27">
+        <v>165</v>
+      </c>
+      <c r="D64" s="32">
         <v>1000</v>
       </c>
-      <c r="E64" s="58"/>
+      <c r="E64" s="52"/>
       <c r="F64" s="20"/>
     </row>
     <row r="65" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2767,15 +2646,15 @@
         <v>56</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D65" s="27">
+        <v>165</v>
+      </c>
+      <c r="D65" s="32">
         <v>1500</v>
       </c>
-      <c r="E65" s="58"/>
+      <c r="E65" s="52"/>
       <c r="F65" s="20"/>
     </row>
     <row r="66" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2783,15 +2662,15 @@
         <v>57</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D66" s="27">
+        <v>165</v>
+      </c>
+      <c r="D66" s="32">
         <v>5500</v>
       </c>
-      <c r="E66" s="58"/>
+      <c r="E66" s="52"/>
       <c r="F66" s="20"/>
     </row>
     <row r="67" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2799,15 +2678,15 @@
         <v>58</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D67" s="27">
+        <v>165</v>
+      </c>
+      <c r="D67" s="32">
         <v>3000</v>
       </c>
-      <c r="E67" s="58"/>
+      <c r="E67" s="52"/>
       <c r="F67" s="20"/>
     </row>
     <row r="68" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2815,15 +2694,15 @@
         <v>59</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D68" s="27">
+        <v>165</v>
+      </c>
+      <c r="D68" s="32">
         <v>7400</v>
       </c>
-      <c r="E68" s="58"/>
+      <c r="E68" s="52"/>
       <c r="F68" s="20"/>
     </row>
     <row r="69" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2831,15 +2710,15 @@
         <v>60</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D69" s="27">
+        <v>165</v>
+      </c>
+      <c r="D69" s="32">
         <v>1500</v>
       </c>
-      <c r="E69" s="58"/>
+      <c r="E69" s="52"/>
       <c r="F69" s="20"/>
     </row>
     <row r="70" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2847,15 +2726,15 @@
         <v>61</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D70" s="27">
+        <v>165</v>
+      </c>
+      <c r="D70" s="32">
         <v>550</v>
       </c>
-      <c r="E70" s="58"/>
+      <c r="E70" s="52"/>
       <c r="F70" s="20"/>
     </row>
     <row r="71" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2863,15 +2742,15 @@
         <v>62</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D71" s="27">
+        <v>165</v>
+      </c>
+      <c r="D71" s="32">
         <v>1000</v>
       </c>
-      <c r="E71" s="58"/>
+      <c r="E71" s="52"/>
       <c r="F71" s="20"/>
     </row>
     <row r="72" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2879,15 +2758,15 @@
         <v>63</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D72" s="27">
+        <v>165</v>
+      </c>
+      <c r="D72" s="32">
         <v>550</v>
       </c>
-      <c r="E72" s="58"/>
+      <c r="E72" s="52"/>
       <c r="F72" s="20"/>
     </row>
     <row r="73" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2895,15 +2774,15 @@
         <v>64</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D73" s="27">
+        <v>165</v>
+      </c>
+      <c r="D73" s="32">
         <v>500</v>
       </c>
-      <c r="E73" s="58"/>
+      <c r="E73" s="52"/>
       <c r="F73" s="20"/>
     </row>
     <row r="74" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2911,15 +2790,15 @@
         <v>65</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D74" s="27">
+        <v>165</v>
+      </c>
+      <c r="D74" s="32">
         <v>2500</v>
       </c>
-      <c r="E74" s="58"/>
+      <c r="E74" s="52"/>
       <c r="F74" s="20"/>
     </row>
     <row r="75" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2927,15 +2806,15 @@
         <v>66</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D75" s="27">
+        <v>165</v>
+      </c>
+      <c r="D75" s="32">
         <v>1500</v>
       </c>
-      <c r="E75" s="58"/>
+      <c r="E75" s="52"/>
       <c r="F75" s="20"/>
     </row>
     <row r="76" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2943,15 +2822,15 @@
         <v>67</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D76" s="27">
+        <v>165</v>
+      </c>
+      <c r="D76" s="32">
         <v>1000</v>
       </c>
-      <c r="E76" s="58"/>
+      <c r="E76" s="52"/>
       <c r="F76" s="20"/>
     </row>
     <row r="77" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2959,15 +2838,15 @@
         <v>68</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D77" s="27">
+        <v>165</v>
+      </c>
+      <c r="D77" s="32">
         <v>550</v>
       </c>
-      <c r="E77" s="58"/>
+      <c r="E77" s="52"/>
       <c r="F77" s="20"/>
     </row>
     <row r="78" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2975,15 +2854,15 @@
         <v>69</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D78" s="27">
+        <v>165</v>
+      </c>
+      <c r="D78" s="32">
         <v>1000</v>
       </c>
-      <c r="E78" s="58"/>
+      <c r="E78" s="52"/>
       <c r="F78" s="20"/>
     </row>
     <row r="79" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2991,15 +2870,15 @@
         <v>70</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D79" s="27">
+        <v>165</v>
+      </c>
+      <c r="D79" s="32">
         <v>1000</v>
       </c>
-      <c r="E79" s="58"/>
+      <c r="E79" s="52"/>
       <c r="F79" s="20"/>
     </row>
     <row r="80" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3007,15 +2886,15 @@
         <v>71</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D80" s="27">
+        <v>165</v>
+      </c>
+      <c r="D80" s="32">
         <v>500</v>
       </c>
-      <c r="E80" s="58"/>
+      <c r="E80" s="52"/>
       <c r="F80" s="20"/>
     </row>
     <row r="81" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3023,15 +2902,15 @@
         <v>72</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D81" s="27">
+        <v>165</v>
+      </c>
+      <c r="D81" s="32">
         <v>600</v>
       </c>
-      <c r="E81" s="58"/>
+      <c r="E81" s="52"/>
       <c r="F81" s="20"/>
     </row>
     <row r="82" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3039,15 +2918,15 @@
         <v>73</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D82" s="27">
+        <v>165</v>
+      </c>
+      <c r="D82" s="32">
         <v>500</v>
       </c>
-      <c r="E82" s="58"/>
+      <c r="E82" s="52"/>
       <c r="F82" s="20"/>
     </row>
     <row r="83" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3055,15 +2934,15 @@
         <v>74</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D83" s="27">
+        <v>165</v>
+      </c>
+      <c r="D83" s="32">
         <v>500</v>
       </c>
-      <c r="E83" s="58"/>
+      <c r="E83" s="52"/>
       <c r="F83" s="20"/>
     </row>
     <row r="84" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3071,15 +2950,15 @@
         <v>75</v>
       </c>
       <c r="B84" s="21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D84" s="27">
+        <v>165</v>
+      </c>
+      <c r="D84" s="32">
         <v>500</v>
       </c>
-      <c r="E84" s="58"/>
+      <c r="E84" s="52"/>
       <c r="F84" s="20"/>
     </row>
     <row r="85" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3087,15 +2966,15 @@
         <v>76</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D85" s="27">
+        <v>165</v>
+      </c>
+      <c r="D85" s="32">
         <v>1500</v>
       </c>
-      <c r="E85" s="58"/>
+      <c r="E85" s="52"/>
       <c r="F85" s="20"/>
     </row>
     <row r="86" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3103,15 +2982,15 @@
         <v>77</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D86" s="27">
+        <v>165</v>
+      </c>
+      <c r="D86" s="32">
         <v>500</v>
       </c>
-      <c r="E86" s="58"/>
+      <c r="E86" s="52"/>
       <c r="F86" s="20"/>
     </row>
     <row r="87" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3119,15 +2998,15 @@
         <v>78</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D87" s="27">
+        <v>165</v>
+      </c>
+      <c r="D87" s="32">
         <v>500</v>
       </c>
-      <c r="E87" s="58"/>
+      <c r="E87" s="52"/>
       <c r="F87" s="20"/>
     </row>
     <row r="88" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3135,15 +3014,15 @@
         <v>79</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D88" s="27">
+        <v>165</v>
+      </c>
+      <c r="D88" s="32">
         <v>1000</v>
       </c>
-      <c r="E88" s="58"/>
+      <c r="E88" s="52"/>
       <c r="F88" s="20"/>
     </row>
     <row r="89" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3151,15 +3030,15 @@
         <v>80</v>
       </c>
       <c r="B89" s="21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D89" s="27">
+        <v>165</v>
+      </c>
+      <c r="D89" s="32">
         <v>1000</v>
       </c>
-      <c r="E89" s="58"/>
+      <c r="E89" s="52"/>
       <c r="F89" s="20"/>
     </row>
     <row r="90" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3167,15 +3046,15 @@
         <v>81</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D90" s="27">
+        <v>165</v>
+      </c>
+      <c r="D90" s="32">
         <v>4000</v>
       </c>
-      <c r="E90" s="58"/>
+      <c r="E90" s="52"/>
       <c r="F90" s="20"/>
     </row>
     <row r="91" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3183,15 +3062,15 @@
         <v>82</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D91" s="27">
+        <v>165</v>
+      </c>
+      <c r="D91" s="32">
         <v>2500</v>
       </c>
-      <c r="E91" s="58"/>
+      <c r="E91" s="52"/>
       <c r="F91" s="20"/>
     </row>
     <row r="92" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3199,15 +3078,15 @@
         <v>83</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D92" s="27">
+        <v>165</v>
+      </c>
+      <c r="D92" s="32">
         <v>500</v>
       </c>
-      <c r="E92" s="58"/>
+      <c r="E92" s="52"/>
       <c r="F92" s="20"/>
     </row>
     <row r="93" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3215,15 +3094,15 @@
         <v>84</v>
       </c>
       <c r="B93" s="21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D93" s="27">
+        <v>165</v>
+      </c>
+      <c r="D93" s="32">
         <v>500</v>
       </c>
-      <c r="E93" s="58"/>
+      <c r="E93" s="52"/>
       <c r="F93" s="20"/>
     </row>
     <row r="94" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3231,15 +3110,15 @@
         <v>85</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D94" s="27">
+        <v>165</v>
+      </c>
+      <c r="D94" s="32">
         <v>8830</v>
       </c>
-      <c r="E94" s="58"/>
+      <c r="E94" s="52"/>
       <c r="F94" s="20"/>
     </row>
     <row r="95" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3247,15 +3126,15 @@
         <v>86</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D95" s="27">
+        <v>165</v>
+      </c>
+      <c r="D95" s="32">
         <v>500</v>
       </c>
-      <c r="E95" s="58"/>
+      <c r="E95" s="52"/>
       <c r="F95" s="20"/>
     </row>
     <row r="96" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3263,15 +3142,15 @@
         <v>87</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D96" s="27">
+        <v>165</v>
+      </c>
+      <c r="D96" s="32">
         <v>5476</v>
       </c>
-      <c r="E96" s="58"/>
+      <c r="E96" s="52"/>
       <c r="F96" s="20"/>
     </row>
     <row r="97" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3279,15 +3158,15 @@
         <v>88</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D97" s="27">
+        <v>165</v>
+      </c>
+      <c r="D97" s="32">
         <v>1000</v>
       </c>
-      <c r="E97" s="58"/>
+      <c r="E97" s="52"/>
       <c r="F97" s="20"/>
     </row>
     <row r="98" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3295,15 +3174,15 @@
         <v>89</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C98" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D98" s="27">
+        <v>165</v>
+      </c>
+      <c r="D98" s="32">
         <v>500</v>
       </c>
-      <c r="E98" s="58"/>
+      <c r="E98" s="52"/>
       <c r="F98" s="20"/>
     </row>
     <row r="99" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3311,15 +3190,15 @@
         <v>90</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D99" s="27">
+        <v>165</v>
+      </c>
+      <c r="D99" s="32">
         <v>6500</v>
       </c>
-      <c r="E99" s="58"/>
+      <c r="E99" s="52"/>
       <c r="F99" s="20"/>
     </row>
     <row r="100" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3327,15 +3206,15 @@
         <v>91</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D100" s="27">
+        <v>165</v>
+      </c>
+      <c r="D100" s="32">
         <v>1000</v>
       </c>
-      <c r="E100" s="58"/>
+      <c r="E100" s="52"/>
       <c r="F100" s="20"/>
     </row>
     <row r="101" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3343,15 +3222,15 @@
         <v>92</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D101" s="27">
+        <v>165</v>
+      </c>
+      <c r="D101" s="32">
         <v>1100</v>
       </c>
-      <c r="E101" s="58"/>
+      <c r="E101" s="52"/>
       <c r="F101" s="20"/>
     </row>
     <row r="102" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3359,15 +3238,15 @@
         <v>93</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C102" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D102" s="27">
+        <v>165</v>
+      </c>
+      <c r="D102" s="32">
         <v>21980</v>
       </c>
-      <c r="E102" s="58"/>
+      <c r="E102" s="52"/>
       <c r="F102" s="20"/>
     </row>
     <row r="103" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3375,15 +3254,15 @@
         <v>94</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D103" s="27">
+        <v>165</v>
+      </c>
+      <c r="D103" s="32">
         <v>24500</v>
       </c>
-      <c r="E103" s="58"/>
+      <c r="E103" s="52"/>
       <c r="F103" s="20"/>
     </row>
     <row r="104" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3391,15 +3270,15 @@
         <v>95</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D104" s="27">
+        <v>165</v>
+      </c>
+      <c r="D104" s="32">
         <v>1000</v>
       </c>
-      <c r="E104" s="58"/>
+      <c r="E104" s="52"/>
       <c r="F104" s="20"/>
     </row>
     <row r="105" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3407,15 +3286,15 @@
         <v>96</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C105" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D105" s="27">
+        <v>165</v>
+      </c>
+      <c r="D105" s="32">
         <v>1000</v>
       </c>
-      <c r="E105" s="58"/>
+      <c r="E105" s="52"/>
       <c r="F105" s="20"/>
     </row>
     <row r="106" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3423,15 +3302,15 @@
         <v>97</v>
       </c>
       <c r="B106" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C106" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D106" s="27">
+        <v>165</v>
+      </c>
+      <c r="D106" s="32">
         <v>1000</v>
       </c>
-      <c r="E106" s="58"/>
+      <c r="E106" s="52"/>
       <c r="F106" s="20"/>
     </row>
     <row r="107" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3439,15 +3318,15 @@
         <v>98</v>
       </c>
       <c r="B107" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D107" s="27">
+        <v>165</v>
+      </c>
+      <c r="D107" s="32">
         <v>500</v>
       </c>
-      <c r="E107" s="58"/>
+      <c r="E107" s="52"/>
       <c r="F107" s="20"/>
     </row>
     <row r="108" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3455,15 +3334,15 @@
         <v>99</v>
       </c>
       <c r="B108" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C108" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D108" s="27">
+        <v>165</v>
+      </c>
+      <c r="D108" s="32">
         <v>1000</v>
       </c>
-      <c r="E108" s="58"/>
+      <c r="E108" s="52"/>
       <c r="F108" s="20"/>
     </row>
     <row r="109" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3471,15 +3350,15 @@
         <v>100</v>
       </c>
       <c r="B109" s="21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C109" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D109" s="27">
+        <v>165</v>
+      </c>
+      <c r="D109" s="32">
         <v>1000</v>
       </c>
-      <c r="E109" s="58"/>
+      <c r="E109" s="52"/>
       <c r="F109" s="20"/>
     </row>
     <row r="110" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3487,15 +3366,15 @@
         <v>101</v>
       </c>
       <c r="B110" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C110" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D110" s="27">
+        <v>165</v>
+      </c>
+      <c r="D110" s="32">
         <v>3500</v>
       </c>
-      <c r="E110" s="58"/>
+      <c r="E110" s="52"/>
       <c r="F110" s="20"/>
     </row>
     <row r="111" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3503,15 +3382,15 @@
         <v>102</v>
       </c>
       <c r="B111" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C111" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D111" s="27">
+        <v>165</v>
+      </c>
+      <c r="D111" s="32">
         <v>14900</v>
       </c>
-      <c r="E111" s="58"/>
+      <c r="E111" s="52"/>
       <c r="F111" s="20"/>
     </row>
     <row r="112" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3519,15 +3398,15 @@
         <v>103</v>
       </c>
       <c r="B112" s="21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D112" s="27">
+        <v>165</v>
+      </c>
+      <c r="D112" s="32">
         <v>1000</v>
       </c>
-      <c r="E112" s="58"/>
+      <c r="E112" s="52"/>
       <c r="F112" s="20"/>
     </row>
     <row r="113" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3535,15 +3414,15 @@
         <v>104</v>
       </c>
       <c r="B113" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C113" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D113" s="27">
+        <v>165</v>
+      </c>
+      <c r="D113" s="32">
         <v>500</v>
       </c>
-      <c r="E113" s="58"/>
+      <c r="E113" s="52"/>
       <c r="F113" s="20"/>
     </row>
     <row r="114" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3551,15 +3430,15 @@
         <v>105</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C114" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D114" s="27">
+        <v>165</v>
+      </c>
+      <c r="D114" s="32">
         <v>500</v>
       </c>
-      <c r="E114" s="58"/>
+      <c r="E114" s="52"/>
       <c r="F114" s="20"/>
     </row>
     <row r="115" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3567,15 +3446,15 @@
         <v>106</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C115" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D115" s="27">
+        <v>165</v>
+      </c>
+      <c r="D115" s="32">
         <v>500</v>
       </c>
-      <c r="E115" s="58"/>
+      <c r="E115" s="52"/>
       <c r="F115" s="20"/>
     </row>
     <row r="116" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3583,15 +3462,15 @@
         <v>107</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D116" s="27">
+        <v>165</v>
+      </c>
+      <c r="D116" s="32">
         <v>10000</v>
       </c>
-      <c r="E116" s="58"/>
+      <c r="E116" s="52"/>
       <c r="F116" s="20"/>
     </row>
     <row r="117" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3599,15 +3478,15 @@
         <v>108</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D117" s="27">
+        <v>165</v>
+      </c>
+      <c r="D117" s="32">
         <v>1000</v>
       </c>
-      <c r="E117" s="58"/>
+      <c r="E117" s="52"/>
       <c r="F117" s="20"/>
     </row>
     <row r="118" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3615,15 +3494,15 @@
         <v>109</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C118" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D118" s="27">
+        <v>165</v>
+      </c>
+      <c r="D118" s="32">
         <v>26500</v>
       </c>
-      <c r="E118" s="58"/>
+      <c r="E118" s="52"/>
       <c r="F118" s="20"/>
     </row>
     <row r="119" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3631,15 +3510,15 @@
         <v>110</v>
       </c>
       <c r="B119" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D119" s="27">
+        <v>165</v>
+      </c>
+      <c r="D119" s="32">
         <v>1000</v>
       </c>
-      <c r="E119" s="58"/>
+      <c r="E119" s="52"/>
       <c r="F119" s="20"/>
     </row>
     <row r="120" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3647,15 +3526,15 @@
         <v>111</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C120" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D120" s="27">
+        <v>165</v>
+      </c>
+      <c r="D120" s="32">
         <v>1600</v>
       </c>
-      <c r="E120" s="58"/>
+      <c r="E120" s="52"/>
       <c r="F120" s="20"/>
     </row>
     <row r="121" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3663,15 +3542,15 @@
         <v>112</v>
       </c>
       <c r="B121" s="21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C121" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D121" s="27">
+        <v>165</v>
+      </c>
+      <c r="D121" s="32">
         <v>13800</v>
       </c>
-      <c r="E121" s="58"/>
+      <c r="E121" s="52"/>
       <c r="F121" s="20"/>
     </row>
     <row r="122" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3679,15 +3558,15 @@
         <v>113</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D122" s="27">
+        <v>165</v>
+      </c>
+      <c r="D122" s="32">
         <v>1000</v>
       </c>
-      <c r="E122" s="58"/>
+      <c r="E122" s="52"/>
       <c r="F122" s="20"/>
     </row>
     <row r="123" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3695,15 +3574,15 @@
         <v>114</v>
       </c>
       <c r="B123" s="21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C123" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D123" s="27">
+        <v>165</v>
+      </c>
+      <c r="D123" s="32">
         <v>1000</v>
       </c>
-      <c r="E123" s="58"/>
+      <c r="E123" s="52"/>
       <c r="F123" s="20"/>
     </row>
     <row r="124" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3711,15 +3590,15 @@
         <v>115</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C124" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D124" s="27">
+        <v>165</v>
+      </c>
+      <c r="D124" s="32">
         <v>5600</v>
       </c>
-      <c r="E124" s="58"/>
+      <c r="E124" s="52"/>
       <c r="F124" s="20"/>
     </row>
     <row r="125" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3727,15 +3606,15 @@
         <v>116</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C125" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D125" s="27">
+        <v>165</v>
+      </c>
+      <c r="D125" s="32">
         <v>2000</v>
       </c>
-      <c r="E125" s="58"/>
+      <c r="E125" s="52"/>
       <c r="F125" s="20"/>
     </row>
     <row r="126" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3743,15 +3622,15 @@
         <v>117</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C126" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D126" s="27">
+        <v>165</v>
+      </c>
+      <c r="D126" s="32">
         <v>1000</v>
       </c>
-      <c r="E126" s="58"/>
+      <c r="E126" s="52"/>
       <c r="F126" s="20"/>
     </row>
     <row r="127" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3759,15 +3638,15 @@
         <v>118</v>
       </c>
       <c r="B127" s="21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C127" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D127" s="27">
+        <v>165</v>
+      </c>
+      <c r="D127" s="32">
         <v>11500</v>
       </c>
-      <c r="E127" s="58"/>
+      <c r="E127" s="52"/>
       <c r="F127" s="20"/>
     </row>
     <row r="128" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3775,15 +3654,15 @@
         <v>119</v>
       </c>
       <c r="B128" s="21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C128" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D128" s="27">
+        <v>165</v>
+      </c>
+      <c r="D128" s="32">
         <v>500</v>
       </c>
-      <c r="E128" s="58"/>
+      <c r="E128" s="52"/>
       <c r="F128" s="20"/>
     </row>
     <row r="129" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3791,15 +3670,15 @@
         <v>120</v>
       </c>
       <c r="B129" s="21" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C129" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D129" s="27">
+        <v>165</v>
+      </c>
+      <c r="D129" s="32">
         <v>1000</v>
       </c>
-      <c r="E129" s="58"/>
+      <c r="E129" s="52"/>
       <c r="F129" s="20"/>
     </row>
     <row r="130" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3807,15 +3686,15 @@
         <v>121</v>
       </c>
       <c r="B130" s="21" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C130" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D130" s="27">
+        <v>165</v>
+      </c>
+      <c r="D130" s="32">
         <v>1000</v>
       </c>
-      <c r="E130" s="58"/>
+      <c r="E130" s="52"/>
       <c r="F130" s="20"/>
     </row>
     <row r="131" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3823,15 +3702,15 @@
         <v>122</v>
       </c>
       <c r="B131" s="21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C131" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D131" s="27">
+        <v>165</v>
+      </c>
+      <c r="D131" s="32">
         <v>700</v>
       </c>
-      <c r="E131" s="58"/>
+      <c r="E131" s="52"/>
       <c r="F131" s="20"/>
     </row>
     <row r="132" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3839,15 +3718,15 @@
         <v>123</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C132" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D132" s="27">
+        <v>165</v>
+      </c>
+      <c r="D132" s="32">
         <v>1000</v>
       </c>
-      <c r="E132" s="58"/>
+      <c r="E132" s="52"/>
       <c r="F132" s="20"/>
     </row>
     <row r="133" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3855,15 +3734,15 @@
         <v>124</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C133" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D133" s="27">
+        <v>165</v>
+      </c>
+      <c r="D133" s="32">
         <v>1000</v>
       </c>
-      <c r="E133" s="58"/>
+      <c r="E133" s="52"/>
       <c r="F133" s="20"/>
     </row>
     <row r="134" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3871,15 +3750,15 @@
         <v>125</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C134" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D134" s="27">
+        <v>165</v>
+      </c>
+      <c r="D134" s="32">
         <v>3455</v>
       </c>
-      <c r="E134" s="58"/>
+      <c r="E134" s="52"/>
       <c r="F134" s="20"/>
     </row>
     <row r="135" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3887,15 +3766,15 @@
         <v>126</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C135" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D135" s="27">
+        <v>165</v>
+      </c>
+      <c r="D135" s="32">
         <v>500</v>
       </c>
-      <c r="E135" s="58"/>
+      <c r="E135" s="52"/>
       <c r="F135" s="20"/>
     </row>
     <row r="136" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3903,15 +3782,15 @@
         <v>127</v>
       </c>
       <c r="B136" s="21" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C136" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D136" s="27">
+        <v>165</v>
+      </c>
+      <c r="D136" s="32">
         <v>500</v>
       </c>
-      <c r="E136" s="58"/>
+      <c r="E136" s="52"/>
       <c r="F136" s="20"/>
     </row>
     <row r="137" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3919,15 +3798,15 @@
         <v>128</v>
       </c>
       <c r="B137" s="21" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C137" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D137" s="27">
+        <v>165</v>
+      </c>
+      <c r="D137" s="32">
         <v>1000</v>
       </c>
-      <c r="E137" s="58"/>
+      <c r="E137" s="52"/>
       <c r="F137" s="20"/>
     </row>
     <row r="138" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3935,15 +3814,15 @@
         <v>129</v>
       </c>
       <c r="B138" s="21" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C138" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D138" s="27">
+        <v>165</v>
+      </c>
+      <c r="D138" s="32">
         <v>2000</v>
       </c>
-      <c r="E138" s="58"/>
+      <c r="E138" s="52"/>
       <c r="F138" s="20"/>
     </row>
     <row r="139" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3951,15 +3830,15 @@
         <v>130</v>
       </c>
       <c r="B139" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C139" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D139" s="27">
+        <v>165</v>
+      </c>
+      <c r="D139" s="32">
         <v>2000</v>
       </c>
-      <c r="E139" s="58"/>
+      <c r="E139" s="52"/>
       <c r="F139" s="20"/>
     </row>
     <row r="140" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3967,15 +3846,15 @@
         <v>131</v>
       </c>
       <c r="B140" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C140" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D140" s="27">
+        <v>165</v>
+      </c>
+      <c r="D140" s="32">
         <v>550</v>
       </c>
-      <c r="E140" s="58"/>
+      <c r="E140" s="52"/>
       <c r="F140" s="22"/>
     </row>
     <row r="141" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3983,15 +3862,15 @@
         <v>132</v>
       </c>
       <c r="B141" s="21" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C141" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D141" s="27">
+        <v>165</v>
+      </c>
+      <c r="D141" s="32">
         <v>1000</v>
       </c>
-      <c r="E141" s="58"/>
+      <c r="E141" s="52"/>
       <c r="F141" s="20"/>
     </row>
     <row r="142" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3999,15 +3878,15 @@
         <v>133</v>
       </c>
       <c r="B142" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C142" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D142" s="27">
+        <v>165</v>
+      </c>
+      <c r="D142" s="32">
         <v>12750</v>
       </c>
-      <c r="E142" s="58"/>
+      <c r="E142" s="52"/>
       <c r="F142" s="20"/>
     </row>
     <row r="143" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4015,15 +3894,15 @@
         <v>134</v>
       </c>
       <c r="B143" s="21" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C143" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D143" s="27">
+        <v>165</v>
+      </c>
+      <c r="D143" s="32">
         <v>500</v>
       </c>
-      <c r="E143" s="58"/>
+      <c r="E143" s="52"/>
       <c r="F143" s="20"/>
     </row>
     <row r="144" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4031,15 +3910,15 @@
         <v>135</v>
       </c>
       <c r="B144" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C144" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D144" s="27">
+        <v>165</v>
+      </c>
+      <c r="D144" s="32">
         <v>500</v>
       </c>
-      <c r="E144" s="58"/>
+      <c r="E144" s="52"/>
       <c r="F144" s="20"/>
     </row>
     <row r="145" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4047,15 +3926,15 @@
         <v>136</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C145" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D145" s="27">
+        <v>165</v>
+      </c>
+      <c r="D145" s="32">
         <v>1500</v>
       </c>
-      <c r="E145" s="58"/>
+      <c r="E145" s="52"/>
       <c r="F145" s="20"/>
     </row>
     <row r="146" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4063,15 +3942,15 @@
         <v>137</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C146" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D146" s="27">
+        <v>165</v>
+      </c>
+      <c r="D146" s="32">
         <v>1000</v>
       </c>
-      <c r="E146" s="58"/>
+      <c r="E146" s="52"/>
       <c r="F146" s="20"/>
     </row>
     <row r="147" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4079,15 +3958,15 @@
         <v>138</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C147" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D147" s="27">
+        <v>165</v>
+      </c>
+      <c r="D147" s="32">
         <v>500</v>
       </c>
-      <c r="E147" s="58"/>
+      <c r="E147" s="52"/>
       <c r="F147" s="20"/>
     </row>
     <row r="148" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4095,17 +3974,17 @@
         <v>139</v>
       </c>
       <c r="B148" s="21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C148" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D148" s="27">
+        <v>165</v>
+      </c>
+      <c r="D148" s="32">
         <v>500</v>
       </c>
-      <c r="E148" s="58"/>
+      <c r="E148" s="52"/>
       <c r="F148" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="149" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4113,15 +3992,15 @@
         <v>140</v>
       </c>
       <c r="B149" s="21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C149" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D149" s="27">
+        <v>165</v>
+      </c>
+      <c r="D149" s="32">
         <v>1000</v>
       </c>
-      <c r="E149" s="58"/>
+      <c r="E149" s="52"/>
       <c r="F149" s="20"/>
     </row>
     <row r="150" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4129,15 +4008,15 @@
         <v>141</v>
       </c>
       <c r="B150" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C150" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D150" s="27">
+        <v>165</v>
+      </c>
+      <c r="D150" s="32">
         <v>500</v>
       </c>
-      <c r="E150" s="58"/>
+      <c r="E150" s="52"/>
       <c r="F150" s="20"/>
     </row>
     <row r="151" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
@@ -4145,17 +4024,17 @@
         <v>142</v>
       </c>
       <c r="B151" s="21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C151" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D151" s="27">
+        <v>165</v>
+      </c>
+      <c r="D151" s="32">
         <v>1005</v>
       </c>
-      <c r="E151" s="58"/>
+      <c r="E151" s="52"/>
       <c r="F151" s="20" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
     </row>
     <row r="152" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4163,15 +4042,15 @@
         <v>143</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C152" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D152" s="27">
+        <v>165</v>
+      </c>
+      <c r="D152" s="32">
         <v>500</v>
       </c>
-      <c r="E152" s="58"/>
+      <c r="E152" s="52"/>
       <c r="F152" s="20"/>
     </row>
     <row r="153" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4179,15 +4058,15 @@
         <v>144</v>
       </c>
       <c r="B153" s="21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C153" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D153" s="27">
+        <v>165</v>
+      </c>
+      <c r="D153" s="32">
         <v>3075</v>
       </c>
-      <c r="E153" s="58"/>
+      <c r="E153" s="52"/>
       <c r="F153" s="20"/>
     </row>
     <row r="154" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4195,17 +4074,17 @@
         <v>145</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="C154" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D154" s="27">
+        <v>165</v>
+      </c>
+      <c r="D154" s="32">
         <v>3500</v>
       </c>
-      <c r="E154" s="58"/>
+      <c r="E154" s="52"/>
       <c r="F154" s="21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="155" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4213,15 +4092,15 @@
         <v>146</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C155" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D155" s="27">
+        <v>165</v>
+      </c>
+      <c r="D155" s="32">
         <v>2200</v>
       </c>
-      <c r="E155" s="58"/>
+      <c r="E155" s="52"/>
       <c r="F155" s="20"/>
     </row>
     <row r="156" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4229,15 +4108,15 @@
         <v>147</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C156" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D156" s="27">
+        <v>165</v>
+      </c>
+      <c r="D156" s="32">
         <v>550</v>
       </c>
-      <c r="E156" s="58"/>
+      <c r="E156" s="52"/>
       <c r="F156" s="20"/>
     </row>
     <row r="157" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4245,15 +4124,15 @@
         <v>148</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C157" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D157" s="27">
+        <v>165</v>
+      </c>
+      <c r="D157" s="32">
         <v>2200</v>
       </c>
-      <c r="E157" s="58"/>
+      <c r="E157" s="52"/>
       <c r="F157" s="20"/>
     </row>
     <row r="158" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4261,15 +4140,15 @@
         <v>149</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C158" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D158" s="27">
+        <v>165</v>
+      </c>
+      <c r="D158" s="32">
         <v>500</v>
       </c>
-      <c r="E158" s="58"/>
+      <c r="E158" s="52"/>
       <c r="F158" s="20"/>
     </row>
     <row r="159" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4277,33 +4156,31 @@
         <v>150</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C159" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D159" s="27">
-        <v>550</v>
-      </c>
-      <c r="E159" s="58"/>
-      <c r="F159" s="21" t="s">
-        <v>225</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="D159" s="32">
+        <v>100</v>
+      </c>
+      <c r="E159" s="52"/>
+      <c r="F159" s="20"/>
     </row>
     <row r="160" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A160" s="20">
         <v>151</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="C160" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D160" s="27">
-        <v>1100</v>
-      </c>
-      <c r="E160" s="58"/>
+        <v>165</v>
+      </c>
+      <c r="D160" s="32">
+        <v>492</v>
+      </c>
+      <c r="E160" s="52"/>
       <c r="F160" s="20"/>
     </row>
     <row r="161" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4311,17 +4188,17 @@
         <v>152</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C161" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D161" s="27">
-        <v>500</v>
-      </c>
-      <c r="E161" s="58"/>
-      <c r="F161" s="22" t="s">
-        <v>226</v>
+        <v>165</v>
+      </c>
+      <c r="D161" s="32">
+        <v>550</v>
+      </c>
+      <c r="E161" s="52"/>
+      <c r="F161" s="21" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="162" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4329,47 +4206,49 @@
         <v>153</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C162" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D162" s="27">
-        <v>20</v>
-      </c>
-      <c r="E162" s="58"/>
-      <c r="F162" s="25"/>
+        <v>165</v>
+      </c>
+      <c r="D162" s="32">
+        <v>1100</v>
+      </c>
+      <c r="E162" s="52"/>
+      <c r="F162" s="20"/>
     </row>
     <row r="163" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A163" s="20">
         <v>154</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C163" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D163" s="27">
-        <v>1000</v>
-      </c>
-      <c r="E163" s="58"/>
-      <c r="F163" s="25"/>
+        <v>165</v>
+      </c>
+      <c r="D163" s="32">
+        <v>500</v>
+      </c>
+      <c r="E163" s="52"/>
+      <c r="F163" s="22" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="164" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A164" s="20">
         <v>155</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C164" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D164" s="27">
-        <v>2000</v>
-      </c>
-      <c r="E164" s="58"/>
+        <v>165</v>
+      </c>
+      <c r="D164" s="32">
+        <v>20</v>
+      </c>
+      <c r="E164" s="52"/>
       <c r="F164" s="25"/>
     </row>
     <row r="165" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4377,31 +4256,31 @@
         <v>156</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C165" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D165" s="27">
-        <v>2000</v>
-      </c>
-      <c r="E165" s="58"/>
-      <c r="F165" s="21"/>
+        <v>165</v>
+      </c>
+      <c r="D165" s="32">
+        <v>1000</v>
+      </c>
+      <c r="E165" s="52"/>
+      <c r="F165" s="25"/>
     </row>
     <row r="166" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A166" s="20">
         <v>157</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C166" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D166" s="27">
-        <v>500</v>
-      </c>
-      <c r="E166" s="58"/>
+        <v>165</v>
+      </c>
+      <c r="D166" s="32">
+        <v>2000</v>
+      </c>
+      <c r="E166" s="52"/>
       <c r="F166" s="25"/>
     </row>
     <row r="167" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4409,31 +4288,31 @@
         <v>158</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C167" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D167" s="27">
+        <v>165</v>
+      </c>
+      <c r="D167" s="32">
         <v>2000</v>
       </c>
-      <c r="E167" s="58"/>
-      <c r="F167" s="25"/>
+      <c r="E167" s="52"/>
+      <c r="F167" s="21"/>
     </row>
     <row r="168" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A168" s="20">
         <v>159</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C168" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D168" s="27">
-        <v>550</v>
-      </c>
-      <c r="E168" s="58"/>
+        <v>165</v>
+      </c>
+      <c r="D168" s="32">
+        <v>500</v>
+      </c>
+      <c r="E168" s="52"/>
       <c r="F168" s="25"/>
     </row>
     <row r="169" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4441,711 +4320,266 @@
         <v>160</v>
       </c>
       <c r="B169" s="21" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C169" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D169" s="27">
-        <v>750</v>
-      </c>
-      <c r="E169" s="58"/>
+        <v>165</v>
+      </c>
+      <c r="D169" s="32">
+        <v>2000</v>
+      </c>
+      <c r="E169" s="52"/>
       <c r="F169" s="25"/>
     </row>
-    <row r="170" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A170" s="20">
         <v>161</v>
       </c>
-      <c r="B170" s="24" t="s">
-        <v>166</v>
+      <c r="B170" s="21" t="s">
+        <v>189</v>
       </c>
       <c r="C170" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D170" s="25">
-        <v>485</v>
-      </c>
-      <c r="E170" s="58"/>
-      <c r="F170" s="23" t="s">
-        <v>222</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="D170" s="32">
+        <v>550</v>
+      </c>
+      <c r="E170" s="52"/>
+      <c r="F170" s="25"/>
     </row>
     <row r="171" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A171" s="20">
         <v>162</v>
       </c>
-      <c r="B171" s="20" t="s">
-        <v>193</v>
+      <c r="B171" s="21" t="s">
+        <v>190</v>
       </c>
       <c r="C171" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D171" s="28">
-        <v>10</v>
-      </c>
-      <c r="E171" s="58"/>
+        <v>165</v>
+      </c>
+      <c r="D171" s="32">
+        <v>750</v>
+      </c>
+      <c r="E171" s="52"/>
       <c r="F171" s="25"/>
     </row>
-    <row r="172" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
       <c r="A172" s="20">
         <v>163</v>
       </c>
-      <c r="B172" s="20" t="s">
-        <v>194</v>
+      <c r="B172" s="24" t="s">
+        <v>164</v>
       </c>
       <c r="C172" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D172" s="29">
-        <v>500</v>
-      </c>
-      <c r="E172" s="58"/>
-      <c r="F172" s="25"/>
-    </row>
-    <row r="173" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+      <c r="D172" s="33">
+        <v>485</v>
+      </c>
+      <c r="E172" s="52"/>
+      <c r="F172" s="23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" s="2" customFormat="1" ht="36" x14ac:dyDescent="0.2">
       <c r="A173" s="20">
         <v>164</v>
       </c>
-      <c r="B173" s="31" t="s">
-        <v>195</v>
+      <c r="B173" s="20" t="s">
+        <v>197</v>
       </c>
       <c r="C173" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D173" s="29">
-        <v>600</v>
-      </c>
-      <c r="E173" s="58"/>
+        <v>165</v>
+      </c>
+      <c r="D173" s="34">
+        <v>500</v>
+      </c>
+      <c r="E173" s="52"/>
       <c r="F173" s="25"/>
     </row>
     <row r="174" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="20">
-        <v>165</v>
-      </c>
-      <c r="B174" s="32" t="s">
-        <v>196</v>
-      </c>
-      <c r="C174" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D174" s="29">
-        <v>340</v>
-      </c>
-      <c r="E174" s="58"/>
-      <c r="F174" s="25"/>
+      <c r="A174" s="6"/>
+      <c r="B174" s="13"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="10"/>
+      <c r="F174" s="8"/>
     </row>
     <row r="175" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="20">
-        <v>166</v>
-      </c>
-      <c r="B175" s="32" t="s">
-        <v>197</v>
-      </c>
-      <c r="C175" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D175" s="29">
-        <v>100</v>
-      </c>
-      <c r="E175" s="58"/>
-      <c r="F175" s="25"/>
-    </row>
-    <row r="176" spans="1:6" s="2" customFormat="1" ht="36" x14ac:dyDescent="0.2">
-      <c r="A176" s="20">
-        <v>167</v>
-      </c>
-      <c r="B176" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="C176" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D176" s="29">
-        <v>500</v>
-      </c>
-      <c r="E176" s="58"/>
-      <c r="F176" s="25"/>
-    </row>
-    <row r="177" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="20">
-        <v>168</v>
-      </c>
-      <c r="B177" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="C177" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D177" s="30">
-        <v>500</v>
-      </c>
-      <c r="E177" s="58"/>
-      <c r="F177" s="25"/>
+      <c r="A175" s="8"/>
+      <c r="B175" s="13"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="3"/>
+      <c r="F175" s="3"/>
+    </row>
+    <row r="176" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B176" s="50"/>
+      <c r="C176" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" s="50"/>
+      <c r="E176" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F176" s="28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="B177" s="51"/>
+      <c r="C177" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="51"/>
+      <c r="E177" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="F177" s="31" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="178" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="20">
-        <v>169</v>
-      </c>
-      <c r="B178" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="C178" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D178" s="30">
-        <v>5300</v>
-      </c>
-      <c r="E178" s="58"/>
-      <c r="F178" s="25"/>
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
+      <c r="C178" s="29"/>
+      <c r="D178" s="29"/>
+      <c r="E178" s="30"/>
+      <c r="F178" s="29"/>
     </row>
     <row r="179" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="20">
-        <v>170</v>
-      </c>
-      <c r="B179" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="C179" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D179" s="30">
-        <v>1000</v>
-      </c>
-      <c r="E179" s="58"/>
-      <c r="F179" s="25"/>
+      <c r="A179" s="29"/>
+      <c r="B179" s="29"/>
+      <c r="C179" s="29"/>
+      <c r="D179" s="29"/>
+      <c r="E179" s="30"/>
+      <c r="F179" s="29"/>
     </row>
     <row r="180" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="20">
-        <v>171</v>
-      </c>
-      <c r="B180" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C180" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D180" s="30">
-        <v>1000</v>
-      </c>
-      <c r="E180" s="58"/>
-      <c r="F180" s="25"/>
+      <c r="A180" s="29"/>
+      <c r="B180" s="29"/>
+      <c r="C180" s="29"/>
+      <c r="D180" s="27"/>
+      <c r="E180" s="30"/>
+      <c r="F180" s="29"/>
     </row>
     <row r="181" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="20">
-        <v>172</v>
-      </c>
-      <c r="B181" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="C181" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D181" s="30">
-        <v>1000</v>
-      </c>
-      <c r="E181" s="58"/>
-      <c r="F181" s="25"/>
+      <c r="A181" s="29"/>
+      <c r="B181" s="29"/>
+      <c r="C181" s="29"/>
+      <c r="D181" s="29"/>
+      <c r="E181" s="29"/>
+      <c r="F181" s="29"/>
     </row>
     <row r="182" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="20">
-        <v>173</v>
-      </c>
-      <c r="B182" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="C182" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D182" s="30">
-        <v>500</v>
-      </c>
-      <c r="E182" s="58"/>
-      <c r="F182" s="25"/>
-    </row>
-    <row r="183" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="20">
-        <v>174</v>
-      </c>
-      <c r="B183" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="C183" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D183" s="30">
-        <v>500</v>
-      </c>
-      <c r="E183" s="58"/>
-      <c r="F183" s="25"/>
-    </row>
-    <row r="184" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="20">
-        <v>175</v>
-      </c>
-      <c r="B184" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="C184" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D184" s="30">
-        <v>500</v>
-      </c>
-      <c r="E184" s="58"/>
-      <c r="F184" s="25"/>
-    </row>
+      <c r="A182" s="29"/>
+      <c r="B182" s="29"/>
+      <c r="C182" s="29"/>
+      <c r="D182" s="29"/>
+      <c r="E182" s="30"/>
+      <c r="F182" s="29"/>
+    </row>
+    <row r="183" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B183" s="50"/>
+      <c r="C183" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D183" s="50"/>
+      <c r="E183" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="F183" s="28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="185" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="20">
-        <v>176</v>
-      </c>
-      <c r="B185" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="C185" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D185" s="30">
-        <v>500</v>
-      </c>
-      <c r="E185" s="58"/>
-      <c r="F185" s="25"/>
-    </row>
-    <row r="186" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="20">
-        <v>177</v>
-      </c>
-      <c r="B186" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="C186" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D186" s="30">
-        <v>120</v>
-      </c>
-      <c r="E186" s="58"/>
-      <c r="F186" s="25"/>
-    </row>
-    <row r="187" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="20">
-        <v>178</v>
-      </c>
-      <c r="B187" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="C187" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D187" s="30">
-        <v>1400</v>
-      </c>
-      <c r="E187" s="58"/>
-      <c r="F187" s="25"/>
-    </row>
-    <row r="188" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="20">
-        <v>179</v>
-      </c>
-      <c r="B188" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="C188" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D188" s="30">
-        <v>500</v>
-      </c>
-      <c r="E188" s="58"/>
-      <c r="F188" s="25"/>
-    </row>
-    <row r="189" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="20">
-        <v>180</v>
-      </c>
-      <c r="B189" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="C189" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D189" s="30">
-        <v>500</v>
-      </c>
-      <c r="E189" s="58"/>
-      <c r="F189" s="25"/>
-    </row>
-    <row r="190" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="20">
-        <v>181</v>
-      </c>
-      <c r="B190" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="C190" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D190" s="30">
-        <v>500</v>
-      </c>
-      <c r="E190" s="58"/>
-      <c r="F190" s="25"/>
-    </row>
-    <row r="191" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="20">
-        <v>182</v>
-      </c>
-      <c r="B191" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="C191" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D191" s="30">
-        <v>3500</v>
-      </c>
-      <c r="E191" s="58"/>
-      <c r="F191" s="25"/>
-    </row>
-    <row r="192" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="20">
-        <v>183</v>
-      </c>
-      <c r="B192" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="C192" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D192" s="30">
-        <v>500</v>
-      </c>
-      <c r="E192" s="58"/>
-      <c r="F192" s="25"/>
-    </row>
-    <row r="193" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="20">
-        <v>184</v>
-      </c>
-      <c r="B193" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="C193" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D193" s="30">
-        <v>500</v>
-      </c>
-      <c r="E193" s="58"/>
-      <c r="F193" s="25"/>
-    </row>
-    <row r="194" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="20">
-        <v>185</v>
-      </c>
-      <c r="B194" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="C194" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D194" s="30">
-        <v>500</v>
-      </c>
-      <c r="E194" s="58"/>
-      <c r="F194" s="25"/>
-    </row>
-    <row r="195" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="20">
-        <v>186</v>
-      </c>
-      <c r="B195" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="C195" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D195" s="30">
-        <v>500</v>
-      </c>
-      <c r="E195" s="58"/>
-      <c r="F195" s="25"/>
-    </row>
-    <row r="196" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="20">
-        <v>187</v>
-      </c>
-      <c r="B196" s="33" t="s">
-        <v>217</v>
-      </c>
-      <c r="C196" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D196" s="30">
-        <v>500</v>
-      </c>
-      <c r="E196" s="58"/>
-      <c r="F196" s="25"/>
-    </row>
-    <row r="197" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="20">
-        <v>188</v>
-      </c>
-      <c r="B197" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="C197" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D197" s="30">
-        <v>500</v>
-      </c>
-      <c r="E197" s="58"/>
-      <c r="F197" s="25"/>
-    </row>
-    <row r="198" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="20">
-        <v>189</v>
-      </c>
-      <c r="B198" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="C198" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D198" s="30">
-        <v>500</v>
-      </c>
-      <c r="E198" s="58"/>
-      <c r="F198" s="25"/>
-    </row>
-    <row r="199" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="20">
-        <v>190</v>
-      </c>
-      <c r="B199" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="C199" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D199" s="34">
-        <v>1000</v>
-      </c>
-      <c r="E199" s="58"/>
-      <c r="F199" s="25"/>
-    </row>
-    <row r="200" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="20">
-        <v>191</v>
-      </c>
-      <c r="B200" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C200" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D200" s="25">
-        <v>5500</v>
-      </c>
-      <c r="E200" s="58"/>
-      <c r="F200" s="25"/>
-    </row>
-    <row r="201" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="20">
-        <v>192</v>
-      </c>
-      <c r="B201" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C201" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D201" s="25">
-        <v>500</v>
-      </c>
-      <c r="E201" s="59"/>
-      <c r="F201" s="25"/>
-    </row>
-    <row r="202" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="6"/>
-      <c r="B202" s="13"/>
-      <c r="C202" s="3"/>
-      <c r="D202" s="7"/>
-      <c r="E202" s="10"/>
-      <c r="F202" s="8"/>
-    </row>
-    <row r="203" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="8"/>
-      <c r="B203" s="13"/>
-      <c r="C203" s="3"/>
-      <c r="D203" s="3"/>
-      <c r="E203" s="3"/>
-      <c r="F203" s="3"/>
-    </row>
-    <row r="204" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="B204" s="55"/>
-      <c r="C204" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D204" s="55"/>
-      <c r="E204" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F204" s="36" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B205" s="56"/>
-      <c r="C205" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="56"/>
-      <c r="E205" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="F205" s="39" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="37"/>
-      <c r="B206" s="37"/>
-      <c r="C206" s="37"/>
-      <c r="D206" s="37"/>
-      <c r="E206" s="38"/>
-      <c r="F206" s="37"/>
-    </row>
-    <row r="207" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="37"/>
-      <c r="B207" s="37"/>
-      <c r="C207" s="37"/>
-      <c r="D207" s="37"/>
-      <c r="E207" s="38"/>
-      <c r="F207" s="37"/>
-    </row>
-    <row r="208" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="37"/>
-      <c r="B208" s="37"/>
-      <c r="C208" s="37"/>
-      <c r="D208" s="35"/>
-      <c r="E208" s="38"/>
-      <c r="F208" s="37"/>
-    </row>
-    <row r="209" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="37"/>
-      <c r="B209" s="37"/>
-      <c r="C209" s="37"/>
-      <c r="D209" s="37"/>
-      <c r="E209" s="37"/>
-      <c r="F209" s="37"/>
-    </row>
-    <row r="210" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="37"/>
-      <c r="B210" s="37"/>
-      <c r="C210" s="37"/>
-      <c r="D210" s="37"/>
-      <c r="E210" s="38"/>
-      <c r="F210" s="37"/>
-    </row>
-    <row r="211" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="B211" s="55"/>
-      <c r="C211" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="D211" s="55"/>
-      <c r="E211" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F211" s="36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="213" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E213" s="12"/>
-      <c r="F213" s="12"/>
-    </row>
-    <row r="214" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="215" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="216" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="217" spans="1:6" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="C217" s="11"/>
-      <c r="D217" s="11"/>
-      <c r="E217" s="11"/>
-      <c r="F217" s="11"/>
-    </row>
-    <row r="218" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="219" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="224" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="F224" s="5"/>
+      <c r="E185" s="12"/>
+      <c r="F185" s="12"/>
+    </row>
+    <row r="186" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="187" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="188" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="189" spans="1:6" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="C189" s="11"/>
+      <c r="D189" s="11"/>
+      <c r="E189" s="11"/>
+      <c r="F189" s="11"/>
+    </row>
+    <row r="190" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="191" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="196" spans="6:6" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="F196" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:F170" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A9:F172" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="13">
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A204:B204"/>
-    <mergeCell ref="A205:B205"/>
-    <mergeCell ref="A211:B211"/>
-    <mergeCell ref="C204:D204"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="C211:D211"/>
-    <mergeCell ref="E10:E201"/>
+    <mergeCell ref="A176:B176"/>
+    <mergeCell ref="A177:B177"/>
+    <mergeCell ref="A183:B183"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="E10:E173"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="A1:B4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B10:B169">
-    <cfRule type="duplicateValues" dxfId="12" priority="35"/>
+  <conditionalFormatting sqref="B1:B158 M1:M9 M110:M1048576 B161:B1048576">
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B171:B201">
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+  <conditionalFormatting sqref="B10:B158 B161:B171">
+    <cfRule type="duplicateValues" dxfId="12" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D200:D201">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+  <conditionalFormatting sqref="B173">
+    <cfRule type="duplicateValues" dxfId="11" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F45">
-    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140">
-    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F148">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F154">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F159">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F161">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F165">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  <conditionalFormatting sqref="F163">
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <conditionalFormatting sqref="F167">
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B159:B160">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="99" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03_240626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03_240626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E83E94B-0970-4E97-83FC-B8818EB8205A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62F9F2C-31F5-49AB-A74F-6F57D9E38945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,15 +16,15 @@
     <sheet name="XuatKho_SX" sheetId="10" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">XuatKho_SX!$A$9:$F$172</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_SX!$A$1:$J$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">XuatKho_SX!$A$9:$F$170</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_SX!$A$1:$J$181</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="200">
   <si>
     <t>STT</t>
   </si>
@@ -129,9 +129,6 @@
     <t>CC0402KRX7R9BB822</t>
   </si>
   <si>
-    <t>EMK316BBJ476ML-T</t>
-  </si>
-  <si>
     <t>CC0603KRX7R9BB474</t>
   </si>
   <si>
@@ -298,9 +295,6 @@
   </si>
   <si>
     <t>ZNR3015ST2R2M</t>
-  </si>
-  <si>
-    <t>DLM0NSN900HY2D</t>
   </si>
   <si>
     <t>VHF100505HQ68NJT</t>
@@ -1025,6 +1019,24 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1060,24 +1072,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1246,13 +1240,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>488016</xdr:colOff>
-      <xdr:row>173</xdr:row>
+      <xdr:row>171</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>307037</xdr:colOff>
-      <xdr:row>173</xdr:row>
+      <xdr:row>171</xdr:row>
       <xdr:rowOff>3941</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1631,7 +1625,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L194"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
@@ -1646,56 +1640,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="37" t="s">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="38"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="44"/>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="37" t="s">
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="38"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="44"/>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="39" t="s">
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="40"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46"/>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="49"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="37"/>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
@@ -1706,7 +1700,7 @@
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="26" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1740,7 +1734,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>15</v>
@@ -1757,13 +1751,13 @@
         <v>23</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D10" s="32">
         <v>500</v>
       </c>
-      <c r="E10" s="52" t="s">
-        <v>168</v>
+      <c r="E10" s="40" t="s">
+        <v>166</v>
       </c>
       <c r="F10" s="20"/>
     </row>
@@ -1772,15 +1766,15 @@
         <v>2</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D11" s="32">
         <v>500</v>
       </c>
-      <c r="E11" s="52"/>
+      <c r="E11" s="40"/>
       <c r="F11" s="20"/>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1791,12 +1785,12 @@
         <v>24</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D12" s="32">
         <v>499</v>
       </c>
-      <c r="E12" s="52"/>
+      <c r="E12" s="40"/>
       <c r="F12" s="20"/>
     </row>
     <row r="13" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1804,15 +1798,15 @@
         <v>4</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D13" s="32">
         <v>510</v>
       </c>
-      <c r="E13" s="52"/>
+      <c r="E13" s="40"/>
       <c r="F13" s="20"/>
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1820,15 +1814,15 @@
         <v>5</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D14" s="32">
         <v>6500</v>
       </c>
-      <c r="E14" s="52"/>
+      <c r="E14" s="40"/>
       <c r="F14" s="21" t="s">
         <v>25</v>
       </c>
@@ -1841,12 +1835,12 @@
         <v>26</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D15" s="32">
         <v>1000</v>
       </c>
-      <c r="E15" s="52"/>
+      <c r="E15" s="40"/>
       <c r="F15" s="20"/>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1857,12 +1851,12 @@
         <v>27</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D16" s="32">
         <v>1000</v>
       </c>
-      <c r="E16" s="52"/>
+      <c r="E16" s="40"/>
       <c r="F16" s="20"/>
     </row>
     <row r="17" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1873,12 +1867,12 @@
         <v>28</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D17" s="32">
         <v>2500</v>
       </c>
-      <c r="E17" s="52"/>
+      <c r="E17" s="40"/>
       <c r="F17" s="20"/>
     </row>
     <row r="18" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1886,15 +1880,15 @@
         <v>9</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D18" s="32">
         <v>2000</v>
       </c>
-      <c r="E18" s="52"/>
+      <c r="E18" s="40"/>
       <c r="F18" s="20"/>
     </row>
     <row r="19" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1905,12 +1899,12 @@
         <v>29</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D19" s="32">
         <v>1000</v>
       </c>
-      <c r="E19" s="52"/>
+      <c r="E19" s="40"/>
       <c r="F19" s="20"/>
     </row>
     <row r="20" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1921,12 +1915,12 @@
         <v>30</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D20" s="32">
         <v>500</v>
       </c>
-      <c r="E20" s="52"/>
+      <c r="E20" s="40"/>
       <c r="F20" s="20"/>
     </row>
     <row r="21" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1937,12 +1931,12 @@
         <v>31</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D21" s="32">
         <v>45400</v>
       </c>
-      <c r="E21" s="52"/>
+      <c r="E21" s="40"/>
       <c r="F21" s="20"/>
     </row>
     <row r="22" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1953,12 +1947,12 @@
         <v>32</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D22" s="32">
         <v>1000</v>
       </c>
-      <c r="E22" s="52"/>
+      <c r="E22" s="40"/>
       <c r="F22" s="20"/>
     </row>
     <row r="23" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1969,12 +1963,12 @@
         <v>33</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D23" s="32">
         <v>500</v>
       </c>
-      <c r="E23" s="52"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="20"/>
     </row>
     <row r="24" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1982,15 +1976,15 @@
         <v>15</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D24" s="32">
         <v>520</v>
       </c>
-      <c r="E24" s="52"/>
+      <c r="E24" s="40"/>
       <c r="F24" s="20"/>
     </row>
     <row r="25" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2001,12 +1995,12 @@
         <v>34</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D25" s="32">
-        <v>500</v>
-      </c>
-      <c r="E25" s="52"/>
+        <v>1500</v>
+      </c>
+      <c r="E25" s="40"/>
       <c r="F25" s="20"/>
     </row>
     <row r="26" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2017,12 +2011,12 @@
         <v>35</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D26" s="32">
         <v>1500</v>
       </c>
-      <c r="E26" s="52"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="20"/>
     </row>
     <row r="27" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2033,12 +2027,12 @@
         <v>36</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D27" s="32">
         <v>1500</v>
       </c>
-      <c r="E27" s="52"/>
+      <c r="E27" s="40"/>
       <c r="F27" s="20"/>
     </row>
     <row r="28" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2049,12 +2043,12 @@
         <v>37</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D28" s="32">
         <v>1500</v>
       </c>
-      <c r="E28" s="52"/>
+      <c r="E28" s="40"/>
       <c r="F28" s="20"/>
     </row>
     <row r="29" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2065,12 +2059,12 @@
         <v>38</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D29" s="32">
-        <v>1500</v>
-      </c>
-      <c r="E29" s="52"/>
+        <v>6500</v>
+      </c>
+      <c r="E29" s="40"/>
       <c r="F29" s="20"/>
     </row>
     <row r="30" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2078,15 +2072,15 @@
         <v>21</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>39</v>
+        <v>150</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D30" s="32">
-        <v>6500</v>
-      </c>
-      <c r="E30" s="52"/>
+        <v>1447</v>
+      </c>
+      <c r="E30" s="40"/>
       <c r="F30" s="20"/>
     </row>
     <row r="31" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2094,16 +2088,18 @@
         <v>22</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D31" s="32">
-        <v>1447</v>
-      </c>
-      <c r="E31" s="52"/>
-      <c r="F31" s="20"/>
+        <v>14000</v>
+      </c>
+      <c r="E31" s="40"/>
+      <c r="F31" s="21" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="32" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="20">
@@ -2113,15 +2109,13 @@
         <v>40</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D32" s="32">
-        <v>14000</v>
-      </c>
-      <c r="E32" s="52"/>
-      <c r="F32" s="21" t="s">
-        <v>163</v>
-      </c>
+        <v>1500</v>
+      </c>
+      <c r="E32" s="40"/>
+      <c r="F32" s="20"/>
     </row>
     <row r="33" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="20">
@@ -2131,12 +2125,12 @@
         <v>41</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D33" s="32">
-        <v>1500</v>
-      </c>
-      <c r="E33" s="52"/>
+        <v>5000</v>
+      </c>
+      <c r="E33" s="40"/>
       <c r="F33" s="20"/>
     </row>
     <row r="34" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2147,12 +2141,12 @@
         <v>42</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D34" s="32">
-        <v>5000</v>
-      </c>
-      <c r="E34" s="52"/>
+        <v>1500</v>
+      </c>
+      <c r="E34" s="40"/>
       <c r="F34" s="20"/>
     </row>
     <row r="35" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2160,15 +2154,15 @@
         <v>26</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D35" s="32">
-        <v>1500</v>
-      </c>
-      <c r="E35" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E35" s="40"/>
       <c r="F35" s="20"/>
     </row>
     <row r="36" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2176,15 +2170,15 @@
         <v>27</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>172</v>
+        <v>43</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D36" s="32">
-        <v>500</v>
-      </c>
-      <c r="E36" s="52"/>
+        <v>2000</v>
+      </c>
+      <c r="E36" s="40"/>
       <c r="F36" s="20"/>
     </row>
     <row r="37" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2192,31 +2186,31 @@
         <v>28</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>44</v>
+        <v>151</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D37" s="32">
-        <v>2000</v>
-      </c>
-      <c r="E37" s="52"/>
+        <v>1520</v>
+      </c>
+      <c r="E37" s="40"/>
       <c r="F37" s="20"/>
     </row>
-    <row r="38" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="20">
         <v>29</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>153</v>
+        <v>44</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D38" s="32">
-        <v>1520</v>
-      </c>
-      <c r="E38" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E38" s="40"/>
       <c r="F38" s="20"/>
     </row>
     <row r="39" spans="1:6" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2227,44 +2221,44 @@
         <v>45</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D39" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E39" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E39" s="40"/>
       <c r="F39" s="20"/>
     </row>
-    <row r="40" spans="1:6" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
       <c r="A40" s="20">
         <v>31</v>
       </c>
-      <c r="B40" s="21" t="s">
-        <v>46</v>
+      <c r="B40" s="22" t="s">
+        <v>196</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D40" s="32">
-        <v>500</v>
-      </c>
-      <c r="E40" s="52"/>
+        <v>520</v>
+      </c>
+      <c r="E40" s="40"/>
       <c r="F40" s="20"/>
     </row>
-    <row r="41" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="20">
         <v>32</v>
       </c>
-      <c r="B41" s="22" t="s">
-        <v>198</v>
+      <c r="B41" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D41" s="32">
-        <v>520</v>
-      </c>
-      <c r="E41" s="52"/>
+        <v>1500</v>
+      </c>
+      <c r="E41" s="40"/>
       <c r="F41" s="20"/>
     </row>
     <row r="42" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2275,12 +2269,12 @@
         <v>47</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D42" s="32">
-        <v>1500</v>
-      </c>
-      <c r="E42" s="52"/>
+        <v>1600</v>
+      </c>
+      <c r="E42" s="40"/>
       <c r="F42" s="20"/>
     </row>
     <row r="43" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2291,12 +2285,12 @@
         <v>48</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D43" s="32">
-        <v>1600</v>
-      </c>
-      <c r="E43" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E43" s="40"/>
       <c r="F43" s="20"/>
     </row>
     <row r="44" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2304,16 +2298,16 @@
         <v>35</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D44" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E44" s="52"/>
-      <c r="F44" s="20"/>
+        <v>500</v>
+      </c>
+      <c r="E44" s="40"/>
+      <c r="F44" s="21"/>
     </row>
     <row r="45" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="20">
@@ -2323,28 +2317,28 @@
         <v>51</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D45" s="32">
         <v>500</v>
       </c>
-      <c r="E45" s="52"/>
-      <c r="F45" s="21"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="20"/>
     </row>
     <row r="46" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="20">
         <v>37</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D46" s="32">
         <v>500</v>
       </c>
-      <c r="E46" s="52"/>
+      <c r="E46" s="40"/>
       <c r="F46" s="20"/>
     </row>
     <row r="47" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2352,15 +2346,15 @@
         <v>38</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D47" s="32">
-        <v>500</v>
-      </c>
-      <c r="E47" s="52"/>
+        <v>2050</v>
+      </c>
+      <c r="E47" s="40"/>
       <c r="F47" s="20"/>
     </row>
     <row r="48" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2371,12 +2365,12 @@
         <v>53</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D48" s="32">
-        <v>2050</v>
-      </c>
-      <c r="E48" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E48" s="40"/>
       <c r="F48" s="20"/>
     </row>
     <row r="49" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2387,12 +2381,12 @@
         <v>54</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D49" s="32">
         <v>500</v>
       </c>
-      <c r="E49" s="52"/>
+      <c r="E49" s="40"/>
       <c r="F49" s="20"/>
     </row>
     <row r="50" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2400,34 +2394,34 @@
         <v>41</v>
       </c>
       <c r="B50" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50" s="32">
+        <v>1600</v>
+      </c>
+      <c r="E50" s="40"/>
+      <c r="F50" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="D50" s="32">
-        <v>500</v>
-      </c>
-      <c r="E50" s="52"/>
-      <c r="F50" s="20"/>
     </row>
     <row r="51" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="20">
         <v>42</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D51" s="32">
-        <v>1600</v>
-      </c>
-      <c r="E51" s="52"/>
-      <c r="F51" s="21" t="s">
-        <v>56</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="E51" s="40"/>
+      <c r="F51" s="20"/>
     </row>
     <row r="52" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="20">
@@ -2437,12 +2431,12 @@
         <v>57</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D52" s="32">
-        <v>600</v>
-      </c>
-      <c r="E52" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E52" s="40"/>
       <c r="F52" s="20"/>
     </row>
     <row r="53" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2453,12 +2447,12 @@
         <v>58</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D53" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E53" s="52"/>
+        <v>5500</v>
+      </c>
+      <c r="E53" s="40"/>
       <c r="F53" s="20"/>
     </row>
     <row r="54" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2469,12 +2463,12 @@
         <v>59</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D54" s="32">
-        <v>5500</v>
-      </c>
-      <c r="E54" s="52"/>
+        <v>3550</v>
+      </c>
+      <c r="E54" s="40"/>
       <c r="F54" s="20"/>
     </row>
     <row r="55" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2485,12 +2479,12 @@
         <v>60</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D55" s="32">
-        <v>3550</v>
-      </c>
-      <c r="E55" s="52"/>
+        <v>550</v>
+      </c>
+      <c r="E55" s="40"/>
       <c r="F55" s="20"/>
     </row>
     <row r="56" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2501,12 +2495,12 @@
         <v>61</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D56" s="32">
-        <v>550</v>
-      </c>
-      <c r="E56" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E56" s="40"/>
       <c r="F56" s="20"/>
     </row>
     <row r="57" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2517,12 +2511,12 @@
         <v>62</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D57" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E57" s="52"/>
+        <v>2000</v>
+      </c>
+      <c r="E57" s="40"/>
       <c r="F57" s="20"/>
     </row>
     <row r="58" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2530,34 +2524,34 @@
         <v>49</v>
       </c>
       <c r="B58" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58" s="32">
+        <v>10770</v>
+      </c>
+      <c r="E58" s="40"/>
+      <c r="F58" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C58" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="D58" s="32">
-        <v>2000</v>
-      </c>
-      <c r="E58" s="52"/>
-      <c r="F58" s="20"/>
     </row>
     <row r="59" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="20">
         <v>50</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>173</v>
+        <v>64</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D59" s="32">
-        <v>10770</v>
-      </c>
-      <c r="E59" s="52"/>
-      <c r="F59" s="21" t="s">
-        <v>64</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="E59" s="40"/>
+      <c r="F59" s="20"/>
     </row>
     <row r="60" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="20">
@@ -2567,12 +2561,12 @@
         <v>65</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D60" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E60" s="52"/>
+        <v>2500</v>
+      </c>
+      <c r="E60" s="40"/>
       <c r="F60" s="20"/>
     </row>
     <row r="61" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2583,12 +2577,12 @@
         <v>66</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D61" s="32">
-        <v>2500</v>
-      </c>
-      <c r="E61" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E61" s="40"/>
       <c r="F61" s="20"/>
     </row>
     <row r="62" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2599,13 +2593,15 @@
         <v>67</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D62" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E62" s="52"/>
-      <c r="F62" s="20"/>
+        <v>500</v>
+      </c>
+      <c r="E62" s="40"/>
+      <c r="F62" s="21" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="63" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="20">
@@ -2615,15 +2611,13 @@
         <v>68</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D63" s="32">
-        <v>500</v>
-      </c>
-      <c r="E63" s="52"/>
-      <c r="F63" s="21" t="s">
-        <v>194</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="E63" s="40"/>
+      <c r="F63" s="20"/>
     </row>
     <row r="64" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="20">
@@ -2633,12 +2627,12 @@
         <v>69</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D64" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E64" s="52"/>
+        <v>1500</v>
+      </c>
+      <c r="E64" s="40"/>
       <c r="F64" s="20"/>
     </row>
     <row r="65" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2649,12 +2643,12 @@
         <v>70</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D65" s="32">
-        <v>1500</v>
-      </c>
-      <c r="E65" s="52"/>
+        <v>5500</v>
+      </c>
+      <c r="E65" s="40"/>
       <c r="F65" s="20"/>
     </row>
     <row r="66" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2665,12 +2659,12 @@
         <v>71</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D66" s="32">
-        <v>5500</v>
-      </c>
-      <c r="E66" s="52"/>
+        <v>3000</v>
+      </c>
+      <c r="E66" s="40"/>
       <c r="F66" s="20"/>
     </row>
     <row r="67" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2681,12 +2675,12 @@
         <v>72</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D67" s="32">
-        <v>3000</v>
-      </c>
-      <c r="E67" s="52"/>
+        <v>7400</v>
+      </c>
+      <c r="E67" s="40"/>
       <c r="F67" s="20"/>
     </row>
     <row r="68" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2697,12 +2691,12 @@
         <v>73</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D68" s="32">
-        <v>7400</v>
-      </c>
-      <c r="E68" s="52"/>
+        <v>1500</v>
+      </c>
+      <c r="E68" s="40"/>
       <c r="F68" s="20"/>
     </row>
     <row r="69" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2713,12 +2707,12 @@
         <v>74</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D69" s="32">
-        <v>1500</v>
-      </c>
-      <c r="E69" s="52"/>
+        <v>550</v>
+      </c>
+      <c r="E69" s="40"/>
       <c r="F69" s="20"/>
     </row>
     <row r="70" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2729,12 +2723,12 @@
         <v>75</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D70" s="32">
-        <v>550</v>
-      </c>
-      <c r="E70" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E70" s="40"/>
       <c r="F70" s="20"/>
     </row>
     <row r="71" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2745,12 +2739,12 @@
         <v>76</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D71" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E71" s="52"/>
+        <v>550</v>
+      </c>
+      <c r="E71" s="40"/>
       <c r="F71" s="20"/>
     </row>
     <row r="72" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2761,12 +2755,12 @@
         <v>77</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D72" s="32">
-        <v>550</v>
-      </c>
-      <c r="E72" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E72" s="40"/>
       <c r="F72" s="20"/>
     </row>
     <row r="73" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2777,12 +2771,12 @@
         <v>78</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D73" s="32">
-        <v>500</v>
-      </c>
-      <c r="E73" s="52"/>
+        <v>2500</v>
+      </c>
+      <c r="E73" s="40"/>
       <c r="F73" s="20"/>
     </row>
     <row r="74" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2793,12 +2787,12 @@
         <v>79</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D74" s="32">
-        <v>2500</v>
-      </c>
-      <c r="E74" s="52"/>
+        <v>1500</v>
+      </c>
+      <c r="E74" s="40"/>
       <c r="F74" s="20"/>
     </row>
     <row r="75" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2809,12 +2803,12 @@
         <v>80</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D75" s="32">
-        <v>1500</v>
-      </c>
-      <c r="E75" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E75" s="40"/>
       <c r="F75" s="20"/>
     </row>
     <row r="76" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2825,12 +2819,12 @@
         <v>81</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D76" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E76" s="52"/>
+        <v>550</v>
+      </c>
+      <c r="E76" s="40"/>
       <c r="F76" s="20"/>
     </row>
     <row r="77" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2841,12 +2835,12 @@
         <v>82</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D77" s="32">
-        <v>550</v>
-      </c>
-      <c r="E77" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E77" s="40"/>
       <c r="F77" s="20"/>
     </row>
     <row r="78" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2857,12 +2851,12 @@
         <v>83</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D78" s="32">
         <v>1000</v>
       </c>
-      <c r="E78" s="52"/>
+      <c r="E78" s="40"/>
       <c r="F78" s="20"/>
     </row>
     <row r="79" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2873,12 +2867,12 @@
         <v>84</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D79" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E79" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E79" s="40"/>
       <c r="F79" s="20"/>
     </row>
     <row r="80" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2889,12 +2883,12 @@
         <v>85</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D80" s="32">
-        <v>500</v>
-      </c>
-      <c r="E80" s="52"/>
+        <v>600</v>
+      </c>
+      <c r="E80" s="40"/>
       <c r="F80" s="20"/>
     </row>
     <row r="81" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2905,12 +2899,12 @@
         <v>86</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D81" s="32">
-        <v>600</v>
-      </c>
-      <c r="E81" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E81" s="40"/>
       <c r="F81" s="20"/>
     </row>
     <row r="82" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2921,12 +2915,12 @@
         <v>87</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D82" s="32">
         <v>500</v>
       </c>
-      <c r="E82" s="52"/>
+      <c r="E82" s="40"/>
       <c r="F82" s="20"/>
     </row>
     <row r="83" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2937,12 +2931,12 @@
         <v>88</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D83" s="32">
         <v>500</v>
       </c>
-      <c r="E83" s="52"/>
+      <c r="E83" s="40"/>
       <c r="F83" s="20"/>
     </row>
     <row r="84" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2953,12 +2947,12 @@
         <v>89</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D84" s="32">
-        <v>500</v>
-      </c>
-      <c r="E84" s="52"/>
+        <v>1500</v>
+      </c>
+      <c r="E84" s="40"/>
       <c r="F84" s="20"/>
     </row>
     <row r="85" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2966,15 +2960,15 @@
         <v>76</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D85" s="32">
-        <v>1500</v>
-      </c>
-      <c r="E85" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E85" s="40"/>
       <c r="F85" s="20"/>
     </row>
     <row r="86" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2982,15 +2976,15 @@
         <v>77</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D86" s="32">
-        <v>500</v>
-      </c>
-      <c r="E86" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E86" s="40"/>
       <c r="F86" s="20"/>
     </row>
     <row r="87" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2998,15 +2992,15 @@
         <v>78</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D87" s="32">
-        <v>500</v>
-      </c>
-      <c r="E87" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E87" s="40"/>
       <c r="F87" s="20"/>
     </row>
     <row r="88" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3014,15 +3008,15 @@
         <v>79</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>154</v>
+        <v>91</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D88" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E88" s="52"/>
+        <v>4000</v>
+      </c>
+      <c r="E88" s="40"/>
       <c r="F88" s="20"/>
     </row>
     <row r="89" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3033,12 +3027,12 @@
         <v>92</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D89" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E89" s="52"/>
+        <v>2500</v>
+      </c>
+      <c r="E89" s="40"/>
       <c r="F89" s="20"/>
     </row>
     <row r="90" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3049,12 +3043,12 @@
         <v>93</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D90" s="32">
-        <v>4000</v>
-      </c>
-      <c r="E90" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E90" s="40"/>
       <c r="F90" s="20"/>
     </row>
     <row r="91" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3062,15 +3056,15 @@
         <v>82</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D91" s="32">
-        <v>2500</v>
-      </c>
-      <c r="E91" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E91" s="40"/>
       <c r="F91" s="20"/>
     </row>
     <row r="92" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3078,15 +3072,15 @@
         <v>83</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D92" s="32">
-        <v>500</v>
-      </c>
-      <c r="E92" s="52"/>
+        <v>8830</v>
+      </c>
+      <c r="E92" s="40"/>
       <c r="F92" s="20"/>
     </row>
     <row r="93" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3094,15 +3088,15 @@
         <v>84</v>
       </c>
       <c r="B93" s="21" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D93" s="32">
         <v>500</v>
       </c>
-      <c r="E93" s="52"/>
+      <c r="E93" s="40"/>
       <c r="F93" s="20"/>
     </row>
     <row r="94" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3113,12 +3107,12 @@
         <v>96</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D94" s="32">
-        <v>8830</v>
-      </c>
-      <c r="E94" s="52"/>
+        <v>5476</v>
+      </c>
+      <c r="E94" s="40"/>
       <c r="F94" s="20"/>
     </row>
     <row r="95" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3129,12 +3123,12 @@
         <v>97</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D95" s="32">
-        <v>500</v>
-      </c>
-      <c r="E95" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E95" s="40"/>
       <c r="F95" s="20"/>
     </row>
     <row r="96" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3145,12 +3139,12 @@
         <v>98</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D96" s="32">
-        <v>5476</v>
-      </c>
-      <c r="E96" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E96" s="40"/>
       <c r="F96" s="20"/>
     </row>
     <row r="97" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3161,12 +3155,12 @@
         <v>99</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D97" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E97" s="52"/>
+        <v>6500</v>
+      </c>
+      <c r="E97" s="40"/>
       <c r="F97" s="20"/>
     </row>
     <row r="98" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3177,12 +3171,12 @@
         <v>100</v>
       </c>
       <c r="C98" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D98" s="32">
-        <v>500</v>
-      </c>
-      <c r="E98" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E98" s="40"/>
       <c r="F98" s="20"/>
     </row>
     <row r="99" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3193,12 +3187,12 @@
         <v>101</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D99" s="32">
-        <v>6500</v>
-      </c>
-      <c r="E99" s="52"/>
+        <v>1100</v>
+      </c>
+      <c r="E99" s="40"/>
       <c r="F99" s="20"/>
     </row>
     <row r="100" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3209,12 +3203,12 @@
         <v>102</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D100" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E100" s="52"/>
+        <v>21980</v>
+      </c>
+      <c r="E100" s="40"/>
       <c r="F100" s="20"/>
     </row>
     <row r="101" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3225,12 +3219,12 @@
         <v>103</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D101" s="32">
-        <v>1100</v>
-      </c>
-      <c r="E101" s="52"/>
+        <v>24500</v>
+      </c>
+      <c r="E101" s="40"/>
       <c r="F101" s="20"/>
     </row>
     <row r="102" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3241,12 +3235,12 @@
         <v>104</v>
       </c>
       <c r="C102" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D102" s="32">
-        <v>21980</v>
-      </c>
-      <c r="E102" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E102" s="40"/>
       <c r="F102" s="20"/>
     </row>
     <row r="103" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3257,12 +3251,12 @@
         <v>105</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D103" s="32">
-        <v>24500</v>
-      </c>
-      <c r="E103" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E103" s="40"/>
       <c r="F103" s="20"/>
     </row>
     <row r="104" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3273,12 +3267,12 @@
         <v>106</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D104" s="32">
         <v>1000</v>
       </c>
-      <c r="E104" s="52"/>
+      <c r="E104" s="40"/>
       <c r="F104" s="20"/>
     </row>
     <row r="105" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3289,12 +3283,12 @@
         <v>107</v>
       </c>
       <c r="C105" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D105" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E105" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E105" s="40"/>
       <c r="F105" s="20"/>
     </row>
     <row r="106" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3305,12 +3299,12 @@
         <v>108</v>
       </c>
       <c r="C106" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D106" s="32">
         <v>1000</v>
       </c>
-      <c r="E106" s="52"/>
+      <c r="E106" s="40"/>
       <c r="F106" s="20"/>
     </row>
     <row r="107" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3321,12 +3315,12 @@
         <v>109</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D107" s="32">
-        <v>500</v>
-      </c>
-      <c r="E107" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E107" s="40"/>
       <c r="F107" s="20"/>
     </row>
     <row r="108" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3337,12 +3331,12 @@
         <v>110</v>
       </c>
       <c r="C108" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D108" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E108" s="52"/>
+        <v>3500</v>
+      </c>
+      <c r="E108" s="40"/>
       <c r="F108" s="20"/>
     </row>
     <row r="109" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3353,12 +3347,12 @@
         <v>111</v>
       </c>
       <c r="C109" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D109" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E109" s="52"/>
+        <v>14900</v>
+      </c>
+      <c r="E109" s="40"/>
       <c r="F109" s="20"/>
     </row>
     <row r="110" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3369,12 +3363,12 @@
         <v>112</v>
       </c>
       <c r="C110" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D110" s="32">
-        <v>3500</v>
-      </c>
-      <c r="E110" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E110" s="40"/>
       <c r="F110" s="20"/>
     </row>
     <row r="111" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3385,12 +3379,12 @@
         <v>113</v>
       </c>
       <c r="C111" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D111" s="32">
-        <v>14900</v>
-      </c>
-      <c r="E111" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E111" s="40"/>
       <c r="F111" s="20"/>
     </row>
     <row r="112" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3401,12 +3395,12 @@
         <v>114</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D112" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E112" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E112" s="40"/>
       <c r="F112" s="20"/>
     </row>
     <row r="113" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3417,12 +3411,12 @@
         <v>115</v>
       </c>
       <c r="C113" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D113" s="32">
         <v>500</v>
       </c>
-      <c r="E113" s="52"/>
+      <c r="E113" s="40"/>
       <c r="F113" s="20"/>
     </row>
     <row r="114" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3433,12 +3427,12 @@
         <v>116</v>
       </c>
       <c r="C114" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D114" s="32">
-        <v>500</v>
-      </c>
-      <c r="E114" s="52"/>
+        <v>10000</v>
+      </c>
+      <c r="E114" s="40"/>
       <c r="F114" s="20"/>
     </row>
     <row r="115" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3449,12 +3443,12 @@
         <v>117</v>
       </c>
       <c r="C115" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D115" s="32">
-        <v>500</v>
-      </c>
-      <c r="E115" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E115" s="40"/>
       <c r="F115" s="20"/>
     </row>
     <row r="116" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3465,12 +3459,12 @@
         <v>118</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D116" s="32">
-        <v>10000</v>
-      </c>
-      <c r="E116" s="52"/>
+        <v>26500</v>
+      </c>
+      <c r="E116" s="40"/>
       <c r="F116" s="20"/>
     </row>
     <row r="117" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3481,12 +3475,12 @@
         <v>119</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D117" s="32">
         <v>1000</v>
       </c>
-      <c r="E117" s="52"/>
+      <c r="E117" s="40"/>
       <c r="F117" s="20"/>
     </row>
     <row r="118" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3497,12 +3491,12 @@
         <v>120</v>
       </c>
       <c r="C118" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D118" s="32">
-        <v>26500</v>
-      </c>
-      <c r="E118" s="52"/>
+        <v>1600</v>
+      </c>
+      <c r="E118" s="40"/>
       <c r="F118" s="20"/>
     </row>
     <row r="119" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3513,12 +3507,12 @@
         <v>121</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D119" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E119" s="52"/>
+        <v>13800</v>
+      </c>
+      <c r="E119" s="40"/>
       <c r="F119" s="20"/>
     </row>
     <row r="120" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3529,12 +3523,12 @@
         <v>122</v>
       </c>
       <c r="C120" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D120" s="32">
-        <v>1600</v>
-      </c>
-      <c r="E120" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E120" s="40"/>
       <c r="F120" s="20"/>
     </row>
     <row r="121" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3545,12 +3539,12 @@
         <v>123</v>
       </c>
       <c r="C121" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D121" s="32">
-        <v>13800</v>
-      </c>
-      <c r="E121" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E121" s="40"/>
       <c r="F121" s="20"/>
     </row>
     <row r="122" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3561,12 +3555,12 @@
         <v>124</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D122" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E122" s="52"/>
+        <v>5600</v>
+      </c>
+      <c r="E122" s="40"/>
       <c r="F122" s="20"/>
     </row>
     <row r="123" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3577,12 +3571,12 @@
         <v>125</v>
       </c>
       <c r="C123" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D123" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E123" s="52"/>
+        <v>2000</v>
+      </c>
+      <c r="E123" s="40"/>
       <c r="F123" s="20"/>
     </row>
     <row r="124" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3593,12 +3587,12 @@
         <v>126</v>
       </c>
       <c r="C124" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D124" s="32">
-        <v>5600</v>
-      </c>
-      <c r="E124" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E124" s="40"/>
       <c r="F124" s="20"/>
     </row>
     <row r="125" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3609,12 +3603,12 @@
         <v>127</v>
       </c>
       <c r="C125" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D125" s="32">
-        <v>2000</v>
-      </c>
-      <c r="E125" s="52"/>
+        <v>11500</v>
+      </c>
+      <c r="E125" s="40"/>
       <c r="F125" s="20"/>
     </row>
     <row r="126" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3625,12 +3619,12 @@
         <v>128</v>
       </c>
       <c r="C126" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D126" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E126" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E126" s="40"/>
       <c r="F126" s="20"/>
     </row>
     <row r="127" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3641,12 +3635,12 @@
         <v>129</v>
       </c>
       <c r="C127" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D127" s="32">
-        <v>11500</v>
-      </c>
-      <c r="E127" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E127" s="40"/>
       <c r="F127" s="20"/>
     </row>
     <row r="128" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3657,12 +3651,12 @@
         <v>130</v>
       </c>
       <c r="C128" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D128" s="32">
-        <v>500</v>
-      </c>
-      <c r="E128" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E128" s="40"/>
       <c r="F128" s="20"/>
     </row>
     <row r="129" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3673,12 +3667,12 @@
         <v>131</v>
       </c>
       <c r="C129" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D129" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E129" s="52"/>
+        <v>700</v>
+      </c>
+      <c r="E129" s="40"/>
       <c r="F129" s="20"/>
     </row>
     <row r="130" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3689,12 +3683,12 @@
         <v>132</v>
       </c>
       <c r="C130" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D130" s="32">
         <v>1000</v>
       </c>
-      <c r="E130" s="52"/>
+      <c r="E130" s="40"/>
       <c r="F130" s="20"/>
     </row>
     <row r="131" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3705,12 +3699,12 @@
         <v>133</v>
       </c>
       <c r="C131" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D131" s="32">
-        <v>700</v>
-      </c>
-      <c r="E131" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E131" s="40"/>
       <c r="F131" s="20"/>
     </row>
     <row r="132" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3718,15 +3712,15 @@
         <v>123</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="C132" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D132" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E132" s="52"/>
+        <v>3455</v>
+      </c>
+      <c r="E132" s="40"/>
       <c r="F132" s="20"/>
     </row>
     <row r="133" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3734,15 +3728,15 @@
         <v>124</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C133" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D133" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E133" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E133" s="40"/>
       <c r="F133" s="20"/>
     </row>
     <row r="134" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3750,15 +3744,15 @@
         <v>125</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C134" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D134" s="32">
-        <v>3455</v>
-      </c>
-      <c r="E134" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E134" s="40"/>
       <c r="F134" s="20"/>
     </row>
     <row r="135" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3769,12 +3763,12 @@
         <v>136</v>
       </c>
       <c r="C135" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D135" s="32">
-        <v>500</v>
-      </c>
-      <c r="E135" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E135" s="40"/>
       <c r="F135" s="20"/>
     </row>
     <row r="136" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3782,15 +3776,15 @@
         <v>127</v>
       </c>
       <c r="B136" s="21" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="C136" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D136" s="32">
-        <v>500</v>
-      </c>
-      <c r="E136" s="52"/>
+        <v>2000</v>
+      </c>
+      <c r="E136" s="40"/>
       <c r="F136" s="20"/>
     </row>
     <row r="137" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3798,15 +3792,15 @@
         <v>128</v>
       </c>
       <c r="B137" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C137" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D137" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E137" s="52"/>
+        <v>2000</v>
+      </c>
+      <c r="E137" s="40"/>
       <c r="F137" s="20"/>
     </row>
     <row r="138" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3814,16 +3808,16 @@
         <v>129</v>
       </c>
       <c r="B138" s="21" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C138" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D138" s="32">
-        <v>2000</v>
-      </c>
-      <c r="E138" s="52"/>
-      <c r="F138" s="20"/>
+        <v>550</v>
+      </c>
+      <c r="E138" s="40"/>
+      <c r="F138" s="22"/>
     </row>
     <row r="139" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="20">
@@ -3833,12 +3827,12 @@
         <v>139</v>
       </c>
       <c r="C139" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D139" s="32">
-        <v>2000</v>
-      </c>
-      <c r="E139" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E139" s="40"/>
       <c r="F139" s="20"/>
     </row>
     <row r="140" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3849,13 +3843,13 @@
         <v>140</v>
       </c>
       <c r="C140" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D140" s="32">
-        <v>550</v>
-      </c>
-      <c r="E140" s="52"/>
-      <c r="F140" s="22"/>
+        <v>12750</v>
+      </c>
+      <c r="E140" s="40"/>
+      <c r="F140" s="20"/>
     </row>
     <row r="141" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A141" s="20">
@@ -3865,12 +3859,12 @@
         <v>141</v>
       </c>
       <c r="C141" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D141" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E141" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E141" s="40"/>
       <c r="F141" s="20"/>
     </row>
     <row r="142" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3881,12 +3875,12 @@
         <v>142</v>
       </c>
       <c r="C142" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D142" s="32">
-        <v>12750</v>
-      </c>
-      <c r="E142" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E142" s="40"/>
       <c r="F142" s="20"/>
     </row>
     <row r="143" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3897,12 +3891,12 @@
         <v>143</v>
       </c>
       <c r="C143" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D143" s="32">
-        <v>500</v>
-      </c>
-      <c r="E143" s="52"/>
+        <v>1500</v>
+      </c>
+      <c r="E143" s="40"/>
       <c r="F143" s="20"/>
     </row>
     <row r="144" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3910,15 +3904,15 @@
         <v>135</v>
       </c>
       <c r="B144" s="21" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="C144" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D144" s="32">
-        <v>500</v>
-      </c>
-      <c r="E144" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E144" s="40"/>
       <c r="F144" s="20"/>
     </row>
     <row r="145" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3926,15 +3920,15 @@
         <v>136</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C145" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D145" s="32">
-        <v>1500</v>
-      </c>
-      <c r="E145" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E145" s="40"/>
       <c r="F145" s="20"/>
     </row>
     <row r="146" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3942,31 +3936,33 @@
         <v>137</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C146" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D146" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E146" s="52"/>
-      <c r="F146" s="20"/>
+        <v>500</v>
+      </c>
+      <c r="E146" s="40"/>
+      <c r="F146" s="21" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="147" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A147" s="20">
         <v>138</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C147" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D147" s="32">
-        <v>500</v>
-      </c>
-      <c r="E147" s="52"/>
+        <v>1000</v>
+      </c>
+      <c r="E147" s="40"/>
       <c r="F147" s="20"/>
     </row>
     <row r="148" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3974,84 +3970,84 @@
         <v>139</v>
       </c>
       <c r="B148" s="21" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="C148" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D148" s="32">
         <v>500</v>
       </c>
-      <c r="E148" s="52"/>
-      <c r="F148" s="21" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E148" s="40"/>
+      <c r="F148" s="20"/>
+    </row>
+    <row r="149" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
       <c r="A149" s="20">
         <v>140</v>
       </c>
       <c r="B149" s="21" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C149" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D149" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E149" s="52"/>
-      <c r="F149" s="20"/>
+        <v>1005</v>
+      </c>
+      <c r="E149" s="40"/>
+      <c r="F149" s="20" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="150" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A150" s="20">
         <v>141</v>
       </c>
       <c r="B150" s="21" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="C150" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D150" s="32">
         <v>500</v>
       </c>
-      <c r="E150" s="52"/>
+      <c r="E150" s="40"/>
       <c r="F150" s="20"/>
     </row>
-    <row r="151" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A151" s="20">
         <v>142</v>
       </c>
       <c r="B151" s="21" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="C151" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D151" s="32">
-        <v>1005</v>
-      </c>
-      <c r="E151" s="52"/>
-      <c r="F151" s="20" t="s">
-        <v>193</v>
-      </c>
+        <v>3075</v>
+      </c>
+      <c r="E151" s="40"/>
+      <c r="F151" s="20"/>
     </row>
     <row r="152" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A152" s="20">
         <v>143</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="C152" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D152" s="32">
-        <v>500</v>
-      </c>
-      <c r="E152" s="52"/>
-      <c r="F152" s="20"/>
+        <v>3500</v>
+      </c>
+      <c r="E152" s="40"/>
+      <c r="F152" s="21" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="153" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A153" s="20">
@@ -4061,12 +4057,12 @@
         <v>149</v>
       </c>
       <c r="C153" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D153" s="32">
-        <v>3075</v>
-      </c>
-      <c r="E153" s="52"/>
+        <v>2200</v>
+      </c>
+      <c r="E153" s="40"/>
       <c r="F153" s="20"/>
     </row>
     <row r="154" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4074,33 +4070,31 @@
         <v>145</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="C154" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D154" s="32">
-        <v>3500</v>
-      </c>
-      <c r="E154" s="52"/>
-      <c r="F154" s="21" t="s">
-        <v>150</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="E154" s="40"/>
+      <c r="F154" s="20"/>
     </row>
     <row r="155" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A155" s="20">
         <v>146</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="C155" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D155" s="32">
         <v>2200</v>
       </c>
-      <c r="E155" s="52"/>
+      <c r="E155" s="40"/>
       <c r="F155" s="20"/>
     </row>
     <row r="156" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4111,12 +4105,12 @@
         <v>177</v>
       </c>
       <c r="C156" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D156" s="32">
-        <v>550</v>
-      </c>
-      <c r="E156" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E156" s="40"/>
       <c r="F156" s="20"/>
     </row>
     <row r="157" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4124,15 +4118,15 @@
         <v>148</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="C157" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D157" s="32">
-        <v>2200</v>
-      </c>
-      <c r="E157" s="52"/>
+        <v>100</v>
+      </c>
+      <c r="E157" s="40"/>
       <c r="F157" s="20"/>
     </row>
     <row r="158" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4140,15 +4134,15 @@
         <v>149</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C158" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D158" s="32">
-        <v>500</v>
-      </c>
-      <c r="E158" s="52"/>
+        <v>492</v>
+      </c>
+      <c r="E158" s="40"/>
       <c r="F158" s="20"/>
     </row>
     <row r="159" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4156,31 +4150,33 @@
         <v>150</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="C159" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D159" s="32">
-        <v>100</v>
-      </c>
-      <c r="E159" s="52"/>
-      <c r="F159" s="20"/>
+        <v>550</v>
+      </c>
+      <c r="E159" s="40"/>
+      <c r="F159" s="21" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="160" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A160" s="20">
         <v>151</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="C160" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D160" s="32">
-        <v>492</v>
-      </c>
-      <c r="E160" s="52"/>
+        <v>1100</v>
+      </c>
+      <c r="E160" s="40"/>
       <c r="F160" s="20"/>
     </row>
     <row r="161" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4191,14 +4187,14 @@
         <v>180</v>
       </c>
       <c r="C161" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D161" s="32">
-        <v>550</v>
-      </c>
-      <c r="E161" s="52"/>
-      <c r="F161" s="21" t="s">
-        <v>195</v>
+        <v>500</v>
+      </c>
+      <c r="E161" s="40"/>
+      <c r="F161" s="22" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="162" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4209,13 +4205,13 @@
         <v>181</v>
       </c>
       <c r="C162" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D162" s="32">
-        <v>1100</v>
-      </c>
-      <c r="E162" s="52"/>
-      <c r="F162" s="20"/>
+        <v>20</v>
+      </c>
+      <c r="E162" s="40"/>
+      <c r="F162" s="25"/>
     </row>
     <row r="163" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A163" s="20">
@@ -4225,15 +4221,13 @@
         <v>182</v>
       </c>
       <c r="C163" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D163" s="32">
-        <v>500</v>
-      </c>
-      <c r="E163" s="52"/>
-      <c r="F163" s="22" t="s">
-        <v>196</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="E163" s="40"/>
+      <c r="F163" s="25"/>
     </row>
     <row r="164" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A164" s="20">
@@ -4243,12 +4237,12 @@
         <v>183</v>
       </c>
       <c r="C164" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D164" s="32">
-        <v>20</v>
-      </c>
-      <c r="E164" s="52"/>
+        <v>2000</v>
+      </c>
+      <c r="E164" s="40"/>
       <c r="F164" s="25"/>
     </row>
     <row r="165" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4259,13 +4253,13 @@
         <v>184</v>
       </c>
       <c r="C165" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D165" s="32">
-        <v>1000</v>
-      </c>
-      <c r="E165" s="52"/>
-      <c r="F165" s="25"/>
+        <v>2000</v>
+      </c>
+      <c r="E165" s="40"/>
+      <c r="F165" s="21"/>
     </row>
     <row r="166" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A166" s="20">
@@ -4275,12 +4269,12 @@
         <v>185</v>
       </c>
       <c r="C166" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D166" s="32">
-        <v>2000</v>
-      </c>
-      <c r="E166" s="52"/>
+        <v>500</v>
+      </c>
+      <c r="E166" s="40"/>
       <c r="F166" s="25"/>
     </row>
     <row r="167" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4291,13 +4285,13 @@
         <v>186</v>
       </c>
       <c r="C167" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D167" s="32">
         <v>2000</v>
       </c>
-      <c r="E167" s="52"/>
-      <c r="F167" s="21"/>
+      <c r="E167" s="40"/>
+      <c r="F167" s="25"/>
     </row>
     <row r="168" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A168" s="20">
@@ -4307,12 +4301,12 @@
         <v>187</v>
       </c>
       <c r="C168" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D168" s="32">
-        <v>500</v>
-      </c>
-      <c r="E168" s="52"/>
+        <v>550</v>
+      </c>
+      <c r="E168" s="40"/>
       <c r="F168" s="25"/>
     </row>
     <row r="169" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4323,133 +4317,117 @@
         <v>188</v>
       </c>
       <c r="C169" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D169" s="32">
-        <v>2000</v>
-      </c>
-      <c r="E169" s="52"/>
+        <v>750</v>
+      </c>
+      <c r="E169" s="40"/>
       <c r="F169" s="25"/>
     </row>
-    <row r="170" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
       <c r="A170" s="20">
         <v>161</v>
       </c>
-      <c r="B170" s="21" t="s">
-        <v>189</v>
+      <c r="B170" s="24" t="s">
+        <v>162</v>
       </c>
       <c r="C170" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="D170" s="32">
-        <v>550</v>
-      </c>
-      <c r="E170" s="52"/>
-      <c r="F170" s="25"/>
-    </row>
-    <row r="171" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+      <c r="D170" s="33">
+        <v>485</v>
+      </c>
+      <c r="E170" s="40"/>
+      <c r="F170" s="23" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" s="2" customFormat="1" ht="36" x14ac:dyDescent="0.2">
       <c r="A171" s="20">
         <v>162</v>
       </c>
-      <c r="B171" s="21" t="s">
-        <v>190</v>
+      <c r="B171" s="20" t="s">
+        <v>195</v>
       </c>
       <c r="C171" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="D171" s="32">
-        <v>750</v>
-      </c>
-      <c r="E171" s="52"/>
+        <v>163</v>
+      </c>
+      <c r="D171" s="34">
+        <v>500</v>
+      </c>
+      <c r="E171" s="40"/>
       <c r="F171" s="25"/>
     </row>
-    <row r="172" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
-      <c r="A172" s="20">
-        <v>163</v>
-      </c>
-      <c r="B172" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="C172" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="D172" s="33">
-        <v>485</v>
-      </c>
-      <c r="E172" s="52"/>
-      <c r="F172" s="23" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" s="2" customFormat="1" ht="36" x14ac:dyDescent="0.2">
-      <c r="A173" s="20">
-        <v>164</v>
-      </c>
-      <c r="B173" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="C173" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="D173" s="34">
-        <v>500</v>
-      </c>
-      <c r="E173" s="52"/>
-      <c r="F173" s="25"/>
+    <row r="172" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="6"/>
+      <c r="B172" s="13"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="10"/>
+      <c r="F172" s="8"/>
+    </row>
+    <row r="173" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="8"/>
+      <c r="B173" s="13"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="3"/>
+      <c r="F173" s="3"/>
     </row>
     <row r="174" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="6"/>
-      <c r="B174" s="13"/>
-      <c r="C174" s="3"/>
-      <c r="D174" s="7"/>
-      <c r="E174" s="10"/>
-      <c r="F174" s="8"/>
-    </row>
-    <row r="175" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="8"/>
-      <c r="B175" s="13"/>
-      <c r="C175" s="3"/>
-      <c r="D175" s="3"/>
-      <c r="E175" s="3"/>
-      <c r="F175" s="3"/>
+      <c r="A174" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B174" s="38"/>
+      <c r="C174" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" s="38"/>
+      <c r="E174" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F174" s="28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B175" s="39"/>
+      <c r="C175" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="39"/>
+      <c r="E175" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="F175" s="31" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="176" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="B176" s="50"/>
-      <c r="C176" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="D176" s="50"/>
-      <c r="E176" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F176" s="28" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="51" t="s">
-        <v>3</v>
-      </c>
-      <c r="B177" s="51"/>
-      <c r="C177" s="51" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="51"/>
-      <c r="E177" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="F177" s="31" t="s">
-        <v>3</v>
-      </c>
+      <c r="A176" s="29"/>
+      <c r="B176" s="29"/>
+      <c r="C176" s="29"/>
+      <c r="D176" s="29"/>
+      <c r="E176" s="30"/>
+      <c r="F176" s="29"/>
+    </row>
+    <row r="177" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="29"/>
+      <c r="B177" s="29"/>
+      <c r="C177" s="29"/>
+      <c r="D177" s="29"/>
+      <c r="E177" s="30"/>
+      <c r="F177" s="29"/>
     </row>
     <row r="178" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A178" s="29"/>
       <c r="B178" s="29"/>
       <c r="C178" s="29"/>
-      <c r="D178" s="29"/>
+      <c r="D178" s="27"/>
       <c r="E178" s="30"/>
       <c r="F178" s="29"/>
     </row>
@@ -4458,126 +4436,110 @@
       <c r="B179" s="29"/>
       <c r="C179" s="29"/>
       <c r="D179" s="29"/>
-      <c r="E179" s="30"/>
+      <c r="E179" s="29"/>
       <c r="F179" s="29"/>
     </row>
     <row r="180" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A180" s="29"/>
       <c r="B180" s="29"/>
       <c r="C180" s="29"/>
-      <c r="D180" s="27"/>
+      <c r="D180" s="29"/>
       <c r="E180" s="30"/>
       <c r="F180" s="29"/>
     </row>
-    <row r="181" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="29"/>
-      <c r="B181" s="29"/>
-      <c r="C181" s="29"/>
-      <c r="D181" s="29"/>
-      <c r="E181" s="29"/>
-      <c r="F181" s="29"/>
-    </row>
-    <row r="182" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="29"/>
-      <c r="B182" s="29"/>
-      <c r="C182" s="29"/>
-      <c r="D182" s="29"/>
-      <c r="E182" s="30"/>
-      <c r="F182" s="29"/>
-    </row>
-    <row r="183" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="50" t="s">
+    <row r="181" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B183" s="50"/>
-      <c r="C183" s="50" t="s">
+      <c r="B181" s="38"/>
+      <c r="C181" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="D183" s="50"/>
-      <c r="E183" s="28" t="s">
+      <c r="D181" s="38"/>
+      <c r="E181" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="F183" s="28" t="s">
+      <c r="F181" s="28" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="182" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="183" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E183" s="12"/>
+      <c r="F183" s="12"/>
+    </row>
     <row r="184" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="185" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E185" s="12"/>
-      <c r="F185" s="12"/>
-    </row>
+    <row r="185" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="186" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="187" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="187" spans="1:6" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="C187" s="11"/>
+      <c r="D187" s="11"/>
+      <c r="E187" s="11"/>
+      <c r="F187" s="11"/>
+    </row>
     <row r="188" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="189" spans="1:6" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="C189" s="11"/>
-      <c r="D189" s="11"/>
-      <c r="E189" s="11"/>
-      <c r="F189" s="11"/>
-    </row>
-    <row r="190" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="191" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="196" spans="6:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="F196" s="5"/>
+    <row r="189" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="194" spans="6:6" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="F194" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:F172" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A9:F170" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="13">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A176:B176"/>
-    <mergeCell ref="A177:B177"/>
-    <mergeCell ref="A183:B183"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="E10:E173"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="A1:B4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A174:B174"/>
+    <mergeCell ref="A175:B175"/>
+    <mergeCell ref="A181:B181"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="E10:E171"/>
   </mergeCells>
-  <conditionalFormatting sqref="B1:B158 M1:M9 M110:M1048576 B161:B1048576">
+  <conditionalFormatting sqref="M108:M1048576 B1:B156 M1:M9 B159:B1048576">
     <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B10:B158 B161:B171">
+  <conditionalFormatting sqref="B159:B169 B10:B156">
     <cfRule type="duplicateValues" dxfId="12" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="11" priority="46"/>
+  <conditionalFormatting sqref="B157:B158">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+  <conditionalFormatting sqref="B171">
+    <cfRule type="duplicateValues" dxfId="10" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F45">
-    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
+  <conditionalFormatting sqref="F31">
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+  <conditionalFormatting sqref="F44">
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F59">
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+  <conditionalFormatting sqref="F50">
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F140">
-    <cfRule type="duplicateValues" dxfId="6" priority="15"/>
+  <conditionalFormatting sqref="F58">
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F148">
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+  <conditionalFormatting sqref="F138">
+    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F154">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+  <conditionalFormatting sqref="F146">
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F152">
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F159">
+    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F161">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F163">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F167">
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B159:B160">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="F165">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="99" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03_240626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03_240626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8B4482-4DEA-4B96-93FC-6F8AA886A331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067BDEAC-D790-4EB3-AE9D-42DE2B1769D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -939,6 +939,27 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -974,27 +995,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1141,58 +1141,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>488016</xdr:colOff>
-      <xdr:row>167</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>307037</xdr:colOff>
-      <xdr:row>167</xdr:row>
-      <xdr:rowOff>3941</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="logo chuan ">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="11424957" y="2119033"/>
-          <a:ext cx="1634377" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>194969</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -1218,7 +1166,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1543,56 +1491,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="28" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="30" t="s">
+      <c r="A2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="31"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="30" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="38"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="32" t="s">
+      <c r="A4" s="45"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="33"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="40"/>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="42"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="31"/>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
@@ -1656,10 +1604,10 @@
       <c r="C10" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="28">
         <v>500</v>
       </c>
-      <c r="E10" s="45" t="s">
+      <c r="E10" s="34" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="17"/>
@@ -1674,10 +1622,10 @@
       <c r="C11" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="28">
         <v>499</v>
       </c>
-      <c r="E11" s="45"/>
+      <c r="E11" s="34"/>
       <c r="F11" s="17"/>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1690,10 +1638,10 @@
       <c r="C12" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="28">
         <v>510</v>
       </c>
-      <c r="E12" s="45"/>
+      <c r="E12" s="34"/>
       <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -1706,10 +1654,10 @@
       <c r="C13" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="28">
         <v>6500</v>
       </c>
-      <c r="E13" s="45"/>
+      <c r="E13" s="34"/>
       <c r="F13" s="17" t="s">
         <v>187</v>
       </c>
@@ -1724,10 +1672,10 @@
       <c r="C14" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="28">
         <v>1000</v>
       </c>
-      <c r="E14" s="45"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="18"/>
     </row>
     <row r="15" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1740,10 +1688,10 @@
       <c r="C15" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D15" s="46">
+      <c r="D15" s="28">
         <v>1000</v>
       </c>
-      <c r="E15" s="45"/>
+      <c r="E15" s="34"/>
       <c r="F15" s="17"/>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1756,10 +1704,10 @@
       <c r="C16" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="28">
         <v>2500</v>
       </c>
-      <c r="E16" s="45"/>
+      <c r="E16" s="34"/>
       <c r="F16" s="17"/>
     </row>
     <row r="17" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1772,10 +1720,10 @@
       <c r="C17" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D17" s="46">
+      <c r="D17" s="28">
         <v>2000</v>
       </c>
-      <c r="E17" s="45"/>
+      <c r="E17" s="34"/>
       <c r="F17" s="17"/>
     </row>
     <row r="18" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1788,10 +1736,10 @@
       <c r="C18" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="46">
+      <c r="D18" s="28">
         <v>1000</v>
       </c>
-      <c r="E18" s="45"/>
+      <c r="E18" s="34"/>
       <c r="F18" s="17"/>
     </row>
     <row r="19" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1804,10 +1752,10 @@
       <c r="C19" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D19" s="46">
+      <c r="D19" s="28">
         <v>500</v>
       </c>
-      <c r="E19" s="45"/>
+      <c r="E19" s="34"/>
       <c r="F19" s="17"/>
     </row>
     <row r="20" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1820,10 +1768,10 @@
       <c r="C20" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D20" s="46">
+      <c r="D20" s="28">
         <v>45400</v>
       </c>
-      <c r="E20" s="45"/>
+      <c r="E20" s="34"/>
       <c r="F20" s="17"/>
     </row>
     <row r="21" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1836,10 +1784,10 @@
       <c r="C21" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D21" s="46">
+      <c r="D21" s="28">
         <v>1000</v>
       </c>
-      <c r="E21" s="45"/>
+      <c r="E21" s="34"/>
       <c r="F21" s="17"/>
     </row>
     <row r="22" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1852,10 +1800,10 @@
       <c r="C22" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D22" s="46">
+      <c r="D22" s="28">
         <v>500</v>
       </c>
-      <c r="E22" s="45"/>
+      <c r="E22" s="34"/>
       <c r="F22" s="17"/>
     </row>
     <row r="23" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1868,10 +1816,10 @@
       <c r="C23" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D23" s="46">
+      <c r="D23" s="28">
         <v>520</v>
       </c>
-      <c r="E23" s="45"/>
+      <c r="E23" s="34"/>
       <c r="F23" s="17"/>
     </row>
     <row r="24" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1884,10 +1832,10 @@
       <c r="C24" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D24" s="46">
+      <c r="D24" s="28">
         <v>500</v>
       </c>
-      <c r="E24" s="45"/>
+      <c r="E24" s="34"/>
       <c r="F24" s="17"/>
     </row>
     <row r="25" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1900,10 +1848,10 @@
       <c r="C25" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D25" s="46">
+      <c r="D25" s="28">
         <v>1500</v>
       </c>
-      <c r="E25" s="45"/>
+      <c r="E25" s="34"/>
       <c r="F25" s="17"/>
     </row>
     <row r="26" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1916,10 +1864,10 @@
       <c r="C26" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D26" s="46">
+      <c r="D26" s="28">
         <v>1500</v>
       </c>
-      <c r="E26" s="45"/>
+      <c r="E26" s="34"/>
       <c r="F26" s="17"/>
     </row>
     <row r="27" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1932,10 +1880,10 @@
       <c r="C27" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D27" s="46">
+      <c r="D27" s="28">
         <v>1500</v>
       </c>
-      <c r="E27" s="45"/>
+      <c r="E27" s="34"/>
       <c r="F27" s="17"/>
     </row>
     <row r="28" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1948,10 +1896,10 @@
       <c r="C28" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D28" s="46">
+      <c r="D28" s="28">
         <v>1500</v>
       </c>
-      <c r="E28" s="45"/>
+      <c r="E28" s="34"/>
       <c r="F28" s="17"/>
     </row>
     <row r="29" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1964,10 +1912,10 @@
       <c r="C29" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D29" s="46">
+      <c r="D29" s="28">
         <v>6500</v>
       </c>
-      <c r="E29" s="45"/>
+      <c r="E29" s="34"/>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1980,10 +1928,10 @@
       <c r="C30" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D30" s="46">
+      <c r="D30" s="28">
         <v>1447</v>
       </c>
-      <c r="E30" s="45"/>
+      <c r="E30" s="34"/>
       <c r="F30" s="17"/>
     </row>
     <row r="31" spans="1:6" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1996,10 +1944,10 @@
       <c r="C31" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D31" s="46">
+      <c r="D31" s="28">
         <v>14000</v>
       </c>
-      <c r="E31" s="45"/>
+      <c r="E31" s="34"/>
       <c r="F31" s="19" t="s">
         <v>188</v>
       </c>
@@ -2014,10 +1962,10 @@
       <c r="C32" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D32" s="46">
+      <c r="D32" s="28">
         <v>1500</v>
       </c>
-      <c r="E32" s="45"/>
+      <c r="E32" s="34"/>
       <c r="F32" s="17"/>
     </row>
     <row r="33" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2030,10 +1978,10 @@
       <c r="C33" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D33" s="46">
+      <c r="D33" s="28">
         <v>5000</v>
       </c>
-      <c r="E33" s="45"/>
+      <c r="E33" s="34"/>
       <c r="F33" s="17"/>
     </row>
     <row r="34" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2046,10 +1994,10 @@
       <c r="C34" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D34" s="46">
+      <c r="D34" s="28">
         <v>1500</v>
       </c>
-      <c r="E34" s="45"/>
+      <c r="E34" s="34"/>
       <c r="F34" s="17"/>
     </row>
     <row r="35" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2062,10 +2010,10 @@
       <c r="C35" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D35" s="46">
+      <c r="D35" s="28">
         <v>500</v>
       </c>
-      <c r="E35" s="45"/>
+      <c r="E35" s="34"/>
       <c r="F35" s="17"/>
     </row>
     <row r="36" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2078,10 +2026,10 @@
       <c r="C36" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D36" s="46">
+      <c r="D36" s="28">
         <v>2000</v>
       </c>
-      <c r="E36" s="45"/>
+      <c r="E36" s="34"/>
       <c r="F36" s="17"/>
     </row>
     <row r="37" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2094,10 +2042,10 @@
       <c r="C37" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="46">
+      <c r="D37" s="28">
         <v>1520</v>
       </c>
-      <c r="E37" s="45"/>
+      <c r="E37" s="34"/>
       <c r="F37" s="17"/>
     </row>
     <row r="38" spans="1:6" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2110,10 +2058,10 @@
       <c r="C38" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D38" s="46">
+      <c r="D38" s="28">
         <v>1000</v>
       </c>
-      <c r="E38" s="45"/>
+      <c r="E38" s="34"/>
       <c r="F38" s="17"/>
     </row>
     <row r="39" spans="1:6" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2126,10 +2074,10 @@
       <c r="C39" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="46">
+      <c r="D39" s="28">
         <v>500</v>
       </c>
-      <c r="E39" s="45"/>
+      <c r="E39" s="34"/>
       <c r="F39" s="17"/>
     </row>
     <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2142,10 +2090,10 @@
       <c r="C40" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D40" s="46">
+      <c r="D40" s="28">
         <v>520</v>
       </c>
-      <c r="E40" s="45"/>
+      <c r="E40" s="34"/>
       <c r="F40" s="17"/>
     </row>
     <row r="41" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2158,10 +2106,10 @@
       <c r="C41" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D41" s="46">
+      <c r="D41" s="28">
         <v>1500</v>
       </c>
-      <c r="E41" s="45"/>
+      <c r="E41" s="34"/>
       <c r="F41" s="17"/>
     </row>
     <row r="42" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2174,10 +2122,10 @@
       <c r="C42" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D42" s="46">
+      <c r="D42" s="28">
         <v>1600</v>
       </c>
-      <c r="E42" s="45"/>
+      <c r="E42" s="34"/>
       <c r="F42" s="17"/>
     </row>
     <row r="43" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2190,10 +2138,10 @@
       <c r="C43" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D43" s="46">
+      <c r="D43" s="28">
         <v>1000</v>
       </c>
-      <c r="E43" s="45"/>
+      <c r="E43" s="34"/>
       <c r="F43" s="17"/>
     </row>
     <row r="44" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2206,10 +2154,10 @@
       <c r="C44" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D44" s="46">
+      <c r="D44" s="28">
         <v>500</v>
       </c>
-      <c r="E44" s="45"/>
+      <c r="E44" s="34"/>
       <c r="F44" s="18"/>
     </row>
     <row r="45" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2222,10 +2170,10 @@
       <c r="C45" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D45" s="46">
+      <c r="D45" s="28">
         <v>500</v>
       </c>
-      <c r="E45" s="45"/>
+      <c r="E45" s="34"/>
       <c r="F45" s="17"/>
     </row>
     <row r="46" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2238,10 +2186,10 @@
       <c r="C46" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D46" s="46">
+      <c r="D46" s="28">
         <v>500</v>
       </c>
-      <c r="E46" s="45"/>
+      <c r="E46" s="34"/>
       <c r="F46" s="17"/>
     </row>
     <row r="47" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2254,10 +2202,10 @@
       <c r="C47" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="46">
+      <c r="D47" s="28">
         <v>2050</v>
       </c>
-      <c r="E47" s="45"/>
+      <c r="E47" s="34"/>
       <c r="F47" s="17"/>
     </row>
     <row r="48" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2270,10 +2218,10 @@
       <c r="C48" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D48" s="46">
+      <c r="D48" s="28">
         <v>500</v>
       </c>
-      <c r="E48" s="45"/>
+      <c r="E48" s="34"/>
       <c r="F48" s="17"/>
     </row>
     <row r="49" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2286,10 +2234,10 @@
       <c r="C49" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D49" s="46">
+      <c r="D49" s="28">
         <v>500</v>
       </c>
-      <c r="E49" s="45"/>
+      <c r="E49" s="34"/>
       <c r="F49" s="17"/>
     </row>
     <row r="50" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2302,10 +2250,10 @@
       <c r="C50" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D50" s="46">
+      <c r="D50" s="28">
         <v>1600</v>
       </c>
-      <c r="E50" s="45"/>
+      <c r="E50" s="34"/>
       <c r="F50" s="18" t="s">
         <v>189</v>
       </c>
@@ -2320,10 +2268,10 @@
       <c r="C51" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D51" s="46">
+      <c r="D51" s="28">
         <v>600</v>
       </c>
-      <c r="E51" s="45"/>
+      <c r="E51" s="34"/>
       <c r="F51" s="17"/>
     </row>
     <row r="52" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2336,10 +2284,10 @@
       <c r="C52" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D52" s="46">
+      <c r="D52" s="28">
         <v>1000</v>
       </c>
-      <c r="E52" s="45"/>
+      <c r="E52" s="34"/>
       <c r="F52" s="17"/>
     </row>
     <row r="53" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2352,10 +2300,10 @@
       <c r="C53" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D53" s="46">
+      <c r="D53" s="28">
         <v>5500</v>
       </c>
-      <c r="E53" s="45"/>
+      <c r="E53" s="34"/>
       <c r="F53" s="17"/>
     </row>
     <row r="54" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2368,10 +2316,10 @@
       <c r="C54" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D54" s="46">
+      <c r="D54" s="28">
         <v>3550</v>
       </c>
-      <c r="E54" s="45"/>
+      <c r="E54" s="34"/>
       <c r="F54" s="17"/>
     </row>
     <row r="55" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2384,10 +2332,10 @@
       <c r="C55" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D55" s="46">
+      <c r="D55" s="28">
         <v>550</v>
       </c>
-      <c r="E55" s="45"/>
+      <c r="E55" s="34"/>
       <c r="F55" s="17"/>
     </row>
     <row r="56" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2400,10 +2348,10 @@
       <c r="C56" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D56" s="46">
+      <c r="D56" s="28">
         <v>1000</v>
       </c>
-      <c r="E56" s="45"/>
+      <c r="E56" s="34"/>
       <c r="F56" s="17"/>
     </row>
     <row r="57" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2416,10 +2364,10 @@
       <c r="C57" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D57" s="46">
+      <c r="D57" s="28">
         <v>2000</v>
       </c>
-      <c r="E57" s="45"/>
+      <c r="E57" s="34"/>
       <c r="F57" s="17"/>
     </row>
     <row r="58" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
@@ -2432,10 +2380,10 @@
       <c r="C58" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D58" s="46">
+      <c r="D58" s="28">
         <v>10770</v>
       </c>
-      <c r="E58" s="45"/>
+      <c r="E58" s="34"/>
       <c r="F58" s="19" t="s">
         <v>190</v>
       </c>
@@ -2450,10 +2398,10 @@
       <c r="C59" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D59" s="46">
+      <c r="D59" s="28">
         <v>1000</v>
       </c>
-      <c r="E59" s="45"/>
+      <c r="E59" s="34"/>
       <c r="F59" s="17"/>
     </row>
     <row r="60" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2466,10 +2414,10 @@
       <c r="C60" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D60" s="46">
+      <c r="D60" s="28">
         <v>2500</v>
       </c>
-      <c r="E60" s="45"/>
+      <c r="E60" s="34"/>
       <c r="F60" s="17"/>
     </row>
     <row r="61" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2482,10 +2430,10 @@
       <c r="C61" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="46">
+      <c r="D61" s="28">
         <v>1000</v>
       </c>
-      <c r="E61" s="45"/>
+      <c r="E61" s="34"/>
       <c r="F61" s="17"/>
     </row>
     <row r="62" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2498,10 +2446,10 @@
       <c r="C62" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D62" s="46">
+      <c r="D62" s="28">
         <v>500</v>
       </c>
-      <c r="E62" s="45"/>
+      <c r="E62" s="34"/>
       <c r="F62" s="18" t="s">
         <v>191</v>
       </c>
@@ -2516,10 +2464,10 @@
       <c r="C63" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D63" s="46">
+      <c r="D63" s="28">
         <v>1000</v>
       </c>
-      <c r="E63" s="45"/>
+      <c r="E63" s="34"/>
       <c r="F63" s="17"/>
     </row>
     <row r="64" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2532,10 +2480,10 @@
       <c r="C64" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D64" s="46">
+      <c r="D64" s="28">
         <v>1500</v>
       </c>
-      <c r="E64" s="45"/>
+      <c r="E64" s="34"/>
       <c r="F64" s="17"/>
     </row>
     <row r="65" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2548,10 +2496,10 @@
       <c r="C65" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D65" s="46">
+      <c r="D65" s="28">
         <v>5500</v>
       </c>
-      <c r="E65" s="45"/>
+      <c r="E65" s="34"/>
       <c r="F65" s="17"/>
     </row>
     <row r="66" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2564,10 +2512,10 @@
       <c r="C66" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D66" s="46">
+      <c r="D66" s="28">
         <v>3000</v>
       </c>
-      <c r="E66" s="45"/>
+      <c r="E66" s="34"/>
       <c r="F66" s="17"/>
     </row>
     <row r="67" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2580,10 +2528,10 @@
       <c r="C67" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D67" s="46">
+      <c r="D67" s="28">
         <v>7400</v>
       </c>
-      <c r="E67" s="45"/>
+      <c r="E67" s="34"/>
       <c r="F67" s="17"/>
     </row>
     <row r="68" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2596,10 +2544,10 @@
       <c r="C68" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D68" s="46">
+      <c r="D68" s="28">
         <v>1500</v>
       </c>
-      <c r="E68" s="45"/>
+      <c r="E68" s="34"/>
       <c r="F68" s="17"/>
     </row>
     <row r="69" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2612,10 +2560,10 @@
       <c r="C69" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D69" s="46">
+      <c r="D69" s="28">
         <v>550</v>
       </c>
-      <c r="E69" s="45"/>
+      <c r="E69" s="34"/>
       <c r="F69" s="17"/>
     </row>
     <row r="70" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2628,10 +2576,10 @@
       <c r="C70" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D70" s="46">
+      <c r="D70" s="28">
         <v>1000</v>
       </c>
-      <c r="E70" s="45"/>
+      <c r="E70" s="34"/>
       <c r="F70" s="17"/>
     </row>
     <row r="71" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2644,10 +2592,10 @@
       <c r="C71" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D71" s="46">
+      <c r="D71" s="28">
         <v>550</v>
       </c>
-      <c r="E71" s="45"/>
+      <c r="E71" s="34"/>
       <c r="F71" s="17"/>
     </row>
     <row r="72" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2660,10 +2608,10 @@
       <c r="C72" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D72" s="46">
+      <c r="D72" s="28">
         <v>500</v>
       </c>
-      <c r="E72" s="45"/>
+      <c r="E72" s="34"/>
       <c r="F72" s="17"/>
     </row>
     <row r="73" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2676,10 +2624,10 @@
       <c r="C73" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D73" s="46">
+      <c r="D73" s="28">
         <v>2500</v>
       </c>
-      <c r="E73" s="45"/>
+      <c r="E73" s="34"/>
       <c r="F73" s="17"/>
     </row>
     <row r="74" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2692,10 +2640,10 @@
       <c r="C74" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D74" s="46">
+      <c r="D74" s="28">
         <v>1500</v>
       </c>
-      <c r="E74" s="45"/>
+      <c r="E74" s="34"/>
       <c r="F74" s="17"/>
     </row>
     <row r="75" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2708,10 +2656,10 @@
       <c r="C75" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D75" s="46">
+      <c r="D75" s="28">
         <v>1000</v>
       </c>
-      <c r="E75" s="45"/>
+      <c r="E75" s="34"/>
       <c r="F75" s="17"/>
     </row>
     <row r="76" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2724,10 +2672,10 @@
       <c r="C76" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D76" s="46">
+      <c r="D76" s="28">
         <v>550</v>
       </c>
-      <c r="E76" s="45"/>
+      <c r="E76" s="34"/>
       <c r="F76" s="17"/>
     </row>
     <row r="77" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2740,10 +2688,10 @@
       <c r="C77" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D77" s="46">
+      <c r="D77" s="28">
         <v>1000</v>
       </c>
-      <c r="E77" s="45"/>
+      <c r="E77" s="34"/>
       <c r="F77" s="17"/>
     </row>
     <row r="78" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2756,10 +2704,10 @@
       <c r="C78" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D78" s="46">
+      <c r="D78" s="28">
         <v>1000</v>
       </c>
-      <c r="E78" s="45"/>
+      <c r="E78" s="34"/>
       <c r="F78" s="17"/>
     </row>
     <row r="79" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2772,10 +2720,10 @@
       <c r="C79" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D79" s="46">
+      <c r="D79" s="28">
         <v>500</v>
       </c>
-      <c r="E79" s="45"/>
+      <c r="E79" s="34"/>
       <c r="F79" s="17"/>
     </row>
     <row r="80" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2788,10 +2736,10 @@
       <c r="C80" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D80" s="46">
+      <c r="D80" s="28">
         <v>600</v>
       </c>
-      <c r="E80" s="45"/>
+      <c r="E80" s="34"/>
       <c r="F80" s="17"/>
     </row>
     <row r="81" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2804,10 +2752,10 @@
       <c r="C81" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D81" s="46">
+      <c r="D81" s="28">
         <v>500</v>
       </c>
-      <c r="E81" s="45"/>
+      <c r="E81" s="34"/>
       <c r="F81" s="17"/>
     </row>
     <row r="82" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2820,10 +2768,10 @@
       <c r="C82" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D82" s="46">
+      <c r="D82" s="28">
         <v>500</v>
       </c>
-      <c r="E82" s="45"/>
+      <c r="E82" s="34"/>
       <c r="F82" s="17"/>
     </row>
     <row r="83" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2836,10 +2784,10 @@
       <c r="C83" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D83" s="46">
+      <c r="D83" s="28">
         <v>500</v>
       </c>
-      <c r="E83" s="45"/>
+      <c r="E83" s="34"/>
       <c r="F83" s="17"/>
     </row>
     <row r="84" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2852,10 +2800,10 @@
       <c r="C84" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D84" s="46">
+      <c r="D84" s="28">
         <v>1500</v>
       </c>
-      <c r="E84" s="45"/>
+      <c r="E84" s="34"/>
       <c r="F84" s="17"/>
     </row>
     <row r="85" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2868,10 +2816,10 @@
       <c r="C85" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D85" s="46">
+      <c r="D85" s="28">
         <v>500</v>
       </c>
-      <c r="E85" s="45"/>
+      <c r="E85" s="34"/>
       <c r="F85" s="17"/>
     </row>
     <row r="86" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2884,10 +2832,10 @@
       <c r="C86" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D86" s="46">
+      <c r="D86" s="28">
         <v>500</v>
       </c>
-      <c r="E86" s="45"/>
+      <c r="E86" s="34"/>
       <c r="F86" s="17"/>
     </row>
     <row r="87" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2900,10 +2848,10 @@
       <c r="C87" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D87" s="46">
+      <c r="D87" s="28">
         <v>1000</v>
       </c>
-      <c r="E87" s="45"/>
+      <c r="E87" s="34"/>
       <c r="F87" s="17"/>
     </row>
     <row r="88" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2916,10 +2864,10 @@
       <c r="C88" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D88" s="46">
+      <c r="D88" s="28">
         <v>1000</v>
       </c>
-      <c r="E88" s="45"/>
+      <c r="E88" s="34"/>
       <c r="F88" s="17"/>
     </row>
     <row r="89" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2932,10 +2880,10 @@
       <c r="C89" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D89" s="46">
+      <c r="D89" s="28">
         <v>4000</v>
       </c>
-      <c r="E89" s="45"/>
+      <c r="E89" s="34"/>
       <c r="F89" s="17"/>
     </row>
     <row r="90" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2948,10 +2896,10 @@
       <c r="C90" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D90" s="46">
+      <c r="D90" s="28">
         <v>2500</v>
       </c>
-      <c r="E90" s="45"/>
+      <c r="E90" s="34"/>
       <c r="F90" s="17"/>
     </row>
     <row r="91" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2964,10 +2912,10 @@
       <c r="C91" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D91" s="46">
+      <c r="D91" s="28">
         <v>500</v>
       </c>
-      <c r="E91" s="45"/>
+      <c r="E91" s="34"/>
       <c r="F91" s="17"/>
     </row>
     <row r="92" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2980,10 +2928,10 @@
       <c r="C92" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D92" s="46">
+      <c r="D92" s="28">
         <v>500</v>
       </c>
-      <c r="E92" s="45"/>
+      <c r="E92" s="34"/>
       <c r="F92" s="17"/>
     </row>
     <row r="93" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2996,10 +2944,10 @@
       <c r="C93" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D93" s="46">
+      <c r="D93" s="28">
         <v>8830</v>
       </c>
-      <c r="E93" s="45"/>
+      <c r="E93" s="34"/>
       <c r="F93" s="17"/>
     </row>
     <row r="94" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3012,10 +2960,10 @@
       <c r="C94" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D94" s="46">
+      <c r="D94" s="28">
         <v>500</v>
       </c>
-      <c r="E94" s="45"/>
+      <c r="E94" s="34"/>
       <c r="F94" s="17"/>
     </row>
     <row r="95" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3028,10 +2976,10 @@
       <c r="C95" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D95" s="46">
+      <c r="D95" s="28">
         <v>1000</v>
       </c>
-      <c r="E95" s="45"/>
+      <c r="E95" s="34"/>
       <c r="F95" s="17"/>
     </row>
     <row r="96" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3044,10 +2992,10 @@
       <c r="C96" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D96" s="46">
+      <c r="D96" s="28">
         <v>500</v>
       </c>
-      <c r="E96" s="45"/>
+      <c r="E96" s="34"/>
       <c r="F96" s="17"/>
     </row>
     <row r="97" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3060,10 +3008,10 @@
       <c r="C97" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D97" s="46">
+      <c r="D97" s="28">
         <v>6500</v>
       </c>
-      <c r="E97" s="45"/>
+      <c r="E97" s="34"/>
       <c r="F97" s="17"/>
     </row>
     <row r="98" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3076,10 +3024,10 @@
       <c r="C98" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D98" s="46">
+      <c r="D98" s="28">
         <v>1000</v>
       </c>
-      <c r="E98" s="45"/>
+      <c r="E98" s="34"/>
       <c r="F98" s="17"/>
     </row>
     <row r="99" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3092,10 +3040,10 @@
       <c r="C99" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D99" s="46">
+      <c r="D99" s="28">
         <v>1100</v>
       </c>
-      <c r="E99" s="45"/>
+      <c r="E99" s="34"/>
       <c r="F99" s="17"/>
     </row>
     <row r="100" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3108,10 +3056,10 @@
       <c r="C100" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D100" s="46">
+      <c r="D100" s="28">
         <v>1000</v>
       </c>
-      <c r="E100" s="45"/>
+      <c r="E100" s="34"/>
       <c r="F100" s="17"/>
     </row>
     <row r="101" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3124,10 +3072,10 @@
       <c r="C101" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D101" s="46">
+      <c r="D101" s="28">
         <v>1000</v>
       </c>
-      <c r="E101" s="45"/>
+      <c r="E101" s="34"/>
       <c r="F101" s="17"/>
     </row>
     <row r="102" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3140,10 +3088,10 @@
       <c r="C102" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D102" s="46">
+      <c r="D102" s="28">
         <v>1000</v>
       </c>
-      <c r="E102" s="45"/>
+      <c r="E102" s="34"/>
       <c r="F102" s="17"/>
     </row>
     <row r="103" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3156,10 +3104,10 @@
       <c r="C103" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D103" s="46">
+      <c r="D103" s="28">
         <v>500</v>
       </c>
-      <c r="E103" s="45"/>
+      <c r="E103" s="34"/>
       <c r="F103" s="17"/>
     </row>
     <row r="104" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3172,10 +3120,10 @@
       <c r="C104" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D104" s="46">
+      <c r="D104" s="28">
         <v>1000</v>
       </c>
-      <c r="E104" s="45"/>
+      <c r="E104" s="34"/>
       <c r="F104" s="17"/>
     </row>
     <row r="105" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3188,10 +3136,10 @@
       <c r="C105" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D105" s="46">
+      <c r="D105" s="28">
         <v>1000</v>
       </c>
-      <c r="E105" s="45"/>
+      <c r="E105" s="34"/>
       <c r="F105" s="17"/>
     </row>
     <row r="106" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3204,10 +3152,10 @@
       <c r="C106" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D106" s="46">
+      <c r="D106" s="28">
         <v>3500</v>
       </c>
-      <c r="E106" s="45"/>
+      <c r="E106" s="34"/>
       <c r="F106" s="17"/>
     </row>
     <row r="107" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3220,10 +3168,10 @@
       <c r="C107" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D107" s="46">
+      <c r="D107" s="28">
         <v>14900</v>
       </c>
-      <c r="E107" s="45"/>
+      <c r="E107" s="34"/>
       <c r="F107" s="17"/>
     </row>
     <row r="108" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3236,10 +3184,10 @@
       <c r="C108" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D108" s="46">
+      <c r="D108" s="28">
         <v>1000</v>
       </c>
-      <c r="E108" s="45"/>
+      <c r="E108" s="34"/>
       <c r="F108" s="17"/>
     </row>
     <row r="109" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3252,10 +3200,10 @@
       <c r="C109" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D109" s="46">
+      <c r="D109" s="28">
         <v>500</v>
       </c>
-      <c r="E109" s="45"/>
+      <c r="E109" s="34"/>
       <c r="F109" s="17"/>
     </row>
     <row r="110" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3268,10 +3216,10 @@
       <c r="C110" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D110" s="46">
+      <c r="D110" s="28">
         <v>500</v>
       </c>
-      <c r="E110" s="45"/>
+      <c r="E110" s="34"/>
       <c r="F110" s="17"/>
     </row>
     <row r="111" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3284,10 +3232,10 @@
       <c r="C111" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D111" s="46">
+      <c r="D111" s="28">
         <v>500</v>
       </c>
-      <c r="E111" s="45"/>
+      <c r="E111" s="34"/>
       <c r="F111" s="17"/>
     </row>
     <row r="112" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3300,10 +3248,10 @@
       <c r="C112" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D112" s="46">
+      <c r="D112" s="28">
         <v>10000</v>
       </c>
-      <c r="E112" s="45"/>
+      <c r="E112" s="34"/>
       <c r="F112" s="17"/>
     </row>
     <row r="113" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3316,10 +3264,10 @@
       <c r="C113" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D113" s="46">
+      <c r="D113" s="28">
         <v>1000</v>
       </c>
-      <c r="E113" s="45"/>
+      <c r="E113" s="34"/>
       <c r="F113" s="17"/>
     </row>
     <row r="114" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3332,10 +3280,10 @@
       <c r="C114" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D114" s="46">
+      <c r="D114" s="28">
         <v>26500</v>
       </c>
-      <c r="E114" s="45"/>
+      <c r="E114" s="34"/>
       <c r="F114" s="17"/>
     </row>
     <row r="115" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3348,10 +3296,10 @@
       <c r="C115" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D115" s="46">
+      <c r="D115" s="28">
         <v>1000</v>
       </c>
-      <c r="E115" s="45"/>
+      <c r="E115" s="34"/>
       <c r="F115" s="17"/>
     </row>
     <row r="116" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3364,10 +3312,10 @@
       <c r="C116" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D116" s="46">
+      <c r="D116" s="28">
         <v>1600</v>
       </c>
-      <c r="E116" s="45"/>
+      <c r="E116" s="34"/>
       <c r="F116" s="17"/>
     </row>
     <row r="117" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3380,10 +3328,10 @@
       <c r="C117" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D117" s="46">
+      <c r="D117" s="28">
         <v>13800</v>
       </c>
-      <c r="E117" s="45"/>
+      <c r="E117" s="34"/>
       <c r="F117" s="17"/>
     </row>
     <row r="118" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3396,10 +3344,10 @@
       <c r="C118" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D118" s="46">
+      <c r="D118" s="28">
         <v>1000</v>
       </c>
-      <c r="E118" s="45"/>
+      <c r="E118" s="34"/>
       <c r="F118" s="17"/>
     </row>
     <row r="119" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3412,10 +3360,10 @@
       <c r="C119" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D119" s="46">
+      <c r="D119" s="28">
         <v>1000</v>
       </c>
-      <c r="E119" s="45"/>
+      <c r="E119" s="34"/>
       <c r="F119" s="17"/>
     </row>
     <row r="120" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3428,10 +3376,10 @@
       <c r="C120" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D120" s="46">
+      <c r="D120" s="28">
         <v>5600</v>
       </c>
-      <c r="E120" s="45"/>
+      <c r="E120" s="34"/>
       <c r="F120" s="17"/>
     </row>
     <row r="121" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3444,10 +3392,10 @@
       <c r="C121" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D121" s="46">
+      <c r="D121" s="28">
         <v>2000</v>
       </c>
-      <c r="E121" s="45"/>
+      <c r="E121" s="34"/>
       <c r="F121" s="17"/>
     </row>
     <row r="122" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3460,10 +3408,10 @@
       <c r="C122" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D122" s="46">
+      <c r="D122" s="28">
         <v>1000</v>
       </c>
-      <c r="E122" s="45"/>
+      <c r="E122" s="34"/>
       <c r="F122" s="17"/>
     </row>
     <row r="123" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3476,10 +3424,10 @@
       <c r="C123" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D123" s="46">
+      <c r="D123" s="28">
         <v>500</v>
       </c>
-      <c r="E123" s="45"/>
+      <c r="E123" s="34"/>
       <c r="F123" s="17"/>
     </row>
     <row r="124" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3492,10 +3440,10 @@
       <c r="C124" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D124" s="46">
+      <c r="D124" s="28">
         <v>1000</v>
       </c>
-      <c r="E124" s="45"/>
+      <c r="E124" s="34"/>
       <c r="F124" s="17"/>
     </row>
     <row r="125" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3508,10 +3456,10 @@
       <c r="C125" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D125" s="46">
+      <c r="D125" s="28">
         <v>1000</v>
       </c>
-      <c r="E125" s="45"/>
+      <c r="E125" s="34"/>
       <c r="F125" s="17"/>
     </row>
     <row r="126" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3524,10 +3472,10 @@
       <c r="C126" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D126" s="46">
+      <c r="D126" s="28">
         <v>700</v>
       </c>
-      <c r="E126" s="45"/>
+      <c r="E126" s="34"/>
       <c r="F126" s="17"/>
     </row>
     <row r="127" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3540,10 +3488,10 @@
       <c r="C127" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D127" s="46">
+      <c r="D127" s="28">
         <v>1000</v>
       </c>
-      <c r="E127" s="45"/>
+      <c r="E127" s="34"/>
       <c r="F127" s="17"/>
     </row>
     <row r="128" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3556,10 +3504,10 @@
       <c r="C128" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D128" s="46">
+      <c r="D128" s="28">
         <v>1000</v>
       </c>
-      <c r="E128" s="45"/>
+      <c r="E128" s="34"/>
       <c r="F128" s="17"/>
     </row>
     <row r="129" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3572,10 +3520,10 @@
       <c r="C129" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D129" s="46">
+      <c r="D129" s="28">
         <v>3455</v>
       </c>
-      <c r="E129" s="45"/>
+      <c r="E129" s="34"/>
       <c r="F129" s="17"/>
     </row>
     <row r="130" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3588,10 +3536,10 @@
       <c r="C130" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D130" s="46">
+      <c r="D130" s="28">
         <v>500</v>
       </c>
-      <c r="E130" s="45"/>
+      <c r="E130" s="34"/>
       <c r="F130" s="17"/>
     </row>
     <row r="131" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3604,10 +3552,10 @@
       <c r="C131" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D131" s="46">
+      <c r="D131" s="28">
         <v>500</v>
       </c>
-      <c r="E131" s="45"/>
+      <c r="E131" s="34"/>
       <c r="F131" s="17"/>
     </row>
     <row r="132" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3620,10 +3568,10 @@
       <c r="C132" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D132" s="46">
+      <c r="D132" s="28">
         <v>1000</v>
       </c>
-      <c r="E132" s="45"/>
+      <c r="E132" s="34"/>
       <c r="F132" s="17"/>
     </row>
     <row r="133" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3636,10 +3584,10 @@
       <c r="C133" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D133" s="46">
+      <c r="D133" s="28">
         <v>2000</v>
       </c>
-      <c r="E133" s="45"/>
+      <c r="E133" s="34"/>
       <c r="F133" s="17"/>
     </row>
     <row r="134" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3652,10 +3600,10 @@
       <c r="C134" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D134" s="46">
+      <c r="D134" s="28">
         <v>2000</v>
       </c>
-      <c r="E134" s="45"/>
+      <c r="E134" s="34"/>
       <c r="F134" s="17"/>
     </row>
     <row r="135" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3668,10 +3616,10 @@
       <c r="C135" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D135" s="46">
+      <c r="D135" s="28">
         <v>550</v>
       </c>
-      <c r="E135" s="45"/>
+      <c r="E135" s="34"/>
       <c r="F135" s="17"/>
     </row>
     <row r="136" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3684,10 +3632,10 @@
       <c r="C136" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D136" s="46">
+      <c r="D136" s="28">
         <v>1000</v>
       </c>
-      <c r="E136" s="45"/>
+      <c r="E136" s="34"/>
       <c r="F136" s="17"/>
     </row>
     <row r="137" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3700,10 +3648,10 @@
       <c r="C137" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D137" s="46">
+      <c r="D137" s="28">
         <v>12750</v>
       </c>
-      <c r="E137" s="45"/>
+      <c r="E137" s="34"/>
       <c r="F137" s="17"/>
     </row>
     <row r="138" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3716,10 +3664,10 @@
       <c r="C138" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D138" s="46">
+      <c r="D138" s="28">
         <v>500</v>
       </c>
-      <c r="E138" s="45"/>
+      <c r="E138" s="34"/>
       <c r="F138" s="19"/>
     </row>
     <row r="139" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3732,10 +3680,10 @@
       <c r="C139" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D139" s="46">
+      <c r="D139" s="28">
         <v>500</v>
       </c>
-      <c r="E139" s="45"/>
+      <c r="E139" s="34"/>
       <c r="F139" s="17"/>
     </row>
     <row r="140" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3748,10 +3696,10 @@
       <c r="C140" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D140" s="46">
+      <c r="D140" s="28">
         <v>1500</v>
       </c>
-      <c r="E140" s="45"/>
+      <c r="E140" s="34"/>
       <c r="F140" s="17"/>
     </row>
     <row r="141" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3764,10 +3712,10 @@
       <c r="C141" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D141" s="46">
+      <c r="D141" s="28">
         <v>1000</v>
       </c>
-      <c r="E141" s="45"/>
+      <c r="E141" s="34"/>
       <c r="F141" s="17"/>
     </row>
     <row r="142" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3780,10 +3728,10 @@
       <c r="C142" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D142" s="46">
+      <c r="D142" s="28">
         <v>500</v>
       </c>
-      <c r="E142" s="45"/>
+      <c r="E142" s="34"/>
       <c r="F142" s="17"/>
     </row>
     <row r="143" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
@@ -3796,10 +3744,10 @@
       <c r="C143" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D143" s="46">
+      <c r="D143" s="28">
         <v>500</v>
       </c>
-      <c r="E143" s="45"/>
+      <c r="E143" s="34"/>
       <c r="F143" s="17" t="s">
         <v>192</v>
       </c>
@@ -3814,10 +3762,10 @@
       <c r="C144" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D144" s="46">
+      <c r="D144" s="28">
         <v>1000</v>
       </c>
-      <c r="E144" s="45"/>
+      <c r="E144" s="34"/>
       <c r="F144" s="17"/>
     </row>
     <row r="145" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3830,10 +3778,10 @@
       <c r="C145" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D145" s="46">
+      <c r="D145" s="28">
         <v>500</v>
       </c>
-      <c r="E145" s="45"/>
+      <c r="E145" s="34"/>
       <c r="F145" s="17"/>
     </row>
     <row r="146" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3846,10 +3794,10 @@
       <c r="C146" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D146" s="46">
+      <c r="D146" s="28">
         <v>1000</v>
       </c>
-      <c r="E146" s="45"/>
+      <c r="E146" s="34"/>
       <c r="F146" s="18"/>
     </row>
     <row r="147" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3862,10 +3810,10 @@
       <c r="C147" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D147" s="46">
+      <c r="D147" s="28">
         <v>500</v>
       </c>
-      <c r="E147" s="45"/>
+      <c r="E147" s="34"/>
       <c r="F147" s="17"/>
     </row>
     <row r="148" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3878,10 +3826,10 @@
       <c r="C148" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D148" s="46">
+      <c r="D148" s="28">
         <v>3075</v>
       </c>
-      <c r="E148" s="45"/>
+      <c r="E148" s="34"/>
       <c r="F148" s="17"/>
     </row>
     <row r="149" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
@@ -3894,10 +3842,10 @@
       <c r="C149" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D149" s="46">
+      <c r="D149" s="28">
         <v>3500</v>
       </c>
-      <c r="E149" s="45"/>
+      <c r="E149" s="34"/>
       <c r="F149" s="17" t="s">
         <v>193</v>
       </c>
@@ -3912,10 +3860,10 @@
       <c r="C150" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D150" s="46">
+      <c r="D150" s="28">
         <v>5476</v>
       </c>
-      <c r="E150" s="45"/>
+      <c r="E150" s="34"/>
       <c r="F150" s="17"/>
     </row>
     <row r="151" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3928,10 +3876,10 @@
       <c r="C151" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D151" s="46">
+      <c r="D151" s="28">
         <v>21980</v>
       </c>
-      <c r="E151" s="45"/>
+      <c r="E151" s="34"/>
       <c r="F151" s="17"/>
     </row>
     <row r="152" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3944,10 +3892,10 @@
       <c r="C152" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D152" s="46">
+      <c r="D152" s="28">
         <v>24500</v>
       </c>
-      <c r="E152" s="45"/>
+      <c r="E152" s="34"/>
       <c r="F152" s="18"/>
     </row>
     <row r="153" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3960,10 +3908,10 @@
       <c r="C153" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D153" s="46">
+      <c r="D153" s="28">
         <v>11500</v>
       </c>
-      <c r="E153" s="45"/>
+      <c r="E153" s="34"/>
       <c r="F153" s="18"/>
     </row>
     <row r="154" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3976,10 +3924,10 @@
       <c r="C154" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D154" s="46">
+      <c r="D154" s="28">
         <v>2200</v>
       </c>
-      <c r="E154" s="45"/>
+      <c r="E154" s="34"/>
       <c r="F154" s="17"/>
     </row>
     <row r="155" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3992,10 +3940,10 @@
       <c r="C155" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D155" s="46">
+      <c r="D155" s="28">
         <v>550</v>
       </c>
-      <c r="E155" s="45"/>
+      <c r="E155" s="34"/>
       <c r="F155" s="17"/>
     </row>
     <row r="156" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4008,10 +3956,10 @@
       <c r="C156" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D156" s="46">
+      <c r="D156" s="28">
         <v>2200</v>
       </c>
-      <c r="E156" s="45"/>
+      <c r="E156" s="34"/>
       <c r="F156" s="17"/>
     </row>
     <row r="157" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4024,10 +3972,10 @@
       <c r="C157" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D157" s="46">
+      <c r="D157" s="28">
         <v>500</v>
       </c>
-      <c r="E157" s="45"/>
+      <c r="E157" s="34"/>
       <c r="F157" s="17"/>
     </row>
     <row r="158" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4040,10 +3988,10 @@
       <c r="C158" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D158" s="46">
+      <c r="D158" s="28">
         <v>500</v>
       </c>
-      <c r="E158" s="45"/>
+      <c r="E158" s="34"/>
       <c r="F158" s="17"/>
     </row>
     <row r="159" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4056,10 +4004,10 @@
       <c r="C159" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D159" s="46">
+      <c r="D159" s="28">
         <v>550</v>
       </c>
-      <c r="E159" s="45"/>
+      <c r="E159" s="34"/>
       <c r="F159" s="18" t="s">
         <v>194</v>
       </c>
@@ -4074,10 +4022,10 @@
       <c r="C160" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D160" s="46">
+      <c r="D160" s="28">
         <v>1100</v>
       </c>
-      <c r="E160" s="45"/>
+      <c r="E160" s="34"/>
       <c r="F160" s="17"/>
     </row>
     <row r="161" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4090,10 +4038,10 @@
       <c r="C161" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D161" s="46">
+      <c r="D161" s="28">
         <v>500</v>
       </c>
-      <c r="E161" s="45"/>
+      <c r="E161" s="34"/>
       <c r="F161" s="19" t="s">
         <v>195</v>
       </c>
@@ -4108,10 +4056,10 @@
       <c r="C162" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D162" s="46">
+      <c r="D162" s="28">
         <v>20</v>
       </c>
-      <c r="E162" s="45"/>
+      <c r="E162" s="34"/>
       <c r="F162" s="21"/>
     </row>
     <row r="163" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4124,10 +4072,10 @@
       <c r="C163" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D163" s="46">
+      <c r="D163" s="28">
         <v>1000</v>
       </c>
-      <c r="E163" s="45"/>
+      <c r="E163" s="34"/>
       <c r="F163" s="21"/>
     </row>
     <row r="164" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4140,10 +4088,10 @@
       <c r="C164" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D164" s="46">
+      <c r="D164" s="28">
         <v>2000</v>
       </c>
-      <c r="E164" s="45"/>
+      <c r="E164" s="34"/>
       <c r="F164" s="21"/>
     </row>
     <row r="165" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4156,10 +4104,10 @@
       <c r="C165" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D165" s="46">
+      <c r="D165" s="28">
         <v>2000</v>
       </c>
-      <c r="E165" s="45"/>
+      <c r="E165" s="34"/>
       <c r="F165" s="18"/>
     </row>
     <row r="166" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4172,10 +4120,10 @@
       <c r="C166" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D166" s="46">
+      <c r="D166" s="28">
         <v>500</v>
       </c>
-      <c r="E166" s="45"/>
+      <c r="E166" s="34"/>
       <c r="F166" s="21"/>
     </row>
     <row r="167" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4188,10 +4136,10 @@
       <c r="C167" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D167" s="46">
+      <c r="D167" s="28">
         <v>2000</v>
       </c>
-      <c r="E167" s="45"/>
+      <c r="E167" s="34"/>
       <c r="F167" s="21"/>
     </row>
     <row r="168" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4207,7 +4155,7 @@
       <c r="D168" s="21">
         <v>485</v>
       </c>
-      <c r="E168" s="45"/>
+      <c r="E168" s="34"/>
       <c r="F168" s="21" t="s">
         <v>186</v>
       </c>
@@ -4221,14 +4169,14 @@
       <c r="F169" s="3"/>
     </row>
     <row r="170" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="43" t="s">
+      <c r="A170" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B170" s="43"/>
-      <c r="C170" s="43" t="s">
+      <c r="B170" s="32"/>
+      <c r="C170" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D170" s="43"/>
+      <c r="D170" s="32"/>
       <c r="E170" s="24" t="s">
         <v>8</v>
       </c>
@@ -4237,14 +4185,14 @@
       </c>
     </row>
     <row r="171" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="44" t="s">
+      <c r="A171" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B171" s="44"/>
-      <c r="C171" s="44" t="s">
+      <c r="B171" s="33"/>
+      <c r="C171" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D171" s="44"/>
+      <c r="D171" s="33"/>
       <c r="E171" s="27" t="s">
         <v>3</v>
       </c>
@@ -4293,14 +4241,14 @@
       <c r="F176" s="25"/>
     </row>
     <row r="177" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="43" t="s">
+      <c r="A177" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B177" s="43"/>
-      <c r="C177" s="43" t="s">
+      <c r="B177" s="32"/>
+      <c r="C177" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D177" s="43"/>
+      <c r="D177" s="32"/>
       <c r="E177" s="24" t="s">
         <v>5</v>
       </c>
@@ -4330,6 +4278,11 @@
   </sheetData>
   <autoFilter ref="A9:F167" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="13">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A1:B4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A170:B170"/>
     <mergeCell ref="A171:B171"/>
@@ -4338,47 +4291,42 @@
     <mergeCell ref="C171:D171"/>
     <mergeCell ref="C177:D177"/>
     <mergeCell ref="E10:E168"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A1:B4"/>
   </mergeCells>
+  <conditionalFormatting sqref="B10:B167">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44">
-    <cfRule type="duplicateValues" dxfId="10" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F138">
-    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F146">
-    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F161">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F165">
-    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M108:M1048576 B1:B9 M1:M9 B168:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:B167">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03_240626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03_240626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067BDEAC-D790-4EB3-AE9D-42DE2B1769D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF0C119-43BE-4E94-923F-C36C70F92B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,15 +16,15 @@
     <sheet name="XuatKho_SX" sheetId="10" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">XuatKho_SX!$A$9:$F$167</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_SX!$A$1:$J$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">XuatKho_SX!$A$9:$F$166</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_SX!$A$1:$J$176</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="195">
   <si>
     <t>STT</t>
   </si>
@@ -547,9 +547,6 @@
   </si>
   <si>
     <t>Heatsink 8.8 x 8.8 x 12mm</t>
-  </si>
-  <si>
-    <t>100x100x2mm</t>
   </si>
   <si>
     <t>Lò Xo Kẹp 17.6mm</t>
@@ -942,24 +939,6 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -995,6 +974,24 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1476,7 +1473,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L190"/>
+  <dimension ref="A1:L189"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
@@ -1491,56 +1488,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="37" t="s">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="38"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="37" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="38"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="39" t="s">
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="40"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="34"/>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="31"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="43"/>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
@@ -1551,7 +1548,7 @@
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="22" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1605,9 +1602,9 @@
         <v>156</v>
       </c>
       <c r="D10" s="28">
-        <v>500</v>
-      </c>
-      <c r="E10" s="34" t="s">
+        <v>494</v>
+      </c>
+      <c r="E10" s="46" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="17"/>
@@ -1623,9 +1620,9 @@
         <v>156</v>
       </c>
       <c r="D11" s="28">
-        <v>499</v>
-      </c>
-      <c r="E11" s="34"/>
+        <v>493</v>
+      </c>
+      <c r="E11" s="46"/>
       <c r="F11" s="17"/>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1641,7 +1638,7 @@
       <c r="D12" s="28">
         <v>510</v>
       </c>
-      <c r="E12" s="34"/>
+      <c r="E12" s="46"/>
       <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -1657,9 +1654,9 @@
       <c r="D13" s="28">
         <v>6500</v>
       </c>
-      <c r="E13" s="34"/>
+      <c r="E13" s="46"/>
       <c r="F13" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1675,7 +1672,7 @@
       <c r="D14" s="28">
         <v>1000</v>
       </c>
-      <c r="E14" s="34"/>
+      <c r="E14" s="46"/>
       <c r="F14" s="18"/>
     </row>
     <row r="15" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1691,7 +1688,7 @@
       <c r="D15" s="28">
         <v>1000</v>
       </c>
-      <c r="E15" s="34"/>
+      <c r="E15" s="46"/>
       <c r="F15" s="17"/>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1707,7 +1704,7 @@
       <c r="D16" s="28">
         <v>2500</v>
       </c>
-      <c r="E16" s="34"/>
+      <c r="E16" s="46"/>
       <c r="F16" s="17"/>
     </row>
     <row r="17" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1723,7 +1720,7 @@
       <c r="D17" s="28">
         <v>2000</v>
       </c>
-      <c r="E17" s="34"/>
+      <c r="E17" s="46"/>
       <c r="F17" s="17"/>
     </row>
     <row r="18" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1739,7 +1736,7 @@
       <c r="D18" s="28">
         <v>1000</v>
       </c>
-      <c r="E18" s="34"/>
+      <c r="E18" s="46"/>
       <c r="F18" s="17"/>
     </row>
     <row r="19" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1755,7 +1752,7 @@
       <c r="D19" s="28">
         <v>500</v>
       </c>
-      <c r="E19" s="34"/>
+      <c r="E19" s="46"/>
       <c r="F19" s="17"/>
     </row>
     <row r="20" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1771,7 +1768,7 @@
       <c r="D20" s="28">
         <v>45400</v>
       </c>
-      <c r="E20" s="34"/>
+      <c r="E20" s="46"/>
       <c r="F20" s="17"/>
     </row>
     <row r="21" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1787,7 +1784,7 @@
       <c r="D21" s="28">
         <v>1000</v>
       </c>
-      <c r="E21" s="34"/>
+      <c r="E21" s="46"/>
       <c r="F21" s="17"/>
     </row>
     <row r="22" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1803,7 +1800,7 @@
       <c r="D22" s="28">
         <v>500</v>
       </c>
-      <c r="E22" s="34"/>
+      <c r="E22" s="46"/>
       <c r="F22" s="17"/>
     </row>
     <row r="23" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1819,7 +1816,7 @@
       <c r="D23" s="28">
         <v>520</v>
       </c>
-      <c r="E23" s="34"/>
+      <c r="E23" s="46"/>
       <c r="F23" s="17"/>
     </row>
     <row r="24" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1827,7 +1824,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>156</v>
@@ -1835,7 +1832,7 @@
       <c r="D24" s="28">
         <v>500</v>
       </c>
-      <c r="E24" s="34"/>
+      <c r="E24" s="46"/>
       <c r="F24" s="17"/>
     </row>
     <row r="25" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1851,7 +1848,7 @@
       <c r="D25" s="28">
         <v>1500</v>
       </c>
-      <c r="E25" s="34"/>
+      <c r="E25" s="46"/>
       <c r="F25" s="17"/>
     </row>
     <row r="26" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1867,7 +1864,7 @@
       <c r="D26" s="28">
         <v>1500</v>
       </c>
-      <c r="E26" s="34"/>
+      <c r="E26" s="46"/>
       <c r="F26" s="17"/>
     </row>
     <row r="27" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1883,7 +1880,7 @@
       <c r="D27" s="28">
         <v>1500</v>
       </c>
-      <c r="E27" s="34"/>
+      <c r="E27" s="46"/>
       <c r="F27" s="17"/>
     </row>
     <row r="28" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1899,7 +1896,7 @@
       <c r="D28" s="28">
         <v>1500</v>
       </c>
-      <c r="E28" s="34"/>
+      <c r="E28" s="46"/>
       <c r="F28" s="17"/>
     </row>
     <row r="29" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1915,7 +1912,7 @@
       <c r="D29" s="28">
         <v>6500</v>
       </c>
-      <c r="E29" s="34"/>
+      <c r="E29" s="46"/>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1931,7 +1928,7 @@
       <c r="D30" s="28">
         <v>1447</v>
       </c>
-      <c r="E30" s="34"/>
+      <c r="E30" s="46"/>
       <c r="F30" s="17"/>
     </row>
     <row r="31" spans="1:6" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1947,9 +1944,9 @@
       <c r="D31" s="28">
         <v>14000</v>
       </c>
-      <c r="E31" s="34"/>
+      <c r="E31" s="46"/>
       <c r="F31" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1965,7 +1962,7 @@
       <c r="D32" s="28">
         <v>1500</v>
       </c>
-      <c r="E32" s="34"/>
+      <c r="E32" s="46"/>
       <c r="F32" s="17"/>
     </row>
     <row r="33" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1981,7 +1978,7 @@
       <c r="D33" s="28">
         <v>5000</v>
       </c>
-      <c r="E33" s="34"/>
+      <c r="E33" s="46"/>
       <c r="F33" s="17"/>
     </row>
     <row r="34" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1997,7 +1994,7 @@
       <c r="D34" s="28">
         <v>1500</v>
       </c>
-      <c r="E34" s="34"/>
+      <c r="E34" s="46"/>
       <c r="F34" s="17"/>
     </row>
     <row r="35" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2013,7 +2010,7 @@
       <c r="D35" s="28">
         <v>500</v>
       </c>
-      <c r="E35" s="34"/>
+      <c r="E35" s="46"/>
       <c r="F35" s="17"/>
     </row>
     <row r="36" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2029,7 +2026,7 @@
       <c r="D36" s="28">
         <v>2000</v>
       </c>
-      <c r="E36" s="34"/>
+      <c r="E36" s="46"/>
       <c r="F36" s="17"/>
     </row>
     <row r="37" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2045,7 +2042,7 @@
       <c r="D37" s="28">
         <v>1520</v>
       </c>
-      <c r="E37" s="34"/>
+      <c r="E37" s="46"/>
       <c r="F37" s="17"/>
     </row>
     <row r="38" spans="1:6" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2061,7 +2058,7 @@
       <c r="D38" s="28">
         <v>1000</v>
       </c>
-      <c r="E38" s="34"/>
+      <c r="E38" s="46"/>
       <c r="F38" s="17"/>
     </row>
     <row r="39" spans="1:6" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2077,7 +2074,7 @@
       <c r="D39" s="28">
         <v>500</v>
       </c>
-      <c r="E39" s="34"/>
+      <c r="E39" s="46"/>
       <c r="F39" s="17"/>
     </row>
     <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2085,7 +2082,7 @@
         <v>31</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>156</v>
@@ -2093,7 +2090,7 @@
       <c r="D40" s="28">
         <v>520</v>
       </c>
-      <c r="E40" s="34"/>
+      <c r="E40" s="46"/>
       <c r="F40" s="17"/>
     </row>
     <row r="41" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2109,7 +2106,7 @@
       <c r="D41" s="28">
         <v>1500</v>
       </c>
-      <c r="E41" s="34"/>
+      <c r="E41" s="46"/>
       <c r="F41" s="17"/>
     </row>
     <row r="42" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2125,7 +2122,7 @@
       <c r="D42" s="28">
         <v>1600</v>
       </c>
-      <c r="E42" s="34"/>
+      <c r="E42" s="46"/>
       <c r="F42" s="17"/>
     </row>
     <row r="43" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2141,7 +2138,7 @@
       <c r="D43" s="28">
         <v>1000</v>
       </c>
-      <c r="E43" s="34"/>
+      <c r="E43" s="46"/>
       <c r="F43" s="17"/>
     </row>
     <row r="44" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2157,7 +2154,7 @@
       <c r="D44" s="28">
         <v>500</v>
       </c>
-      <c r="E44" s="34"/>
+      <c r="E44" s="46"/>
       <c r="F44" s="18"/>
     </row>
     <row r="45" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2173,7 +2170,7 @@
       <c r="D45" s="28">
         <v>500</v>
       </c>
-      <c r="E45" s="34"/>
+      <c r="E45" s="46"/>
       <c r="F45" s="17"/>
     </row>
     <row r="46" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2189,7 +2186,7 @@
       <c r="D46" s="28">
         <v>500</v>
       </c>
-      <c r="E46" s="34"/>
+      <c r="E46" s="46"/>
       <c r="F46" s="17"/>
     </row>
     <row r="47" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2205,7 +2202,7 @@
       <c r="D47" s="28">
         <v>2050</v>
       </c>
-      <c r="E47" s="34"/>
+      <c r="E47" s="46"/>
       <c r="F47" s="17"/>
     </row>
     <row r="48" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2221,7 +2218,7 @@
       <c r="D48" s="28">
         <v>500</v>
       </c>
-      <c r="E48" s="34"/>
+      <c r="E48" s="46"/>
       <c r="F48" s="17"/>
     </row>
     <row r="49" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2237,7 +2234,7 @@
       <c r="D49" s="28">
         <v>500</v>
       </c>
-      <c r="E49" s="34"/>
+      <c r="E49" s="46"/>
       <c r="F49" s="17"/>
     </row>
     <row r="50" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2253,9 +2250,9 @@
       <c r="D50" s="28">
         <v>1600</v>
       </c>
-      <c r="E50" s="34"/>
+      <c r="E50" s="46"/>
       <c r="F50" s="18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2271,7 +2268,7 @@
       <c r="D51" s="28">
         <v>600</v>
       </c>
-      <c r="E51" s="34"/>
+      <c r="E51" s="46"/>
       <c r="F51" s="17"/>
     </row>
     <row r="52" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2287,7 +2284,7 @@
       <c r="D52" s="28">
         <v>1000</v>
       </c>
-      <c r="E52" s="34"/>
+      <c r="E52" s="46"/>
       <c r="F52" s="17"/>
     </row>
     <row r="53" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2303,7 +2300,7 @@
       <c r="D53" s="28">
         <v>5500</v>
       </c>
-      <c r="E53" s="34"/>
+      <c r="E53" s="46"/>
       <c r="F53" s="17"/>
     </row>
     <row r="54" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2319,7 +2316,7 @@
       <c r="D54" s="28">
         <v>3550</v>
       </c>
-      <c r="E54" s="34"/>
+      <c r="E54" s="46"/>
       <c r="F54" s="17"/>
     </row>
     <row r="55" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2335,7 +2332,7 @@
       <c r="D55" s="28">
         <v>550</v>
       </c>
-      <c r="E55" s="34"/>
+      <c r="E55" s="46"/>
       <c r="F55" s="17"/>
     </row>
     <row r="56" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2351,7 +2348,7 @@
       <c r="D56" s="28">
         <v>1000</v>
       </c>
-      <c r="E56" s="34"/>
+      <c r="E56" s="46"/>
       <c r="F56" s="17"/>
     </row>
     <row r="57" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2367,7 +2364,7 @@
       <c r="D57" s="28">
         <v>2000</v>
       </c>
-      <c r="E57" s="34"/>
+      <c r="E57" s="46"/>
       <c r="F57" s="17"/>
     </row>
     <row r="58" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
@@ -2383,9 +2380,9 @@
       <c r="D58" s="28">
         <v>10770</v>
       </c>
-      <c r="E58" s="34"/>
+      <c r="E58" s="46"/>
       <c r="F58" s="19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2401,7 +2398,7 @@
       <c r="D59" s="28">
         <v>1000</v>
       </c>
-      <c r="E59" s="34"/>
+      <c r="E59" s="46"/>
       <c r="F59" s="17"/>
     </row>
     <row r="60" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2417,7 +2414,7 @@
       <c r="D60" s="28">
         <v>2500</v>
       </c>
-      <c r="E60" s="34"/>
+      <c r="E60" s="46"/>
       <c r="F60" s="17"/>
     </row>
     <row r="61" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2433,7 +2430,7 @@
       <c r="D61" s="28">
         <v>1000</v>
       </c>
-      <c r="E61" s="34"/>
+      <c r="E61" s="46"/>
       <c r="F61" s="17"/>
     </row>
     <row r="62" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2449,9 +2446,9 @@
       <c r="D62" s="28">
         <v>500</v>
       </c>
-      <c r="E62" s="34"/>
+      <c r="E62" s="46"/>
       <c r="F62" s="18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2467,7 +2464,7 @@
       <c r="D63" s="28">
         <v>1000</v>
       </c>
-      <c r="E63" s="34"/>
+      <c r="E63" s="46"/>
       <c r="F63" s="17"/>
     </row>
     <row r="64" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2483,7 +2480,7 @@
       <c r="D64" s="28">
         <v>1500</v>
       </c>
-      <c r="E64" s="34"/>
+      <c r="E64" s="46"/>
       <c r="F64" s="17"/>
     </row>
     <row r="65" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2499,7 +2496,7 @@
       <c r="D65" s="28">
         <v>5500</v>
       </c>
-      <c r="E65" s="34"/>
+      <c r="E65" s="46"/>
       <c r="F65" s="17"/>
     </row>
     <row r="66" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2515,7 +2512,7 @@
       <c r="D66" s="28">
         <v>3000</v>
       </c>
-      <c r="E66" s="34"/>
+      <c r="E66" s="46"/>
       <c r="F66" s="17"/>
     </row>
     <row r="67" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2531,7 +2528,7 @@
       <c r="D67" s="28">
         <v>7400</v>
       </c>
-      <c r="E67" s="34"/>
+      <c r="E67" s="46"/>
       <c r="F67" s="17"/>
     </row>
     <row r="68" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2547,7 +2544,7 @@
       <c r="D68" s="28">
         <v>1500</v>
       </c>
-      <c r="E68" s="34"/>
+      <c r="E68" s="46"/>
       <c r="F68" s="17"/>
     </row>
     <row r="69" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2563,7 +2560,7 @@
       <c r="D69" s="28">
         <v>550</v>
       </c>
-      <c r="E69" s="34"/>
+      <c r="E69" s="46"/>
       <c r="F69" s="17"/>
     </row>
     <row r="70" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2579,7 +2576,7 @@
       <c r="D70" s="28">
         <v>1000</v>
       </c>
-      <c r="E70" s="34"/>
+      <c r="E70" s="46"/>
       <c r="F70" s="17"/>
     </row>
     <row r="71" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2595,7 +2592,7 @@
       <c r="D71" s="28">
         <v>550</v>
       </c>
-      <c r="E71" s="34"/>
+      <c r="E71" s="46"/>
       <c r="F71" s="17"/>
     </row>
     <row r="72" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2611,7 +2608,7 @@
       <c r="D72" s="28">
         <v>500</v>
       </c>
-      <c r="E72" s="34"/>
+      <c r="E72" s="46"/>
       <c r="F72" s="17"/>
     </row>
     <row r="73" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2627,7 +2624,7 @@
       <c r="D73" s="28">
         <v>2500</v>
       </c>
-      <c r="E73" s="34"/>
+      <c r="E73" s="46"/>
       <c r="F73" s="17"/>
     </row>
     <row r="74" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2643,7 +2640,7 @@
       <c r="D74" s="28">
         <v>1500</v>
       </c>
-      <c r="E74" s="34"/>
+      <c r="E74" s="46"/>
       <c r="F74" s="17"/>
     </row>
     <row r="75" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2659,7 +2656,7 @@
       <c r="D75" s="28">
         <v>1000</v>
       </c>
-      <c r="E75" s="34"/>
+      <c r="E75" s="46"/>
       <c r="F75" s="17"/>
     </row>
     <row r="76" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2675,7 +2672,7 @@
       <c r="D76" s="28">
         <v>550</v>
       </c>
-      <c r="E76" s="34"/>
+      <c r="E76" s="46"/>
       <c r="F76" s="17"/>
     </row>
     <row r="77" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2691,7 +2688,7 @@
       <c r="D77" s="28">
         <v>1000</v>
       </c>
-      <c r="E77" s="34"/>
+      <c r="E77" s="46"/>
       <c r="F77" s="17"/>
     </row>
     <row r="78" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2707,7 +2704,7 @@
       <c r="D78" s="28">
         <v>1000</v>
       </c>
-      <c r="E78" s="34"/>
+      <c r="E78" s="46"/>
       <c r="F78" s="17"/>
     </row>
     <row r="79" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2723,7 +2720,7 @@
       <c r="D79" s="28">
         <v>500</v>
       </c>
-      <c r="E79" s="34"/>
+      <c r="E79" s="46"/>
       <c r="F79" s="17"/>
     </row>
     <row r="80" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2739,7 +2736,7 @@
       <c r="D80" s="28">
         <v>600</v>
       </c>
-      <c r="E80" s="34"/>
+      <c r="E80" s="46"/>
       <c r="F80" s="17"/>
     </row>
     <row r="81" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2755,7 +2752,7 @@
       <c r="D81" s="28">
         <v>500</v>
       </c>
-      <c r="E81" s="34"/>
+      <c r="E81" s="46"/>
       <c r="F81" s="17"/>
     </row>
     <row r="82" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2771,7 +2768,7 @@
       <c r="D82" s="28">
         <v>500</v>
       </c>
-      <c r="E82" s="34"/>
+      <c r="E82" s="46"/>
       <c r="F82" s="17"/>
     </row>
     <row r="83" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2787,7 +2784,7 @@
       <c r="D83" s="28">
         <v>500</v>
       </c>
-      <c r="E83" s="34"/>
+      <c r="E83" s="46"/>
       <c r="F83" s="17"/>
     </row>
     <row r="84" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2803,7 +2800,7 @@
       <c r="D84" s="28">
         <v>1500</v>
       </c>
-      <c r="E84" s="34"/>
+      <c r="E84" s="46"/>
       <c r="F84" s="17"/>
     </row>
     <row r="85" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2819,7 +2816,7 @@
       <c r="D85" s="28">
         <v>500</v>
       </c>
-      <c r="E85" s="34"/>
+      <c r="E85" s="46"/>
       <c r="F85" s="17"/>
     </row>
     <row r="86" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2827,7 +2824,7 @@
         <v>77</v>
       </c>
       <c r="B86" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C86" s="17" t="s">
         <v>156</v>
@@ -2835,7 +2832,7 @@
       <c r="D86" s="28">
         <v>500</v>
       </c>
-      <c r="E86" s="34"/>
+      <c r="E86" s="46"/>
       <c r="F86" s="17"/>
     </row>
     <row r="87" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2851,7 +2848,7 @@
       <c r="D87" s="28">
         <v>1000</v>
       </c>
-      <c r="E87" s="34"/>
+      <c r="E87" s="46"/>
       <c r="F87" s="17"/>
     </row>
     <row r="88" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2867,7 +2864,7 @@
       <c r="D88" s="28">
         <v>1000</v>
       </c>
-      <c r="E88" s="34"/>
+      <c r="E88" s="46"/>
       <c r="F88" s="17"/>
     </row>
     <row r="89" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2883,7 +2880,7 @@
       <c r="D89" s="28">
         <v>4000</v>
       </c>
-      <c r="E89" s="34"/>
+      <c r="E89" s="46"/>
       <c r="F89" s="17"/>
     </row>
     <row r="90" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2899,7 +2896,7 @@
       <c r="D90" s="28">
         <v>2500</v>
       </c>
-      <c r="E90" s="34"/>
+      <c r="E90" s="46"/>
       <c r="F90" s="17"/>
     </row>
     <row r="91" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2915,7 +2912,7 @@
       <c r="D91" s="28">
         <v>500</v>
       </c>
-      <c r="E91" s="34"/>
+      <c r="E91" s="46"/>
       <c r="F91" s="17"/>
     </row>
     <row r="92" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2931,7 +2928,7 @@
       <c r="D92" s="28">
         <v>500</v>
       </c>
-      <c r="E92" s="34"/>
+      <c r="E92" s="46"/>
       <c r="F92" s="17"/>
     </row>
     <row r="93" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2945,9 +2942,9 @@
         <v>156</v>
       </c>
       <c r="D93" s="28">
-        <v>8830</v>
-      </c>
-      <c r="E93" s="34"/>
+        <v>8820</v>
+      </c>
+      <c r="E93" s="46"/>
       <c r="F93" s="17"/>
     </row>
     <row r="94" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2963,7 +2960,7 @@
       <c r="D94" s="28">
         <v>500</v>
       </c>
-      <c r="E94" s="34"/>
+      <c r="E94" s="46"/>
       <c r="F94" s="17"/>
     </row>
     <row r="95" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2979,7 +2976,7 @@
       <c r="D95" s="28">
         <v>1000</v>
       </c>
-      <c r="E95" s="34"/>
+      <c r="E95" s="46"/>
       <c r="F95" s="17"/>
     </row>
     <row r="96" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2995,7 +2992,7 @@
       <c r="D96" s="28">
         <v>500</v>
       </c>
-      <c r="E96" s="34"/>
+      <c r="E96" s="46"/>
       <c r="F96" s="17"/>
     </row>
     <row r="97" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3011,7 +3008,7 @@
       <c r="D97" s="28">
         <v>6500</v>
       </c>
-      <c r="E97" s="34"/>
+      <c r="E97" s="46"/>
       <c r="F97" s="17"/>
     </row>
     <row r="98" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3027,7 +3024,7 @@
       <c r="D98" s="28">
         <v>1000</v>
       </c>
-      <c r="E98" s="34"/>
+      <c r="E98" s="46"/>
       <c r="F98" s="17"/>
     </row>
     <row r="99" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3043,7 +3040,7 @@
       <c r="D99" s="28">
         <v>1100</v>
       </c>
-      <c r="E99" s="34"/>
+      <c r="E99" s="46"/>
       <c r="F99" s="17"/>
     </row>
     <row r="100" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3059,7 +3056,7 @@
       <c r="D100" s="28">
         <v>1000</v>
       </c>
-      <c r="E100" s="34"/>
+      <c r="E100" s="46"/>
       <c r="F100" s="17"/>
     </row>
     <row r="101" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3075,7 +3072,7 @@
       <c r="D101" s="28">
         <v>1000</v>
       </c>
-      <c r="E101" s="34"/>
+      <c r="E101" s="46"/>
       <c r="F101" s="17"/>
     </row>
     <row r="102" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3091,7 +3088,7 @@
       <c r="D102" s="28">
         <v>1000</v>
       </c>
-      <c r="E102" s="34"/>
+      <c r="E102" s="46"/>
       <c r="F102" s="17"/>
     </row>
     <row r="103" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3107,7 +3104,7 @@
       <c r="D103" s="28">
         <v>500</v>
       </c>
-      <c r="E103" s="34"/>
+      <c r="E103" s="46"/>
       <c r="F103" s="17"/>
     </row>
     <row r="104" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3123,7 +3120,7 @@
       <c r="D104" s="28">
         <v>1000</v>
       </c>
-      <c r="E104" s="34"/>
+      <c r="E104" s="46"/>
       <c r="F104" s="17"/>
     </row>
     <row r="105" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3139,7 +3136,7 @@
       <c r="D105" s="28">
         <v>1000</v>
       </c>
-      <c r="E105" s="34"/>
+      <c r="E105" s="46"/>
       <c r="F105" s="17"/>
     </row>
     <row r="106" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3155,7 +3152,7 @@
       <c r="D106" s="28">
         <v>3500</v>
       </c>
-      <c r="E106" s="34"/>
+      <c r="E106" s="46"/>
       <c r="F106" s="17"/>
     </row>
     <row r="107" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3171,7 +3168,7 @@
       <c r="D107" s="28">
         <v>14900</v>
       </c>
-      <c r="E107" s="34"/>
+      <c r="E107" s="46"/>
       <c r="F107" s="17"/>
     </row>
     <row r="108" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3187,7 +3184,7 @@
       <c r="D108" s="28">
         <v>1000</v>
       </c>
-      <c r="E108" s="34"/>
+      <c r="E108" s="46"/>
       <c r="F108" s="17"/>
     </row>
     <row r="109" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3203,7 +3200,7 @@
       <c r="D109" s="28">
         <v>500</v>
       </c>
-      <c r="E109" s="34"/>
+      <c r="E109" s="46"/>
       <c r="F109" s="17"/>
     </row>
     <row r="110" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3219,7 +3216,7 @@
       <c r="D110" s="28">
         <v>500</v>
       </c>
-      <c r="E110" s="34"/>
+      <c r="E110" s="46"/>
       <c r="F110" s="17"/>
     </row>
     <row r="111" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3235,7 +3232,7 @@
       <c r="D111" s="28">
         <v>500</v>
       </c>
-      <c r="E111" s="34"/>
+      <c r="E111" s="46"/>
       <c r="F111" s="17"/>
     </row>
     <row r="112" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3251,7 +3248,7 @@
       <c r="D112" s="28">
         <v>10000</v>
       </c>
-      <c r="E112" s="34"/>
+      <c r="E112" s="46"/>
       <c r="F112" s="17"/>
     </row>
     <row r="113" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3267,7 +3264,7 @@
       <c r="D113" s="28">
         <v>1000</v>
       </c>
-      <c r="E113" s="34"/>
+      <c r="E113" s="46"/>
       <c r="F113" s="17"/>
     </row>
     <row r="114" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3283,7 +3280,7 @@
       <c r="D114" s="28">
         <v>26500</v>
       </c>
-      <c r="E114" s="34"/>
+      <c r="E114" s="46"/>
       <c r="F114" s="17"/>
     </row>
     <row r="115" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3299,7 +3296,7 @@
       <c r="D115" s="28">
         <v>1000</v>
       </c>
-      <c r="E115" s="34"/>
+      <c r="E115" s="46"/>
       <c r="F115" s="17"/>
     </row>
     <row r="116" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3315,7 +3312,7 @@
       <c r="D116" s="28">
         <v>1600</v>
       </c>
-      <c r="E116" s="34"/>
+      <c r="E116" s="46"/>
       <c r="F116" s="17"/>
     </row>
     <row r="117" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3331,7 +3328,7 @@
       <c r="D117" s="28">
         <v>13800</v>
       </c>
-      <c r="E117" s="34"/>
+      <c r="E117" s="46"/>
       <c r="F117" s="17"/>
     </row>
     <row r="118" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3347,7 +3344,7 @@
       <c r="D118" s="28">
         <v>1000</v>
       </c>
-      <c r="E118" s="34"/>
+      <c r="E118" s="46"/>
       <c r="F118" s="17"/>
     </row>
     <row r="119" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3363,7 +3360,7 @@
       <c r="D119" s="28">
         <v>1000</v>
       </c>
-      <c r="E119" s="34"/>
+      <c r="E119" s="46"/>
       <c r="F119" s="17"/>
     </row>
     <row r="120" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3379,7 +3376,7 @@
       <c r="D120" s="28">
         <v>5600</v>
       </c>
-      <c r="E120" s="34"/>
+      <c r="E120" s="46"/>
       <c r="F120" s="17"/>
     </row>
     <row r="121" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3395,7 +3392,7 @@
       <c r="D121" s="28">
         <v>2000</v>
       </c>
-      <c r="E121" s="34"/>
+      <c r="E121" s="46"/>
       <c r="F121" s="17"/>
     </row>
     <row r="122" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3411,7 +3408,7 @@
       <c r="D122" s="28">
         <v>1000</v>
       </c>
-      <c r="E122" s="34"/>
+      <c r="E122" s="46"/>
       <c r="F122" s="17"/>
     </row>
     <row r="123" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3427,7 +3424,7 @@
       <c r="D123" s="28">
         <v>500</v>
       </c>
-      <c r="E123" s="34"/>
+      <c r="E123" s="46"/>
       <c r="F123" s="17"/>
     </row>
     <row r="124" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3443,7 +3440,7 @@
       <c r="D124" s="28">
         <v>1000</v>
       </c>
-      <c r="E124" s="34"/>
+      <c r="E124" s="46"/>
       <c r="F124" s="17"/>
     </row>
     <row r="125" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3459,7 +3456,7 @@
       <c r="D125" s="28">
         <v>1000</v>
       </c>
-      <c r="E125" s="34"/>
+      <c r="E125" s="46"/>
       <c r="F125" s="17"/>
     </row>
     <row r="126" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3475,7 +3472,7 @@
       <c r="D126" s="28">
         <v>700</v>
       </c>
-      <c r="E126" s="34"/>
+      <c r="E126" s="46"/>
       <c r="F126" s="17"/>
     </row>
     <row r="127" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3491,7 +3488,7 @@
       <c r="D127" s="28">
         <v>1000</v>
       </c>
-      <c r="E127" s="34"/>
+      <c r="E127" s="46"/>
       <c r="F127" s="17"/>
     </row>
     <row r="128" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3507,7 +3504,7 @@
       <c r="D128" s="28">
         <v>1000</v>
       </c>
-      <c r="E128" s="34"/>
+      <c r="E128" s="46"/>
       <c r="F128" s="17"/>
     </row>
     <row r="129" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3523,7 +3520,7 @@
       <c r="D129" s="28">
         <v>3455</v>
       </c>
-      <c r="E129" s="34"/>
+      <c r="E129" s="46"/>
       <c r="F129" s="17"/>
     </row>
     <row r="130" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3539,7 +3536,7 @@
       <c r="D130" s="28">
         <v>500</v>
       </c>
-      <c r="E130" s="34"/>
+      <c r="E130" s="46"/>
       <c r="F130" s="17"/>
     </row>
     <row r="131" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3555,7 +3552,7 @@
       <c r="D131" s="28">
         <v>500</v>
       </c>
-      <c r="E131" s="34"/>
+      <c r="E131" s="46"/>
       <c r="F131" s="17"/>
     </row>
     <row r="132" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3571,7 +3568,7 @@
       <c r="D132" s="28">
         <v>1000</v>
       </c>
-      <c r="E132" s="34"/>
+      <c r="E132" s="46"/>
       <c r="F132" s="17"/>
     </row>
     <row r="133" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3587,7 +3584,7 @@
       <c r="D133" s="28">
         <v>2000</v>
       </c>
-      <c r="E133" s="34"/>
+      <c r="E133" s="46"/>
       <c r="F133" s="17"/>
     </row>
     <row r="134" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3603,7 +3600,7 @@
       <c r="D134" s="28">
         <v>2000</v>
       </c>
-      <c r="E134" s="34"/>
+      <c r="E134" s="46"/>
       <c r="F134" s="17"/>
     </row>
     <row r="135" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3619,7 +3616,7 @@
       <c r="D135" s="28">
         <v>550</v>
       </c>
-      <c r="E135" s="34"/>
+      <c r="E135" s="46"/>
       <c r="F135" s="17"/>
     </row>
     <row r="136" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3635,7 +3632,7 @@
       <c r="D136" s="28">
         <v>1000</v>
       </c>
-      <c r="E136" s="34"/>
+      <c r="E136" s="46"/>
       <c r="F136" s="17"/>
     </row>
     <row r="137" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3651,7 +3648,7 @@
       <c r="D137" s="28">
         <v>12750</v>
       </c>
-      <c r="E137" s="34"/>
+      <c r="E137" s="46"/>
       <c r="F137" s="17"/>
     </row>
     <row r="138" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3667,7 +3664,7 @@
       <c r="D138" s="28">
         <v>500</v>
       </c>
-      <c r="E138" s="34"/>
+      <c r="E138" s="46"/>
       <c r="F138" s="19"/>
     </row>
     <row r="139" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3683,7 +3680,7 @@
       <c r="D139" s="28">
         <v>500</v>
       </c>
-      <c r="E139" s="34"/>
+      <c r="E139" s="46"/>
       <c r="F139" s="17"/>
     </row>
     <row r="140" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3699,7 +3696,7 @@
       <c r="D140" s="28">
         <v>1500</v>
       </c>
-      <c r="E140" s="34"/>
+      <c r="E140" s="46"/>
       <c r="F140" s="17"/>
     </row>
     <row r="141" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3715,7 +3712,7 @@
       <c r="D141" s="28">
         <v>1000</v>
       </c>
-      <c r="E141" s="34"/>
+      <c r="E141" s="46"/>
       <c r="F141" s="17"/>
     </row>
     <row r="142" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3731,7 +3728,7 @@
       <c r="D142" s="28">
         <v>500</v>
       </c>
-      <c r="E142" s="34"/>
+      <c r="E142" s="46"/>
       <c r="F142" s="17"/>
     </row>
     <row r="143" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
@@ -3747,9 +3744,9 @@
       <c r="D143" s="28">
         <v>500</v>
       </c>
-      <c r="E143" s="34"/>
+      <c r="E143" s="46"/>
       <c r="F143" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="144" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3765,7 +3762,7 @@
       <c r="D144" s="28">
         <v>1000</v>
       </c>
-      <c r="E144" s="34"/>
+      <c r="E144" s="46"/>
       <c r="F144" s="17"/>
     </row>
     <row r="145" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3781,7 +3778,7 @@
       <c r="D145" s="28">
         <v>500</v>
       </c>
-      <c r="E145" s="34"/>
+      <c r="E145" s="46"/>
       <c r="F145" s="17"/>
     </row>
     <row r="146" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3797,7 +3794,7 @@
       <c r="D146" s="28">
         <v>1000</v>
       </c>
-      <c r="E146" s="34"/>
+      <c r="E146" s="46"/>
       <c r="F146" s="18"/>
     </row>
     <row r="147" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3813,7 +3810,7 @@
       <c r="D147" s="28">
         <v>500</v>
       </c>
-      <c r="E147" s="34"/>
+      <c r="E147" s="46"/>
       <c r="F147" s="17"/>
     </row>
     <row r="148" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3829,7 +3826,7 @@
       <c r="D148" s="28">
         <v>3075</v>
       </c>
-      <c r="E148" s="34"/>
+      <c r="E148" s="46"/>
       <c r="F148" s="17"/>
     </row>
     <row r="149" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
@@ -3837,7 +3834,7 @@
         <v>140</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C149" s="17" t="s">
         <v>156</v>
@@ -3845,9 +3842,9 @@
       <c r="D149" s="28">
         <v>3500</v>
       </c>
-      <c r="E149" s="34"/>
+      <c r="E149" s="46"/>
       <c r="F149" s="17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="150" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3863,7 +3860,7 @@
       <c r="D150" s="28">
         <v>5476</v>
       </c>
-      <c r="E150" s="34"/>
+      <c r="E150" s="46"/>
       <c r="F150" s="17"/>
     </row>
     <row r="151" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3879,7 +3876,7 @@
       <c r="D151" s="28">
         <v>21980</v>
       </c>
-      <c r="E151" s="34"/>
+      <c r="E151" s="46"/>
       <c r="F151" s="17"/>
     </row>
     <row r="152" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3895,7 +3892,7 @@
       <c r="D152" s="28">
         <v>24500</v>
       </c>
-      <c r="E152" s="34"/>
+      <c r="E152" s="46"/>
       <c r="F152" s="18"/>
     </row>
     <row r="153" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3909,9 +3906,9 @@
         <v>156</v>
       </c>
       <c r="D153" s="28">
-        <v>11500</v>
-      </c>
-      <c r="E153" s="34"/>
+        <v>11000</v>
+      </c>
+      <c r="E153" s="46"/>
       <c r="F153" s="18"/>
     </row>
     <row r="154" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3927,7 +3924,7 @@
       <c r="D154" s="28">
         <v>2200</v>
       </c>
-      <c r="E154" s="34"/>
+      <c r="E154" s="46"/>
       <c r="F154" s="17"/>
     </row>
     <row r="155" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3941,9 +3938,9 @@
         <v>156</v>
       </c>
       <c r="D155" s="28">
-        <v>550</v>
-      </c>
-      <c r="E155" s="34"/>
+        <v>500</v>
+      </c>
+      <c r="E155" s="46"/>
       <c r="F155" s="17"/>
     </row>
     <row r="156" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3957,9 +3954,9 @@
         <v>156</v>
       </c>
       <c r="D156" s="28">
-        <v>2200</v>
-      </c>
-      <c r="E156" s="34"/>
+        <v>2000</v>
+      </c>
+      <c r="E156" s="46"/>
       <c r="F156" s="17"/>
     </row>
     <row r="157" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3973,9 +3970,9 @@
         <v>156</v>
       </c>
       <c r="D157" s="28">
-        <v>500</v>
-      </c>
-      <c r="E157" s="34"/>
+        <v>100</v>
+      </c>
+      <c r="E157" s="46"/>
       <c r="F157" s="17"/>
     </row>
     <row r="158" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3991,7 +3988,7 @@
       <c r="D158" s="28">
         <v>500</v>
       </c>
-      <c r="E158" s="34"/>
+      <c r="E158" s="46"/>
       <c r="F158" s="17"/>
     </row>
     <row r="159" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4005,11 +4002,11 @@
         <v>156</v>
       </c>
       <c r="D159" s="28">
-        <v>550</v>
-      </c>
-      <c r="E159" s="34"/>
+        <v>500</v>
+      </c>
+      <c r="E159" s="46"/>
       <c r="F159" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="160" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4025,7 +4022,7 @@
       <c r="D160" s="28">
         <v>1100</v>
       </c>
-      <c r="E160" s="34"/>
+      <c r="E160" s="46"/>
       <c r="F160" s="17"/>
     </row>
     <row r="161" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4041,9 +4038,9 @@
       <c r="D161" s="28">
         <v>500</v>
       </c>
-      <c r="E161" s="34"/>
+      <c r="E161" s="46"/>
       <c r="F161" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="162" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4057,9 +4054,9 @@
         <v>156</v>
       </c>
       <c r="D162" s="28">
-        <v>20</v>
-      </c>
-      <c r="E162" s="34"/>
+        <v>1000</v>
+      </c>
+      <c r="E162" s="46"/>
       <c r="F162" s="21"/>
     </row>
     <row r="163" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4073,9 +4070,9 @@
         <v>156</v>
       </c>
       <c r="D163" s="28">
-        <v>1000</v>
-      </c>
-      <c r="E163" s="34"/>
+        <v>2000</v>
+      </c>
+      <c r="E163" s="46"/>
       <c r="F163" s="21"/>
     </row>
     <row r="164" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4091,8 +4088,8 @@
       <c r="D164" s="28">
         <v>2000</v>
       </c>
-      <c r="E164" s="34"/>
-      <c r="F164" s="21"/>
+      <c r="E164" s="46"/>
+      <c r="F164" s="18"/>
     </row>
     <row r="165" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A165" s="17">
@@ -4105,10 +4102,10 @@
         <v>156</v>
       </c>
       <c r="D165" s="28">
-        <v>2000</v>
-      </c>
-      <c r="E165" s="34"/>
-      <c r="F165" s="18"/>
+        <v>500</v>
+      </c>
+      <c r="E165" s="46"/>
+      <c r="F165" s="21"/>
     </row>
     <row r="166" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A166" s="17">
@@ -4121,84 +4118,76 @@
         <v>156</v>
       </c>
       <c r="D166" s="28">
-        <v>500</v>
-      </c>
-      <c r="E166" s="34"/>
+        <v>2000</v>
+      </c>
+      <c r="E166" s="46"/>
       <c r="F166" s="21"/>
     </row>
     <row r="167" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A167" s="17">
         <v>158</v>
       </c>
-      <c r="B167" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="C167" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="D167" s="28">
-        <v>2000</v>
-      </c>
-      <c r="E167" s="34"/>
-      <c r="F167" s="21"/>
+      <c r="B167" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C167" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D167" s="21">
+        <v>485</v>
+      </c>
+      <c r="E167" s="46"/>
+      <c r="F167" s="21" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="168" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="21">
-        <v>159</v>
-      </c>
-      <c r="B168" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="C168" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D168" s="21">
-        <v>485</v>
-      </c>
-      <c r="E168" s="34"/>
-      <c r="F168" s="21" t="s">
-        <v>186</v>
-      </c>
+      <c r="A168" s="6"/>
+      <c r="B168" s="10"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="3"/>
+      <c r="F168" s="3"/>
     </row>
     <row r="169" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="6"/>
-      <c r="B169" s="10"/>
-      <c r="C169" s="3"/>
-      <c r="D169" s="3"/>
-      <c r="E169" s="3"/>
-      <c r="F169" s="3"/>
-    </row>
-    <row r="170" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="32" t="s">
+      <c r="A169" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B170" s="32"/>
-      <c r="C170" s="32" t="s">
+      <c r="B169" s="44"/>
+      <c r="C169" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="D170" s="32"/>
-      <c r="E170" s="24" t="s">
+      <c r="D169" s="44"/>
+      <c r="E169" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="F170" s="24" t="s">
+      <c r="F169" s="24" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="33" t="s">
+    <row r="170" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B171" s="33"/>
-      <c r="C171" s="33" t="s">
+      <c r="B170" s="45"/>
+      <c r="C170" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D171" s="33"/>
-      <c r="E171" s="27" t="s">
+      <c r="D170" s="45"/>
+      <c r="E170" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F171" s="27" t="s">
+      <c r="F170" s="27" t="s">
         <v>3</v>
       </c>
+    </row>
+    <row r="171" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="25"/>
+      <c r="B171" s="25"/>
+      <c r="C171" s="25"/>
+      <c r="D171" s="25"/>
+      <c r="E171" s="26"/>
+      <c r="F171" s="25"/>
     </row>
     <row r="172" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A172" s="25"/>
@@ -4212,7 +4201,7 @@
       <c r="A173" s="25"/>
       <c r="B173" s="25"/>
       <c r="C173" s="25"/>
-      <c r="D173" s="25"/>
+      <c r="D173" s="23"/>
       <c r="E173" s="26"/>
       <c r="F173" s="25"/>
     </row>
@@ -4220,8 +4209,8 @@
       <c r="A174" s="25"/>
       <c r="B174" s="25"/>
       <c r="C174" s="25"/>
-      <c r="D174" s="23"/>
-      <c r="E174" s="26"/>
+      <c r="D174" s="25"/>
+      <c r="E174" s="25"/>
       <c r="F174" s="25"/>
     </row>
     <row r="175" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4229,104 +4218,96 @@
       <c r="B175" s="25"/>
       <c r="C175" s="25"/>
       <c r="D175" s="25"/>
-      <c r="E175" s="25"/>
+      <c r="E175" s="26"/>
       <c r="F175" s="25"/>
     </row>
-    <row r="176" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="25"/>
-      <c r="B176" s="25"/>
-      <c r="C176" s="25"/>
-      <c r="D176" s="25"/>
-      <c r="E176" s="26"/>
-      <c r="F176" s="25"/>
-    </row>
-    <row r="177" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="32" t="s">
+    <row r="176" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B177" s="32"/>
-      <c r="C177" s="32" t="s">
+      <c r="B176" s="44"/>
+      <c r="C176" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D177" s="32"/>
-      <c r="E177" s="24" t="s">
+      <c r="D176" s="44"/>
+      <c r="E176" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="F177" s="24" t="s">
+      <c r="F176" s="24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="179" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E179" s="9"/>
-      <c r="F179" s="9"/>
-    </row>
-    <row r="180" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="181" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="182" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="183" spans="1:6" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
-      <c r="E183" s="8"/>
-      <c r="F183" s="8"/>
-    </row>
-    <row r="184" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="185" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="190" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="F190" s="5"/>
+    <row r="177" spans="3:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="178" spans="3:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E178" s="9"/>
+      <c r="F178" s="9"/>
+    </row>
+    <row r="179" spans="3:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="180" spans="3:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="181" spans="3:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="182" spans="3:6" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="C182" s="8"/>
+      <c r="D182" s="8"/>
+      <c r="E182" s="8"/>
+      <c r="F182" s="8"/>
+    </row>
+    <row r="183" spans="3:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="184" spans="3:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="189" spans="3:6" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="F189" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:F167" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A9:F166" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="13">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A169:B169"/>
+    <mergeCell ref="A170:B170"/>
+    <mergeCell ref="A176:B176"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="E10:E167"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="A1:B4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A170:B170"/>
-    <mergeCell ref="A171:B171"/>
-    <mergeCell ref="A177:B177"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="E10:E168"/>
   </mergeCells>
-  <conditionalFormatting sqref="B10:B167">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44">
-    <cfRule type="duplicateValues" dxfId="9" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F138">
-    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F146">
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159">
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F161">
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F165">
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+  <conditionalFormatting sqref="F164">
+    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M108:M1048576 B1:B9 M1:M9 B168:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="B167:B1048576 M108:M1048576 B1:B9 M1:M9">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:B166">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
